--- a/data_contrast/experiment_data.xlsx
+++ b/data_contrast/experiment_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\data_contrast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_4995F8DE1743DA82B86ED5505665B8B14E944330" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F722B5F-875E-44E3-8300-BF3111F16B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>仿真值</t>
   </si>
@@ -39,13 +39,10 @@
     <t>实测值</t>
   </si>
   <si>
-    <t>仿真值与实测值的相对误差</t>
+    <t>模型预测值(使用特征工程)</t>
   </si>
   <si>
-    <t>模型预测值</t>
-  </si>
-  <si>
-    <t>模型预测值与实测值的相对误差</t>
+    <t>模型预测值(未使用特征工程)</t>
   </si>
   <si>
     <t>N</t>
@@ -92,26 +89,11 @@
   <si>
     <t>R[Ω]</t>
   </si>
-  <si>
-    <t>电感相对误差%</t>
-  </si>
-  <si>
-    <t>电阻相对误差%</t>
-  </si>
-  <si>
-    <t>电感平均相对误差%</t>
-  </si>
-  <si>
-    <t>电阻平均相对误差%</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -151,19 +133,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -175,6 +154,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -488,18 +474,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB51"/>
+  <dimension ref="A1:Z49"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="20" max="20" width="17.875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="18" style="1" customWidth="1"/>
+    <col min="20" max="21" width="13.75" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="16.375" style="1" customWidth="1"/>
-    <col min="28" max="28" width="17" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="L1" t="s">
         <v>0</v>
       </c>
       <c r="P1" t="s">
@@ -508,85 +491,79 @@
       <c r="T1" t="s">
         <v>2</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>3</v>
       </c>
-      <c r="AA1" t="s">
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>12</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" t="s">
+      <c r="L2" t="s">
         <v>14</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>15</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>16</v>
       </c>
-      <c r="N2" t="s">
+      <c r="P2" t="s">
         <v>17</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" t="s">
-        <v>19</v>
-      </c>
       <c r="R2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" t="s">
         <v>17</v>
       </c>
-      <c r="T2" t="s">
-        <v>20</v>
-      </c>
       <c r="U2" t="s">
-        <v>21</v>
-      </c>
-      <c r="W2" t="s">
         <v>18</v>
       </c>
+      <c r="V2" t="s">
+        <v>16</v>
+      </c>
       <c r="X2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -640,34 +617,28 @@
         <f t="shared" ref="R3:R49" si="4">6780000*2*3.1415926*P3*0.000001/Q3</f>
         <v>88.449435412259007</v>
       </c>
-      <c r="T3" s="2">
-        <f t="shared" ref="T3:T49" si="5">ABS(L3-P3)/P3*100</f>
-        <v>89.799243991989314</v>
-      </c>
-      <c r="U3" s="2">
-        <f t="shared" ref="U3:U49" si="6">ABS(M3-Q3)/Q3*100</f>
-        <v>2.3328131857977752</v>
-      </c>
-      <c r="W3">
-        <v>0.24802376329898829</v>
+      <c r="T3">
+        <v>0.12408220767974849</v>
+      </c>
+      <c r="U3">
+        <v>7.6971098780632019E-2</v>
+      </c>
+      <c r="V3">
+        <f>6780000*2*3.1415926*T3*0.000001/U3</f>
+        <v>68.673847611413464</v>
       </c>
       <c r="X3">
-        <v>0.1059732288122177</v>
+        <v>0.1031891107559204</v>
       </c>
       <c r="Y3">
-        <f t="shared" ref="Y3:Y49" si="7">6780000*2*3.1415926*W3*0.000001/X3</f>
-        <v>99.702645258115766</v>
-      </c>
-      <c r="AA3" s="2">
-        <f t="shared" ref="AA3:AA49" si="8">ABS(W3-P3)/P3*100</f>
-        <v>37.974946205489701</v>
-      </c>
-      <c r="AB3" s="2">
-        <f t="shared" ref="AB3:AB49" si="9">ABS(X3-Q3)/Q3*100</f>
-        <v>22.402029167014366</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+        <v>7.0287048816680908E-2</v>
+      </c>
+      <c r="Z3">
+        <f>6780000*2*3.1415926*X3*0.000001/Y3</f>
+        <v>62.541474481504522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -721,34 +692,28 @@
         <f t="shared" si="4"/>
         <v>67.919679029324811</v>
       </c>
-      <c r="T4" s="2">
-        <f t="shared" si="5"/>
-        <v>91.588842330840777</v>
-      </c>
-      <c r="U4" s="2">
-        <f t="shared" si="6"/>
-        <v>3.5425341669089958</v>
-      </c>
-      <c r="W4">
-        <v>0.24802376329898829</v>
+      <c r="T4">
+        <v>0.16146913170814511</v>
+      </c>
+      <c r="U4">
+        <v>8.6934715509414673E-2</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V3:V49" si="5">6780000*2*3.1415926*T4*0.000001/U4</f>
+        <v>79.123561502886048</v>
       </c>
       <c r="X4">
-        <v>0.1059732288122177</v>
+        <v>0.17454767227172849</v>
       </c>
       <c r="Y4">
-        <f t="shared" si="7"/>
-        <v>99.702645258115766</v>
-      </c>
-      <c r="AA4" s="2">
-        <f t="shared" si="8"/>
-        <v>13.087617772655619</v>
-      </c>
-      <c r="AB4" s="2">
-        <f t="shared" si="9"/>
-        <v>22.96217736826279</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.12292706966400151</v>
+      </c>
+      <c r="Z4">
+        <f t="shared" ref="Z4:Z49" si="6">6780000*2*3.1415926*X4*0.000001/Y4</f>
+        <v>60.488955775686705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -802,34 +767,28 @@
         <f t="shared" si="4"/>
         <v>81.995395457907264</v>
       </c>
-      <c r="T5" s="2">
-        <f t="shared" si="5"/>
-        <v>12.55538395464696</v>
-      </c>
-      <c r="U5" s="2">
-        <f t="shared" si="6"/>
-        <v>15.898569066710754</v>
-      </c>
-      <c r="W5">
-        <v>0.24802376329898829</v>
+      <c r="T5">
+        <v>0.1689397990703583</v>
+      </c>
+      <c r="U5">
+        <v>8.8925570249557495E-2</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>80.9309930352523</v>
       </c>
       <c r="X5">
-        <v>0.1059732288122177</v>
+        <v>0.1994786262512207</v>
       </c>
       <c r="Y5">
-        <f t="shared" si="7"/>
-        <v>99.702645258115766</v>
-      </c>
-      <c r="AA5" s="2">
-        <f t="shared" si="8"/>
-        <v>6.5211146276362726</v>
-      </c>
-      <c r="AB5" s="2">
-        <f t="shared" si="9"/>
-        <v>12.397099436043892</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.1150748729705811</v>
+      </c>
+      <c r="Z5">
+        <f t="shared" si="6"/>
+        <v>73.845735323464666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -883,34 +842,28 @@
         <f t="shared" si="4"/>
         <v>106.26082868762136</v>
       </c>
-      <c r="T6" s="2">
-        <f t="shared" si="5"/>
-        <v>10.34079191787518</v>
-      </c>
-      <c r="U6" s="2">
-        <f t="shared" si="6"/>
-        <v>16.74820196518753</v>
-      </c>
-      <c r="W6">
-        <v>0.24802376329898829</v>
+      <c r="T6">
+        <v>0.19643175601959231</v>
+      </c>
+      <c r="U6">
+        <v>9.6252202987670898E-2</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>86.938186279299558</v>
       </c>
       <c r="X6">
-        <v>0.1059732288122177</v>
+        <v>0.21352458000183111</v>
       </c>
       <c r="Y6">
-        <f t="shared" si="7"/>
-        <v>99.702645258115766</v>
-      </c>
-      <c r="AA6" s="2">
-        <f t="shared" si="8"/>
-        <v>1.0362405487161002</v>
-      </c>
-      <c r="AB6" s="2">
-        <f t="shared" si="9"/>
-        <v>7.6821444445527503</v>
-      </c>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+        <v>7.3583334684371948E-2</v>
+      </c>
+      <c r="Z6">
+        <f t="shared" si="6"/>
+        <v>123.61693336601557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -964,34 +917,28 @@
         <f t="shared" si="4"/>
         <v>82.09108586752015</v>
       </c>
-      <c r="T7" s="2">
-        <f t="shared" si="5"/>
-        <v>7.4506165113799661</v>
-      </c>
-      <c r="U7" s="2">
-        <f t="shared" si="6"/>
-        <v>15.196523447967838</v>
-      </c>
-      <c r="W7">
-        <v>0.41671633720397949</v>
+      <c r="T7">
+        <v>0.38469091057777399</v>
+      </c>
+      <c r="U7">
+        <v>0.18547867238521579</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>88.354261483392563</v>
       </c>
       <c r="X7">
-        <v>0.19645699858665469</v>
+        <v>0.40105938911437988</v>
       </c>
       <c r="Y7">
-        <f t="shared" si="7"/>
-        <v>90.361322235326355</v>
-      </c>
-      <c r="AA7" s="2">
-        <f t="shared" si="8"/>
-        <v>3.4171563519261388</v>
-      </c>
-      <c r="AB7" s="2">
-        <f t="shared" si="9"/>
-        <v>12.256811707612906</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.17784106731414789</v>
+      </c>
+      <c r="Z7">
+        <f t="shared" si="6"/>
+        <v>96.06964517307199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1045,34 +992,28 @@
         <f t="shared" si="4"/>
         <v>126.57336980166569</v>
       </c>
-      <c r="T8" s="2">
-        <f t="shared" si="5"/>
-        <v>6.6397479333587723</v>
-      </c>
-      <c r="U8" s="2">
-        <f t="shared" si="6"/>
-        <v>9.246349758162026</v>
-      </c>
-      <c r="W8">
-        <v>0.362203449010849</v>
+      <c r="T8">
+        <v>0.35672712326049799</v>
+      </c>
+      <c r="U8">
+        <v>0.14150333404541021</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>107.39375155922346</v>
       </c>
       <c r="X8">
-        <v>0.14358808100223541</v>
+        <v>0.36836838722228998</v>
       </c>
       <c r="Y8">
-        <f t="shared" si="7"/>
-        <v>107.45923510329642</v>
-      </c>
-      <c r="AA8" s="2">
-        <f t="shared" si="8"/>
-        <v>7.8714360903347327</v>
-      </c>
-      <c r="AB8" s="2">
-        <f t="shared" si="9"/>
-        <v>8.5157806848816655</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.12534976005554199</v>
+      </c>
+      <c r="Z8">
+        <f t="shared" si="6"/>
+        <v>125.18964287226396</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1126,34 +1067,28 @@
         <f t="shared" si="4"/>
         <v>136.99878560125703</v>
       </c>
-      <c r="T9" s="2">
-        <f t="shared" si="5"/>
-        <v>6.3261210478370122</v>
-      </c>
-      <c r="U9" s="2">
-        <f t="shared" si="6"/>
-        <v>9.6468174347981375</v>
-      </c>
-      <c r="W9">
-        <v>0.41758072376251221</v>
+      <c r="T9">
+        <v>0.40904849767684942</v>
+      </c>
+      <c r="U9">
+        <v>0.15694709122180939</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>111.02763414391758</v>
       </c>
       <c r="X9">
-        <v>0.161831334233284</v>
+        <v>0.43056869506835938</v>
       </c>
       <c r="Y9">
-        <f t="shared" si="7"/>
-        <v>109.92269885552047</v>
-      </c>
-      <c r="AA9" s="2">
-        <f t="shared" si="8"/>
-        <v>7.2187162524691306</v>
-      </c>
-      <c r="AB9" s="2">
-        <f t="shared" si="9"/>
-        <v>15.635108419638447</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.14516684412956241</v>
+      </c>
+      <c r="Z9">
+        <f t="shared" si="6"/>
+        <v>126.35271262872628</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1207,34 +1142,28 @@
         <f t="shared" si="4"/>
         <v>106.23927183097523</v>
       </c>
-      <c r="T10" s="2">
-        <f t="shared" si="5"/>
-        <v>6.5910470646425496</v>
-      </c>
-      <c r="U10" s="2">
-        <f t="shared" si="6"/>
-        <v>3.208589999051136</v>
-      </c>
-      <c r="W10">
-        <v>0.50073379278182983</v>
+      <c r="T10">
+        <v>0.46865791082382202</v>
+      </c>
+      <c r="U10">
+        <v>0.213797852396965</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>93.381784435212921</v>
       </c>
       <c r="X10">
-        <v>0.22311745584011081</v>
+        <v>0.48204529285430908</v>
       </c>
       <c r="Y10">
-        <f t="shared" si="7"/>
-        <v>95.605506601888834</v>
-      </c>
-      <c r="AA10" s="2">
-        <f t="shared" si="8"/>
-        <v>4.7418877636057868</v>
-      </c>
-      <c r="AB10" s="2">
-        <f t="shared" si="9"/>
-        <v>5.8532383718145988</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.19915902614593509</v>
+      </c>
+      <c r="Z10">
+        <f t="shared" si="6"/>
+        <v>103.1091976044388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1288,34 +1217,28 @@
         <f t="shared" si="4"/>
         <v>87.101060954697189</v>
       </c>
-      <c r="T11" s="2">
-        <f t="shared" si="5"/>
-        <v>27.101478404108427</v>
-      </c>
-      <c r="U11" s="2">
-        <f t="shared" si="6"/>
-        <v>78.44825359088658</v>
-      </c>
-      <c r="W11">
-        <v>0.37718492746353149</v>
+      <c r="T11">
+        <v>0.36116534471511841</v>
+      </c>
+      <c r="U11">
+        <v>0.2251284122467041</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="5"/>
+        <v>68.341627617848729</v>
       </c>
       <c r="X11">
-        <v>0.1903194934129715</v>
+        <v>0.38369858264923101</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="7"/>
-        <v>84.426854986363566</v>
-      </c>
-      <c r="AA11" s="2">
-        <f t="shared" si="8"/>
-        <v>8.6298957235698062</v>
-      </c>
-      <c r="AB11" s="2">
-        <f t="shared" si="9"/>
-        <v>5.7357635398853395</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.19164204597473139</v>
+      </c>
+      <c r="Z11">
+        <f t="shared" si="6"/>
+        <v>85.2921282014794</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1369,34 +1292,28 @@
         <f t="shared" si="4"/>
         <v>106.34825883698332</v>
       </c>
-      <c r="T12" s="2">
-        <f t="shared" si="5"/>
-        <v>8.2197520250368168</v>
-      </c>
-      <c r="U12" s="2">
-        <f t="shared" si="6"/>
-        <v>4.0801746403786927</v>
-      </c>
-      <c r="W12">
-        <v>0.49952501058578491</v>
+      <c r="T12">
+        <v>0.50276118516921997</v>
+      </c>
+      <c r="U12">
+        <v>0.22522106766700739</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="5"/>
+        <v>95.096007341020382</v>
       </c>
       <c r="X12">
-        <v>0.19827504456043241</v>
+        <v>0.48176538944244379</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="7"/>
-        <v>107.32446601232216</v>
-      </c>
-      <c r="AA12" s="2">
-        <f t="shared" si="8"/>
-        <v>8.0403146933385692</v>
-      </c>
-      <c r="AB12" s="2">
-        <f t="shared" si="9"/>
-        <v>8.8767661379510088</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.1967687010765076</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="6"/>
+        <v>104.30115859472703</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1450,34 +1367,28 @@
         <f t="shared" si="4"/>
         <v>111.11416589715785</v>
       </c>
-      <c r="T13" s="2">
-        <f t="shared" si="5"/>
-        <v>24.696333988732178</v>
-      </c>
-      <c r="U13" s="2">
-        <f t="shared" si="6"/>
-        <v>84.008394398145867</v>
-      </c>
-      <c r="W13">
-        <v>0.48427659273147577</v>
+      <c r="T13">
+        <v>0.4650338888168335</v>
+      </c>
+      <c r="U13">
+        <v>0.17284254729747769</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="5"/>
+        <v>114.61553855367758</v>
       </c>
       <c r="X13">
-        <v>0.18546582758426669</v>
+        <v>0.49842798709869379</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="7"/>
-        <v>111.23440374637205</v>
-      </c>
-      <c r="AA13" s="2">
-        <f t="shared" si="8"/>
-        <v>8.4439458669270984</v>
-      </c>
-      <c r="AB13" s="2">
-        <f t="shared" si="9"/>
-        <v>8.5429125774117605</v>
-      </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.19587200880050659</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="6"/>
+        <v>108.4025748000511</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1531,34 +1442,28 @@
         <f t="shared" si="4"/>
         <v>124.72617713017445</v>
       </c>
-      <c r="T14" s="2">
-        <f t="shared" si="5"/>
-        <v>6.0041675967596806</v>
-      </c>
-      <c r="U14" s="2">
-        <f t="shared" si="6"/>
-        <v>11.413465450903926</v>
-      </c>
-      <c r="W14">
-        <v>0.52081942558288574</v>
+      <c r="T14">
+        <v>0.49436432123184199</v>
+      </c>
+      <c r="U14">
+        <v>0.18015462160110471</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="5"/>
+        <v>116.89912670455033</v>
       </c>
       <c r="X14">
-        <v>0.17022643983364111</v>
+        <v>0.51373791694641113</v>
       </c>
       <c r="Y14">
-        <f t="shared" si="7"/>
-        <v>130.33759790238324</v>
-      </c>
-      <c r="AA14" s="2">
-        <f t="shared" si="8"/>
-        <v>6.2431277078513503</v>
-      </c>
-      <c r="AB14" s="2">
-        <f t="shared" si="9"/>
-        <v>10.279639575374954</v>
-      </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.18338131904602051</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="6"/>
+        <v>119.34276154239784</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1612,34 +1517,28 @@
         <f t="shared" si="4"/>
         <v>134.00409276942264</v>
       </c>
-      <c r="T15" s="2">
-        <f t="shared" si="5"/>
-        <v>5.9301236894988509</v>
-      </c>
-      <c r="U15" s="2">
-        <f t="shared" si="6"/>
-        <v>11.259286029303674</v>
-      </c>
-      <c r="W15">
-        <v>0.59926110506057739</v>
+      <c r="T15">
+        <v>0.58772408962249756</v>
+      </c>
+      <c r="U15">
+        <v>0.20158037543296811</v>
+      </c>
+      <c r="V15">
+        <f t="shared" si="5"/>
+        <v>124.20377534801528</v>
       </c>
       <c r="X15">
-        <v>0.1831464767456055</v>
+        <v>0.59992742538452148</v>
       </c>
       <c r="Y15">
-        <f t="shared" si="7"/>
-        <v>139.38854258086567</v>
-      </c>
-      <c r="AA15" s="2">
-        <f t="shared" si="8"/>
-        <v>6.6469700651819688</v>
-      </c>
-      <c r="AB15" s="2">
-        <f t="shared" si="9"/>
-        <v>10.253110821970161</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.1948093771934509</v>
+      </c>
+      <c r="Z15">
+        <f t="shared" si="6"/>
+        <v>131.18929942431464</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -1693,34 +1592,28 @@
         <f t="shared" si="4"/>
         <v>145.98553133207395</v>
       </c>
-      <c r="T16" s="2">
-        <f t="shared" si="5"/>
-        <v>5.0966208925944017</v>
-      </c>
-      <c r="U16" s="2">
-        <f t="shared" si="6"/>
-        <v>7.6703476337903513</v>
-      </c>
-      <c r="W16">
-        <v>0.74201822280883789</v>
+      <c r="T16">
+        <v>0.70015197992324829</v>
+      </c>
+      <c r="U16">
+        <v>0.2239689230918884</v>
+      </c>
+      <c r="V16">
+        <f t="shared" si="5"/>
+        <v>133.17236557427739</v>
       </c>
       <c r="X16">
-        <v>0.22569674253463751</v>
+        <v>0.76006722450256348</v>
       </c>
       <c r="Y16">
-        <f t="shared" si="7"/>
-        <v>140.05506997283391</v>
-      </c>
-      <c r="AA16" s="2">
-        <f t="shared" si="8"/>
-        <v>4.2334706372011652</v>
-      </c>
-      <c r="AB16" s="2">
-        <f t="shared" si="9"/>
-        <v>0.1783535892801808</v>
-      </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.23711210489273071</v>
+      </c>
+      <c r="Z16">
+        <f t="shared" si="6"/>
+        <v>136.55507160516052</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -1774,34 +1667,28 @@
         <f t="shared" si="4"/>
         <v>150.44431949239907</v>
       </c>
-      <c r="T17" s="2">
-        <f t="shared" si="5"/>
-        <v>4.9989251598038535</v>
-      </c>
-      <c r="U17" s="2">
-        <f t="shared" si="6"/>
-        <v>5.7436367236723651</v>
-      </c>
-      <c r="W17">
-        <v>0.92956411838531494</v>
+      <c r="T17">
+        <v>1.0431568622589109</v>
+      </c>
+      <c r="U17">
+        <v>0.30557018518447882</v>
+      </c>
+      <c r="V17">
+        <f t="shared" si="5"/>
+        <v>145.42805533834331</v>
       </c>
       <c r="X17">
-        <v>0.27559497952461243</v>
+        <v>0.92759287357330322</v>
       </c>
       <c r="Y17">
-        <f t="shared" si="7"/>
-        <v>143.68704202629135</v>
-      </c>
-      <c r="AA17" s="2">
-        <f t="shared" si="8"/>
-        <v>5.2325828191423192</v>
-      </c>
-      <c r="AB17" s="2">
-        <f t="shared" si="9"/>
-        <v>0.77588495963548887</v>
-      </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.29882404208183289</v>
+      </c>
+      <c r="Z17">
+        <f t="shared" si="6"/>
+        <v>132.23652323777208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1855,34 +1742,28 @@
         <f t="shared" si="4"/>
         <v>194.56703501335093</v>
       </c>
-      <c r="T18" s="2">
-        <f t="shared" si="5"/>
-        <v>4.2099149472925648</v>
-      </c>
-      <c r="U18" s="2">
-        <f t="shared" si="6"/>
-        <v>8.0360302045183314</v>
-      </c>
-      <c r="W18">
-        <v>1.06830894947052</v>
+      <c r="T18">
+        <v>1.1460273265838621</v>
+      </c>
+      <c r="U18">
+        <v>0.31722116470336909</v>
+      </c>
+      <c r="V18">
+        <f t="shared" si="5"/>
+        <v>153.9013299436742</v>
       </c>
       <c r="X18">
-        <v>0.27330285310745239</v>
+        <v>1.05478823184967</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="7"/>
-        <v>166.51841021512232</v>
-      </c>
-      <c r="AA18" s="2">
-        <f t="shared" si="8"/>
-        <v>3.7472790818524269</v>
-      </c>
-      <c r="AB18" s="2">
-        <f t="shared" si="9"/>
-        <v>12.465681703408251</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.28100436925888062</v>
+      </c>
+      <c r="Z18">
+        <f t="shared" si="6"/>
+        <v>159.90489476481977</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4</v>
       </c>
@@ -1936,34 +1817,28 @@
         <f t="shared" si="4"/>
         <v>104.00971088235249</v>
       </c>
-      <c r="T19" s="2">
-        <f t="shared" si="5"/>
-        <v>4.7647188388772062</v>
-      </c>
-      <c r="U19" s="2">
-        <f t="shared" si="6"/>
-        <v>15.066874103705938</v>
-      </c>
-      <c r="W19">
-        <v>0.82163166999816895</v>
+      <c r="T19">
+        <v>0.63737165927886963</v>
+      </c>
+      <c r="U19">
+        <v>0.42281004786491388</v>
+      </c>
+      <c r="V19">
+        <f t="shared" si="5"/>
+        <v>64.218033733229362</v>
       </c>
       <c r="X19">
-        <v>0.534984290599823</v>
+        <v>0.62943422794342041</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="7"/>
-        <v>65.425296009178936</v>
-      </c>
-      <c r="AA19" s="2">
-        <f t="shared" si="8"/>
-        <v>26.998836094684208</v>
-      </c>
-      <c r="AB19" s="2">
-        <f t="shared" si="9"/>
-        <v>101.89610181893842</v>
-      </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.47128748893737787</v>
+      </c>
+      <c r="Z19">
+        <f t="shared" si="6"/>
+        <v>56.894986617585147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -2017,34 +1892,28 @@
         <f t="shared" si="4"/>
         <v>109.36374157525063</v>
       </c>
-      <c r="T20" s="2">
-        <f t="shared" si="5"/>
-        <v>5.1597752554344796</v>
-      </c>
-      <c r="U20" s="2">
-        <f t="shared" si="6"/>
-        <v>17.883843878787879</v>
-      </c>
-      <c r="W20">
-        <v>0.65782558917999268</v>
+      <c r="T20">
+        <v>0.47585126757621771</v>
+      </c>
+      <c r="U20">
+        <v>0.32726007699966431</v>
+      </c>
+      <c r="V20">
+        <f t="shared" si="5"/>
+        <v>61.942361309380743</v>
       </c>
       <c r="X20">
-        <v>0.45139503479003912</v>
+        <v>0.51356363296508789</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="7"/>
-        <v>62.08169138260029</v>
-      </c>
-      <c r="AA20" s="2">
-        <f t="shared" si="8"/>
-        <v>24.23758506864958</v>
-      </c>
-      <c r="AB20" s="2">
-        <f t="shared" si="9"/>
-        <v>118.85819868607959</v>
-      </c>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.40556862950325012</v>
+      </c>
+      <c r="Z20">
+        <f t="shared" si="6"/>
+        <v>53.94354233015698</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4</v>
       </c>
@@ -2098,34 +1967,28 @@
         <f t="shared" si="4"/>
         <v>104.2199582569137</v>
       </c>
-      <c r="T21" s="2">
-        <f t="shared" si="5"/>
-        <v>4.24115539040874</v>
-      </c>
-      <c r="U21" s="2">
-        <f t="shared" si="6"/>
-        <v>5.9708498825539227</v>
-      </c>
-      <c r="W21">
-        <v>0.86089038848876953</v>
+      <c r="T21">
+        <v>0.79386031627655029</v>
+      </c>
+      <c r="U21">
+        <v>0.42268052697181702</v>
+      </c>
+      <c r="V21">
+        <f t="shared" si="5"/>
+        <v>80.009472561073849</v>
       </c>
       <c r="X21">
-        <v>0.47330862283706671</v>
+        <v>0.77157771587371826</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="7"/>
-        <v>77.484172145620278</v>
-      </c>
-      <c r="AA21" s="2">
-        <f t="shared" si="8"/>
-        <v>7.3456181561596932</v>
-      </c>
-      <c r="AB21" s="2">
-        <f t="shared" si="9"/>
-        <v>44.385047081256431</v>
-      </c>
-    </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.42089086771011353</v>
+      </c>
+      <c r="Z21">
+        <f t="shared" si="6"/>
+        <v>78.094370455966526</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4</v>
       </c>
@@ -2179,34 +2042,28 @@
         <f t="shared" si="4"/>
         <v>130.96725692891812</v>
       </c>
-      <c r="T22" s="2">
-        <f t="shared" si="5"/>
-        <v>3.6510369585172833</v>
-      </c>
-      <c r="U22" s="2">
-        <f t="shared" si="6"/>
-        <v>27.738585587098928</v>
-      </c>
-      <c r="W22">
-        <v>0.8703080415725708</v>
+      <c r="T22">
+        <v>0.97864878177642822</v>
+      </c>
+      <c r="U22">
+        <v>0.46412968635559082</v>
+      </c>
+      <c r="V22">
+        <f t="shared" si="5"/>
+        <v>89.824967197820229</v>
       </c>
       <c r="X22">
-        <v>0.39379972219467158</v>
+        <v>0.89939093589782715</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="7"/>
-        <v>94.14714308012033</v>
-      </c>
-      <c r="AA22" s="2">
-        <f t="shared" si="8"/>
-        <v>4.8926824351345459</v>
-      </c>
-      <c r="AB22" s="2">
-        <f t="shared" si="9"/>
-        <v>32.302947150905943</v>
-      </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.3657647967338562</v>
+      </c>
+      <c r="Z22">
+        <f t="shared" si="6"/>
+        <v>104.75051263659994</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
@@ -2260,34 +2117,28 @@
         <f t="shared" si="4"/>
         <v>126.30219274150836</v>
       </c>
-      <c r="T23" s="2">
-        <f t="shared" si="5"/>
-        <v>3.7662477752224741</v>
-      </c>
-      <c r="U23" s="2">
-        <f t="shared" si="6"/>
-        <v>18.874153622672829</v>
-      </c>
-      <c r="W23">
-        <v>0.93598878383636475</v>
+      <c r="T23">
+        <v>1.1072015762329099</v>
+      </c>
+      <c r="U23">
+        <v>0.46378690004348749</v>
+      </c>
+      <c r="V23">
+        <f t="shared" si="5"/>
+        <v>101.69925526877898</v>
       </c>
       <c r="X23">
-        <v>0.42837667465209961</v>
+        <v>0.97504770755767822</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="7"/>
-        <v>93.079573386847642</v>
-      </c>
-      <c r="AA23" s="2">
-        <f t="shared" si="8"/>
-        <v>6.4104805683066939</v>
-      </c>
-      <c r="AB23" s="2">
-        <f t="shared" si="9"/>
-        <v>26.994152333718606</v>
-      </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.45917254686355591</v>
+      </c>
+      <c r="Z23">
+        <f t="shared" si="6"/>
+        <v>90.460608740819751</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4</v>
       </c>
@@ -2341,34 +2192,28 @@
         <f t="shared" si="4"/>
         <v>117.97405195907693</v>
       </c>
-      <c r="T24" s="2">
-        <f t="shared" si="5"/>
-        <v>3.8700182309803726</v>
-      </c>
-      <c r="U24" s="2">
-        <f t="shared" si="6"/>
-        <v>18.622274506466983</v>
-      </c>
-      <c r="W24">
-        <v>0.93247711658477783</v>
+      <c r="T24">
+        <v>1.042928218841553</v>
+      </c>
+      <c r="U24">
+        <v>0.4536978006362915</v>
+      </c>
+      <c r="V24">
+        <f t="shared" si="5"/>
+        <v>97.925838586523</v>
       </c>
       <c r="X24">
-        <v>0.434345543384552</v>
+        <v>0.94797658920288086</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="7"/>
-        <v>91.456034765070314</v>
-      </c>
-      <c r="AA24" s="2">
-        <f t="shared" si="8"/>
-        <v>4.4945392493775014</v>
-      </c>
-      <c r="AB24" s="2">
-        <f t="shared" si="9"/>
-        <v>23.197624059607449</v>
-      </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.43526840209960938</v>
+      </c>
+      <c r="Z24">
+        <f t="shared" si="6"/>
+        <v>92.779072377486202</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4</v>
       </c>
@@ -2422,34 +2267,28 @@
         <f t="shared" si="4"/>
         <v>130.83566673849759</v>
       </c>
-      <c r="T25" s="2">
-        <f t="shared" si="5"/>
-        <v>3.333571561554558</v>
-      </c>
-      <c r="U25" s="2">
-        <f t="shared" si="6"/>
-        <v>3.8276534915302731</v>
-      </c>
-      <c r="W25">
-        <v>1.2330232858657839</v>
+      <c r="T25">
+        <v>1.428875327110291</v>
+      </c>
+      <c r="U25">
+        <v>0.52277225255966187</v>
+      </c>
+      <c r="V25">
+        <f t="shared" si="5"/>
+        <v>116.43709556087644</v>
       </c>
       <c r="X25">
-        <v>0.42327266931533808</v>
+        <v>1.2423417568206789</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="7"/>
-        <v>124.09680669104765</v>
-      </c>
-      <c r="AA25" s="2">
-        <f t="shared" si="8"/>
-        <v>4.3500670339163756</v>
-      </c>
-      <c r="AB25" s="2">
-        <f t="shared" si="9"/>
-        <v>0.84403528824198593</v>
-      </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.42533254623413091</v>
+      </c>
+      <c r="Z25">
+        <f t="shared" si="6"/>
+        <v>124.42911766901474</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -2503,34 +2342,28 @@
         <f t="shared" si="4"/>
         <v>107.35538368975843</v>
       </c>
-      <c r="T26" s="2">
-        <f t="shared" si="5"/>
-        <v>5.5670046427003035</v>
-      </c>
-      <c r="U26" s="2">
-        <f t="shared" si="6"/>
-        <v>51.846682582848466</v>
-      </c>
-      <c r="W26">
-        <v>1.503465414047241</v>
+      <c r="T26">
+        <v>1.999053478240967</v>
+      </c>
+      <c r="U26">
+        <v>0.89127510786056519</v>
+      </c>
+      <c r="V26">
+        <f t="shared" si="5"/>
+        <v>95.548129570897459</v>
       </c>
       <c r="X26">
-        <v>0.89343369007110596</v>
+        <v>1.546310186386108</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="7"/>
-        <v>71.687043838990817</v>
-      </c>
-      <c r="AA26" s="2">
-        <f t="shared" si="8"/>
-        <v>5.6737929576986703</v>
-      </c>
-      <c r="AB26" s="2">
-        <f t="shared" si="9"/>
-        <v>41.258805032745052</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.83409583568572998</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" si="6"/>
+        <v>78.975106222321756</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -2584,34 +2417,28 @@
         <f t="shared" si="4"/>
         <v>97.429935119835179</v>
       </c>
-      <c r="T27" s="2">
-        <f t="shared" si="5"/>
-        <v>4.7754027436527533</v>
-      </c>
-      <c r="U27" s="2">
-        <f t="shared" si="6"/>
-        <v>10.576503028221776</v>
-      </c>
-      <c r="W27">
-        <v>1.3647022247314451</v>
+      <c r="T27">
+        <v>1.828563451766968</v>
+      </c>
+      <c r="U27">
+        <v>0.78356689214706421</v>
+      </c>
+      <c r="V27">
+        <f t="shared" si="5"/>
+        <v>99.413076130037794</v>
       </c>
       <c r="X27">
-        <v>0.72680854797363281</v>
+        <v>1.3802802562713621</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="7"/>
-        <v>79.988477030683157</v>
-      </c>
-      <c r="AA27" s="2">
-        <f t="shared" si="8"/>
-        <v>6.8589800210588967</v>
-      </c>
-      <c r="AB27" s="2">
-        <f t="shared" si="9"/>
-        <v>13.450385235644486</v>
-      </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.68571579456329346</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="6"/>
+        <v>85.749713492701531</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -2665,34 +2492,28 @@
         <f t="shared" si="4"/>
         <v>124.57159008466202</v>
       </c>
-      <c r="T28" s="2">
-        <f t="shared" si="5"/>
-        <v>4.1292825652155356</v>
-      </c>
-      <c r="U28" s="2">
-        <f t="shared" si="6"/>
-        <v>9.3694273270283777</v>
-      </c>
-      <c r="W28">
-        <v>2.2716133594512939</v>
+      <c r="T28">
+        <v>2.899238109588623</v>
+      </c>
+      <c r="U28">
+        <v>1.037422895431519</v>
+      </c>
+      <c r="V28">
+        <f t="shared" si="5"/>
+        <v>119.05225093650134</v>
       </c>
       <c r="X28">
-        <v>0.85571670532226563</v>
+        <v>2.234885692596436</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="7"/>
-        <v>113.08733210752563</v>
-      </c>
-      <c r="AA28" s="2">
-        <f t="shared" si="8"/>
-        <v>3.3314881717820306</v>
-      </c>
-      <c r="AB28" s="2">
-        <f t="shared" si="9"/>
-        <v>6.485403847967353</v>
-      </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.82216966152191162</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="6"/>
+        <v>115.79863044329494</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -2746,34 +2567,28 @@
         <f t="shared" si="4"/>
         <v>161.12589949719245</v>
       </c>
-      <c r="T29" s="2">
-        <f t="shared" si="5"/>
-        <v>4.1711175630894726</v>
-      </c>
-      <c r="U29" s="2">
-        <f t="shared" si="6"/>
-        <v>11.894673351330512</v>
-      </c>
-      <c r="W29">
-        <v>1.9059193134307859</v>
+      <c r="T29">
+        <v>2.488350629806519</v>
+      </c>
+      <c r="U29">
+        <v>0.75081330537796021</v>
+      </c>
+      <c r="V29">
+        <f t="shared" si="5"/>
+        <v>141.18519911817518</v>
       </c>
       <c r="X29">
-        <v>0.58219581842422485</v>
+        <v>1.856438040733337</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="7"/>
-        <v>139.4584981606244</v>
-      </c>
-      <c r="AA29" s="2">
-        <f t="shared" si="8"/>
-        <v>2.83358075805323</v>
-      </c>
-      <c r="AB29" s="2">
-        <f t="shared" si="9"/>
-        <v>12.2629807991178</v>
-      </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.5606423020362854</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="6"/>
+        <v>141.06008801625333</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -2827,34 +2642,28 @@
         <f t="shared" si="4"/>
         <v>141.60345063636763</v>
       </c>
-      <c r="T30" s="2">
-        <f t="shared" si="5"/>
-        <v>4.108458406320378</v>
-      </c>
-      <c r="U30" s="2">
-        <f t="shared" si="6"/>
-        <v>9.4979361646505289</v>
-      </c>
-      <c r="W30">
-        <v>2.7258999347686772</v>
+      <c r="T30">
+        <v>3.400421142578125</v>
+      </c>
+      <c r="U30">
+        <v>1.117282390594482</v>
+      </c>
+      <c r="V30">
+        <f t="shared" si="5"/>
+        <v>129.65202631120223</v>
       </c>
       <c r="X30">
-        <v>0.93374359607696533</v>
+        <v>2.7297852039337158</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="7"/>
-        <v>124.36318264212724</v>
-      </c>
-      <c r="AA30" s="2">
-        <f t="shared" si="8"/>
-        <v>2.5524636339085083</v>
-      </c>
-      <c r="AB30" s="2">
-        <f t="shared" si="9"/>
-        <v>10.956531605980153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.89298427104949951</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="6"/>
+        <v>130.22495647400189</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -2908,34 +2717,28 @@
         <f t="shared" si="4"/>
         <v>84.076232483520172</v>
       </c>
-      <c r="T31" s="2">
-        <f t="shared" si="5"/>
-        <v>4.1427571444456763</v>
-      </c>
-      <c r="U31" s="2">
-        <f t="shared" si="6"/>
-        <v>1.0708962384233855</v>
-      </c>
-      <c r="W31">
-        <v>4.4331645965576172</v>
+      <c r="T31">
+        <v>4.8900747299194336</v>
+      </c>
+      <c r="U31">
+        <v>1.8915525674819951</v>
+      </c>
+      <c r="V31">
+        <f t="shared" si="5"/>
+        <v>110.13025269997745</v>
       </c>
       <c r="X31">
-        <v>2.3870658874511719</v>
+        <v>4.2812275886535636</v>
       </c>
       <c r="Y31">
-        <f t="shared" si="7"/>
-        <v>79.115031364860272</v>
-      </c>
-      <c r="AA31" s="2">
-        <f t="shared" si="8"/>
-        <v>1.4085489479013227</v>
-      </c>
-      <c r="AB31" s="2">
-        <f t="shared" si="9"/>
-        <v>4.7739932164847323</v>
-      </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.2">
+        <v>2.2499954700469971</v>
+      </c>
+      <c r="Z31">
+        <f t="shared" si="6"/>
+        <v>81.058063941426369</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2989,34 +2792,28 @@
         <f t="shared" si="4"/>
         <v>148.38157874051376</v>
       </c>
-      <c r="T32" s="2">
-        <f t="shared" si="5"/>
-        <v>4.0636118141049433</v>
-      </c>
-      <c r="U32" s="2">
-        <f t="shared" si="6"/>
-        <v>12.452502537060967</v>
-      </c>
-      <c r="W32">
-        <v>3.420789480209351</v>
+      <c r="T32">
+        <v>4.3625879287719727</v>
+      </c>
+      <c r="U32">
+        <v>1.395170927047729</v>
+      </c>
+      <c r="V32">
+        <f t="shared" si="5"/>
+        <v>133.2067800522955</v>
       </c>
       <c r="X32">
-        <v>1.1621384620666499</v>
+        <v>3.3504526615142818</v>
       </c>
       <c r="Y32">
-        <f t="shared" si="7"/>
-        <v>125.39436715472146</v>
-      </c>
-      <c r="AA32" s="2">
-        <f t="shared" si="8"/>
-        <v>2.2882835782412831</v>
-      </c>
-      <c r="AB32" s="2">
-        <f t="shared" si="9"/>
-        <v>15.624162975489982</v>
-      </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.1225990056991579</v>
+      </c>
+      <c r="Z32">
+        <f t="shared" si="6"/>
+        <v>127.14180940971868</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>5</v>
       </c>
@@ -3070,34 +2867,28 @@
         <f t="shared" si="4"/>
         <v>135.64147033128543</v>
       </c>
-      <c r="T33" s="2">
-        <f t="shared" si="5"/>
-        <v>64.403865791268757</v>
-      </c>
-      <c r="U33" s="2">
-        <f t="shared" si="6"/>
-        <v>61.302675656108597</v>
-      </c>
-      <c r="W33">
-        <v>2.9876964092254639</v>
+      <c r="T33">
+        <v>4.344942569732666</v>
+      </c>
+      <c r="U33">
+        <v>1.4827631711959841</v>
+      </c>
+      <c r="V33">
+        <f t="shared" si="5"/>
+        <v>124.83081465186743</v>
       </c>
       <c r="X33">
-        <v>1.2134144306182859</v>
+        <v>3.031828880310059</v>
       </c>
       <c r="Y33">
-        <f t="shared" si="7"/>
-        <v>104.89067118610016</v>
-      </c>
-      <c r="AA33" s="2">
-        <f t="shared" si="8"/>
-        <v>15.083662766443165</v>
-      </c>
-      <c r="AB33" s="2">
-        <f t="shared" si="9"/>
-        <v>9.811260689437642</v>
-      </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.185233354568481</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="6"/>
+        <v>108.97085931062652</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -3151,34 +2942,28 @@
         <f t="shared" si="4"/>
         <v>91.084828507187908</v>
       </c>
-      <c r="T34" s="2">
-        <f t="shared" si="5"/>
-        <v>4.6146258694841285</v>
-      </c>
-      <c r="U34" s="2">
-        <f t="shared" si="6"/>
-        <v>5.8941098486752752</v>
-      </c>
-      <c r="W34">
-        <v>3.2423274517059331</v>
+      <c r="T34">
+        <v>4.2311654090881348</v>
+      </c>
+      <c r="U34">
+        <v>1.8176496028900151</v>
+      </c>
+      <c r="V34">
+        <f t="shared" si="5"/>
+        <v>99.165222912261541</v>
       </c>
       <c r="X34">
-        <v>1.5256941318511961</v>
+        <v>3.2388663291931148</v>
       </c>
       <c r="Y34">
-        <f t="shared" si="7"/>
-        <v>90.531340767766494</v>
-      </c>
-      <c r="AA34" s="2">
-        <f t="shared" si="8"/>
-        <v>4.477286871934326</v>
-      </c>
-      <c r="AB34" s="2">
-        <f t="shared" si="9"/>
-        <v>3.8932830329955181</v>
-      </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.499395608901978</v>
+      </c>
+      <c r="Z34">
+        <f t="shared" si="6"/>
+        <v>92.020872099947198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -3232,34 +3017,28 @@
         <f t="shared" si="4"/>
         <v>94.4561902306083</v>
       </c>
-      <c r="T35" s="2">
-        <f t="shared" si="5"/>
-        <v>4.1841537820301911</v>
-      </c>
-      <c r="U35" s="2">
-        <f t="shared" si="6"/>
-        <v>12.540884875474065</v>
-      </c>
-      <c r="W35">
-        <v>2.8235123157501221</v>
+      <c r="T35">
+        <v>3.729662179946899</v>
+      </c>
+      <c r="U35">
+        <v>1.5458499193191531</v>
+      </c>
+      <c r="V35">
+        <f t="shared" si="5"/>
+        <v>102.78073613644416</v>
       </c>
       <c r="X35">
-        <v>1.3617532253265381</v>
+        <v>2.78761887550354</v>
       </c>
       <c r="Y35">
-        <f t="shared" si="7"/>
-        <v>88.328494582250812</v>
-      </c>
-      <c r="AA35" s="2">
-        <f t="shared" si="8"/>
-        <v>2.7113115653600044</v>
-      </c>
-      <c r="AB35" s="2">
-        <f t="shared" si="9"/>
-        <v>4.037988030142726</v>
-      </c>
-    </row>
-    <row r="36" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1.449684262275696</v>
+      </c>
+      <c r="Z35">
+        <f t="shared" si="6"/>
+        <v>81.916148969306022</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -3313,34 +3092,28 @@
         <f t="shared" si="4"/>
         <v>98.027871854575253</v>
       </c>
-      <c r="T36" s="2">
-        <f t="shared" si="5"/>
-        <v>4.111652548969329</v>
-      </c>
-      <c r="U36" s="2">
-        <f t="shared" si="6"/>
-        <v>29.215118735809014</v>
-      </c>
-      <c r="W36">
-        <v>2.584694623947144</v>
+      <c r="T36">
+        <v>3.4584255218505859</v>
+      </c>
+      <c r="U36">
+        <v>1.3760194778442381</v>
+      </c>
+      <c r="V36">
+        <f t="shared" si="5"/>
+        <v>107.06891477891692</v>
       </c>
       <c r="X36">
-        <v>1.2065291404724121</v>
+        <v>2.571627140045166</v>
       </c>
       <c r="Y36">
-        <f t="shared" si="7"/>
-        <v>91.260108072584558</v>
-      </c>
-      <c r="AA36" s="2">
-        <f t="shared" si="8"/>
-        <v>2.1319718308540714</v>
-      </c>
-      <c r="AB36" s="2">
-        <f t="shared" si="9"/>
-        <v>5.1258290905647961</v>
-      </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.2581450939178469</v>
+      </c>
+      <c r="Z36">
+        <f t="shared" si="6"/>
+        <v>87.073665449534516</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -3394,34 +3167,28 @@
         <f t="shared" si="4"/>
         <v>75.980708729842561</v>
       </c>
-      <c r="T37" s="2">
-        <f t="shared" si="5"/>
-        <v>5.3921708259311494</v>
-      </c>
-      <c r="U37" s="2">
-        <f t="shared" si="6"/>
-        <v>3.2215962646755849</v>
-      </c>
-      <c r="W37">
-        <v>5.4683771133422852</v>
+      <c r="T37">
+        <v>5.6507425308227539</v>
+      </c>
+      <c r="U37">
+        <v>2.348324060440063</v>
+      </c>
+      <c r="V37">
+        <f t="shared" si="5"/>
+        <v>102.50783157291923</v>
       </c>
       <c r="X37">
-        <v>3.3716306686401372</v>
+        <v>5.4126324653625488</v>
       </c>
       <c r="Y37">
-        <f t="shared" si="7"/>
-        <v>69.092040074397261</v>
-      </c>
-      <c r="AA37" s="2">
-        <f t="shared" si="8"/>
-        <v>3.9911316722740882</v>
-      </c>
-      <c r="AB37" s="2">
-        <f t="shared" si="9"/>
-        <v>5.5812196605541784</v>
-      </c>
-    </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.2">
+        <v>3.2283375263214111</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="6"/>
+        <v>71.423176056409957</v>
+      </c>
+    </row>
+    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -3475,34 +3242,28 @@
         <f t="shared" si="4"/>
         <v>149.61301959775122</v>
       </c>
-      <c r="T38" s="2">
-        <f t="shared" si="5"/>
-        <v>4.1069042972819183</v>
-      </c>
-      <c r="U38" s="2">
-        <f t="shared" si="6"/>
-        <v>8.2463538883684944</v>
-      </c>
-      <c r="W38">
-        <v>3.000944852828979</v>
+      <c r="T38">
+        <v>3.788763284683228</v>
+      </c>
+      <c r="U38">
+        <v>1.2012449502944951</v>
+      </c>
+      <c r="V38">
+        <f t="shared" si="5"/>
+        <v>134.3616882048486</v>
       </c>
       <c r="X38">
-        <v>0.92463088035583496</v>
+        <v>2.935302734375</v>
       </c>
       <c r="Y38">
-        <f t="shared" si="7"/>
-        <v>138.26083511856322</v>
-      </c>
-      <c r="AA38" s="2">
-        <f t="shared" si="8"/>
-        <v>3.1484636814917213</v>
-      </c>
-      <c r="AB38" s="2">
-        <f t="shared" si="9"/>
-        <v>4.8037268751300637</v>
-      </c>
-    </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.92695754766464233</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="6"/>
+        <v>134.89709863030177</v>
+      </c>
+    </row>
+    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3556,34 +3317,28 @@
         <f t="shared" si="4"/>
         <v>87.829154013435073</v>
       </c>
-      <c r="T39" s="2">
-        <f t="shared" si="5"/>
-        <v>5.5950694182904614</v>
-      </c>
-      <c r="U39" s="2">
-        <f t="shared" si="6"/>
-        <v>4.375201898579979</v>
-      </c>
-      <c r="W39">
-        <v>5.9895129203796387</v>
+      <c r="T39">
+        <v>6.186798095703125</v>
+      </c>
+      <c r="U39">
+        <v>2.3957376480102539</v>
+      </c>
+      <c r="V39">
+        <f t="shared" si="5"/>
+        <v>110.01103239346604</v>
       </c>
       <c r="X39">
-        <v>3.2302484512329102</v>
+        <v>5.8588285446166992</v>
       </c>
       <c r="Y39">
-        <f t="shared" si="7"/>
-        <v>78.988730508435808</v>
-      </c>
-      <c r="AA39" s="2">
-        <f t="shared" si="8"/>
-        <v>4.5282944341424605</v>
-      </c>
-      <c r="AB39" s="2">
-        <f t="shared" si="9"/>
-        <v>6.1569046381054333</v>
-      </c>
-    </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.2">
+        <v>3.1004500389099121</v>
+      </c>
+      <c r="Z39">
+        <f t="shared" si="6"/>
+        <v>80.499949174369604</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3637,34 +3392,28 @@
         <f t="shared" si="4"/>
         <v>68.543898627471719</v>
       </c>
-      <c r="T40" s="2">
-        <f t="shared" si="5"/>
-        <v>3.0521090890563718</v>
-      </c>
-      <c r="U40" s="2">
-        <f t="shared" si="6"/>
-        <v>0.1765696303101032</v>
-      </c>
-      <c r="W40">
-        <v>6.8145890235900879</v>
+      <c r="T40">
+        <v>6.6462020874023438</v>
+      </c>
+      <c r="U40">
+        <v>2.687197208404541</v>
+      </c>
+      <c r="V40">
+        <f t="shared" si="5"/>
+        <v>105.36189125484339</v>
       </c>
       <c r="X40">
-        <v>4.4260163307189941</v>
+        <v>6.5131745338439941</v>
       </c>
       <c r="Y40">
-        <f t="shared" si="7"/>
-        <v>65.589785737461199</v>
-      </c>
-      <c r="AA40" s="2">
-        <f t="shared" si="8"/>
-        <v>0.33553731838522349</v>
-      </c>
-      <c r="AB40" s="2">
-        <f t="shared" si="9"/>
-        <v>4.8545718111154512</v>
-      </c>
-    </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.2">
+        <v>4.4666094779968262</v>
+      </c>
+      <c r="Z40">
+        <f t="shared" si="6"/>
+        <v>62.118975973910089</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3718,34 +3467,28 @@
         <f t="shared" si="4"/>
         <v>110.78777520519267</v>
       </c>
-      <c r="T41" s="2">
-        <f t="shared" si="5"/>
-        <v>3.8151692737918483</v>
-      </c>
-      <c r="U41" s="2">
-        <f t="shared" si="6"/>
-        <v>14.367041283621774</v>
-      </c>
-      <c r="W41">
-        <v>2.4934344291687012</v>
+      <c r="T41">
+        <v>3.117445707321167</v>
+      </c>
+      <c r="U41">
+        <v>1.3539582490921021</v>
+      </c>
+      <c r="V41">
+        <f t="shared" si="5"/>
+        <v>98.085132003700153</v>
       </c>
       <c r="X41">
-        <v>1.001788854598999</v>
+        <v>2.284206628799438</v>
       </c>
       <c r="Y41">
-        <f t="shared" si="7"/>
-        <v>106.03062248444149</v>
-      </c>
-      <c r="AA41" s="2">
-        <f t="shared" si="8"/>
-        <v>8.9502066402473552</v>
-      </c>
-      <c r="AB41" s="2">
-        <f t="shared" si="9"/>
-        <v>13.838348950466367</v>
-      </c>
-    </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.020569920539856</v>
+      </c>
+      <c r="Z41">
+        <f t="shared" si="6"/>
+        <v>95.345934174494772</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3799,34 +3542,28 @@
         <f t="shared" si="4"/>
         <v>120.39173601764369</v>
       </c>
-      <c r="T42" s="2">
-        <f t="shared" si="5"/>
-        <v>4.064183722833314</v>
-      </c>
-      <c r="U42" s="2">
-        <f t="shared" si="6"/>
-        <v>1.231517598654859</v>
-      </c>
-      <c r="W42">
-        <v>1.699249267578125</v>
+      <c r="T42">
+        <v>2.380269050598145</v>
+      </c>
+      <c r="U42">
+        <v>0.97218215465545654</v>
+      </c>
+      <c r="V42">
+        <f t="shared" si="5"/>
+        <v>104.30087687788139</v>
       </c>
       <c r="X42">
-        <v>0.6909172534942627</v>
+        <v>1.682604312896729</v>
       </c>
       <c r="Y42">
-        <f t="shared" si="7"/>
-        <v>104.77088399687854</v>
-      </c>
-      <c r="AA42" s="2">
-        <f t="shared" si="8"/>
-        <v>3.9212220073433763</v>
-      </c>
-      <c r="AB42" s="2">
-        <f t="shared" si="9"/>
-        <v>10.403677393180473</v>
-      </c>
-    </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.67118847370147705</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="6"/>
+        <v>106.79405149029421</v>
+      </c>
+    </row>
+    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3880,34 +3617,28 @@
         <f t="shared" si="4"/>
         <v>119.87425316438599</v>
       </c>
-      <c r="T43" s="2">
-        <f t="shared" si="5"/>
-        <v>4.3835484569684775</v>
-      </c>
-      <c r="U43" s="2">
-        <f t="shared" si="6"/>
-        <v>2.0707287233986746</v>
-      </c>
-      <c r="W43">
-        <v>2.0686521530151372</v>
+      <c r="T43">
+        <v>3.051730632781982</v>
+      </c>
+      <c r="U43">
+        <v>1.186030268669128</v>
+      </c>
+      <c r="V43">
+        <f t="shared" si="5"/>
+        <v>109.61247375724629</v>
       </c>
       <c r="X43">
-        <v>0.83330827951431274</v>
+        <v>2.0290639400482182</v>
       </c>
       <c r="Y43">
-        <f t="shared" si="7"/>
-        <v>105.75266668847046</v>
-      </c>
-      <c r="AA43" s="2">
-        <f t="shared" si="8"/>
-        <v>5.2554661072118085</v>
-      </c>
-      <c r="AB43" s="2">
-        <f t="shared" si="9"/>
-        <v>7.3961593352810455</v>
-      </c>
-    </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.2">
+        <v>0.82050019502639771</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" si="6"/>
+        <v>105.34807371864109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3961,34 +3692,28 @@
         <f t="shared" si="4"/>
         <v>124.05557869819053</v>
       </c>
-      <c r="T44" s="2">
-        <f t="shared" si="5"/>
-        <v>3.9787767271886918</v>
-      </c>
-      <c r="U44" s="2">
-        <f t="shared" si="6"/>
-        <v>56.834822043922692</v>
-      </c>
-      <c r="W44">
-        <v>3.102859258651733</v>
+      <c r="T44">
+        <v>3.8110892772674561</v>
+      </c>
+      <c r="U44">
+        <v>1.3752356767654419</v>
+      </c>
+      <c r="V44">
+        <f t="shared" si="5"/>
+        <v>118.0542283763864</v>
       </c>
       <c r="X44">
-        <v>1.861116290092468</v>
+        <v>3.0317082405090332</v>
       </c>
       <c r="Y44">
-        <f t="shared" si="7"/>
-        <v>71.022854210349138</v>
-      </c>
-      <c r="AA44" s="2">
-        <f t="shared" si="8"/>
-        <v>1.9323875268099617</v>
-      </c>
-      <c r="AB44" s="2">
-        <f t="shared" si="9"/>
-        <v>71.294642438331152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.65027928352356</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="6"/>
+        <v>78.259940099466448</v>
+      </c>
+    </row>
+    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>7</v>
       </c>
@@ -4042,34 +3767,28 @@
         <f t="shared" si="4"/>
         <v>117.38720001137789</v>
       </c>
-      <c r="T45" s="2">
-        <f t="shared" si="5"/>
-        <v>4.7073043691195764</v>
-      </c>
-      <c r="U45" s="2">
-        <f t="shared" si="6"/>
-        <v>3.2827402662356167</v>
-      </c>
-      <c r="W45">
-        <v>2.7647426128387451</v>
+      <c r="T45">
+        <v>3.5112113952636719</v>
+      </c>
+      <c r="U45">
+        <v>1.2591737508773799</v>
+      </c>
+      <c r="V45">
+        <f t="shared" si="5"/>
+        <v>118.79027027152203</v>
       </c>
       <c r="X45">
-        <v>1.183271527290344</v>
+        <v>2.7036724090576172</v>
       </c>
       <c r="Y45">
-        <f t="shared" si="7"/>
-        <v>99.535922719780757</v>
-      </c>
-      <c r="AA45" s="2">
-        <f t="shared" si="8"/>
-        <v>3.6742173772299824</v>
-      </c>
-      <c r="AB45" s="2">
-        <f t="shared" si="9"/>
-        <v>13.601337105447767</v>
-      </c>
-    </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.1111242771148679</v>
+      </c>
+      <c r="Z45">
+        <f t="shared" si="6"/>
+        <v>103.65756131273389</v>
+      </c>
+    </row>
+    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>7</v>
       </c>
@@ -4123,34 +3842,28 @@
         <f t="shared" si="4"/>
         <v>117.797055321</v>
       </c>
-      <c r="T46" s="2">
-        <f t="shared" si="5"/>
-        <v>3.8844941859082596</v>
-      </c>
-      <c r="U46" s="2">
-        <f t="shared" si="6"/>
-        <v>10.771184902682798</v>
-      </c>
-      <c r="W46">
-        <v>4.0099797248840332</v>
+      <c r="T46">
+        <v>5.0375103950500488</v>
+      </c>
+      <c r="U46">
+        <v>1.879160523414612</v>
+      </c>
+      <c r="V46">
+        <f t="shared" si="5"/>
+        <v>114.19882350244472</v>
       </c>
       <c r="X46">
-        <v>1.601717591285706</v>
+        <v>4.0133037567138672</v>
       </c>
       <c r="Y46">
-        <f t="shared" si="7"/>
-        <v>106.65120979509615</v>
-      </c>
-      <c r="AA46" s="2">
-        <f t="shared" si="8"/>
-        <v>4.6446216706529153</v>
-      </c>
-      <c r="AB46" s="2">
-        <f t="shared" si="9"/>
-        <v>5.3207253607118679</v>
-      </c>
-    </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.2">
+        <v>1.6114711761474609</v>
+      </c>
+      <c r="Z46">
+        <f t="shared" si="6"/>
+        <v>106.09356539094222</v>
+      </c>
+    </row>
+    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>7</v>
       </c>
@@ -4204,34 +3917,28 @@
         <f t="shared" si="4"/>
         <v>89.221511714556357</v>
       </c>
-      <c r="T47" s="2">
-        <f t="shared" si="5"/>
-        <v>6.2759463050099438</v>
-      </c>
-      <c r="U47" s="2">
-        <f t="shared" si="6"/>
-        <v>1.0075647763815918</v>
-      </c>
-      <c r="W47">
-        <v>6.3505568504333496</v>
+      <c r="T47">
+        <v>6.8021421432495117</v>
+      </c>
+      <c r="U47">
+        <v>2.712111234664917</v>
+      </c>
+      <c r="V47">
+        <f t="shared" si="5"/>
+        <v>106.84341484604528</v>
       </c>
       <c r="X47">
-        <v>3.3231453895568852</v>
+        <v>6.1517362594604492</v>
       </c>
       <c r="Y47">
-        <f t="shared" si="7"/>
-        <v>81.408925138155098</v>
-      </c>
-      <c r="AA47" s="2">
-        <f t="shared" si="8"/>
-        <v>2.8372574903098222</v>
-      </c>
-      <c r="AB47" s="2">
-        <f t="shared" si="9"/>
-        <v>6.4871788238819947</v>
-      </c>
-    </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.2">
+        <v>3.1605591773986821</v>
+      </c>
+      <c r="Z47">
+        <f t="shared" si="6"/>
+        <v>82.916953368222082</v>
+      </c>
+    </row>
+    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>7</v>
       </c>
@@ -4285,34 +3992,28 @@
         <f t="shared" si="4"/>
         <v>101.79507028989894</v>
       </c>
-      <c r="T48" s="2">
-        <f t="shared" si="5"/>
-        <v>5.8006759119568931</v>
-      </c>
-      <c r="U48" s="2">
-        <f t="shared" si="6"/>
-        <v>0.66094489918848365</v>
-      </c>
-      <c r="W48">
-        <v>6.7300195693969727</v>
+      <c r="T48">
+        <v>6.9928774833679199</v>
+      </c>
+      <c r="U48">
+        <v>2.5616440773010249</v>
+      </c>
+      <c r="V48">
+        <f t="shared" si="5"/>
+        <v>116.29115576754151</v>
       </c>
       <c r="X48">
-        <v>3.0132348537445068</v>
+        <v>6.5255260467529297</v>
       </c>
       <c r="Y48">
-        <f t="shared" si="7"/>
-        <v>95.146518056775179</v>
-      </c>
-      <c r="AA48" s="2">
-        <f t="shared" si="8"/>
-        <v>3.1122114336331732</v>
-      </c>
-      <c r="AB48" s="2">
-        <f t="shared" si="9"/>
-        <v>3.6580155404213088</v>
-      </c>
-    </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.2">
+        <v>2.839781761169434</v>
+      </c>
+      <c r="Z48">
+        <f t="shared" si="6"/>
+        <v>97.890403074605743</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>7</v>
       </c>
@@ -4366,77 +4067,40 @@
         <f t="shared" si="4"/>
         <v>21.682405083838052</v>
       </c>
-      <c r="T49" s="2">
-        <f t="shared" si="5"/>
-        <v>114.24844497969586</v>
-      </c>
-      <c r="U49" s="2">
-        <f t="shared" si="6"/>
-        <v>528.37763708206683</v>
-      </c>
-      <c r="W49">
-        <v>16.826993942260739</v>
+      <c r="T49">
+        <v>11.79590320587158</v>
+      </c>
+      <c r="U49">
+        <v>5.8723592758178711</v>
+      </c>
+      <c r="V49">
+        <f t="shared" si="5"/>
+        <v>85.571301367411564</v>
       </c>
       <c r="X49">
-        <v>16.23152923583984</v>
+        <v>14.01251125335693</v>
       </c>
       <c r="Y49">
-        <f t="shared" si="7"/>
-        <v>44.162805514409442</v>
-      </c>
-      <c r="AA49" s="2">
-        <f t="shared" si="8"/>
-        <v>33.008225407035837</v>
-      </c>
-      <c r="AB49" s="2">
-        <f t="shared" si="9"/>
-        <v>67.109363250577843</v>
-      </c>
-    </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="T50" t="s">
-        <v>22</v>
-      </c>
-      <c r="U50" t="s">
-        <v>23</v>
-      </c>
-      <c r="W50"/>
-      <c r="AA50" t="s">
-        <v>22</v>
-      </c>
-      <c r="AB50" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="T51" s="2">
-        <f>AVERAGEIF(T3:T49, "&lt;=50", T3:T49)</f>
-        <v>6.1365574141374859</v>
-      </c>
-      <c r="U51" s="2">
-        <f>AVERAGEIF(U3:U49, "&lt;=50", U3:U49)</f>
-        <v>9.3641724638717125</v>
-      </c>
-      <c r="W51"/>
-      <c r="AA51" s="2">
-        <f>AVERAGEIF(AA3:AA49, "&lt;=50", AA3:AA49)</f>
-        <v>7.2448324400878743</v>
-      </c>
-      <c r="AB51" s="2">
-        <f>AVERAGEIF(AB3:AB49, "&lt;=50", AB3:AB49)</f>
-        <v>11.681832499286866</v>
+        <v>11.848756790161129</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="6"/>
+        <v>50.379371363106422</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="T3:U49">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>OR($T3&gt;=30, $U3&gt;=30)</formula>
+  <conditionalFormatting sqref="Q34:Q37 A34:E40 J34:N40 Q39:Q40">
+    <cfRule type="expression" dxfId="2" priority="22">
+      <formula>#REF!*0.9&gt;$M34</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="23">
+      <formula>#REF!*1.05&lt;$L34</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA3:AB49 AA51:AB51">
+  <conditionalFormatting sqref="T3:U49">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>OR($AA3&gt;=30, $AB3&gt;=30)</formula>
+      <formula>OR($T3&gt;=50, $U3&gt;=50)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data_contrast/experiment_data.xlsx
+++ b/data_contrast/experiment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\data_contrast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F722B5F-875E-44E3-8300-BF3111F16B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6250174C-49F5-4FBE-8A3D-073CEA3EFF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1365" yWindow="1425" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="仿真数据" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
   <si>
     <t>仿真值</t>
   </si>
@@ -89,6 +89,26 @@
   <si>
     <t>R[Ω]</t>
   </si>
+  <si>
+    <t>仿真值相对误差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>R%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>使用特征工程相对误差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未使用特征工程相对误差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -111,12 +131,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -133,11 +159,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -474,14 +503,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:AI50"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="20" max="21" width="13.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.625" customWidth="1"/>
+    <col min="20" max="20" width="11.125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.125" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
       <c r="L1" t="s">
         <v>0</v>
       </c>
@@ -494,8 +525,17 @@
       <c r="X1" t="s">
         <v>3</v>
       </c>
+      <c r="AB1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -562,8 +602,26 @@
       <c r="Z2" t="s">
         <v>16</v>
       </c>
+      <c r="AB2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -599,13 +657,13 @@
         <v>6.78</v>
       </c>
       <c r="L3">
-        <v>1.8336879E-2</v>
+        <v>0.14960399999999999</v>
       </c>
       <c r="M3">
-        <v>8.8597703E-2</v>
+        <v>7.9237000000000002E-2</v>
       </c>
       <c r="N3">
-        <v>8.8168313170000001</v>
+        <v>80.431822999999994</v>
       </c>
       <c r="P3">
         <v>0.17976</v>
@@ -637,8 +695,32 @@
         <f>6780000*2*3.1415926*X3*0.000001/Y3</f>
         <v>62.541474481504522</v>
       </c>
+      <c r="AB3">
+        <f>ABS(P3-L3)/P3*100</f>
+        <v>16.775700934579447</v>
+      </c>
+      <c r="AC3">
+        <f>ABS(Q3-M3)/Q3*100</f>
+        <v>8.4790593453302225</v>
+      </c>
+      <c r="AE3">
+        <f>ABS(P3-T3)/P3*100</f>
+        <v>30.973404717540891</v>
+      </c>
+      <c r="AF3">
+        <f>ABS(Q3-U3)/Q3*100</f>
+        <v>11.096238327713719</v>
+      </c>
+      <c r="AH3">
+        <f>ABS(P3-X3)/P3*100</f>
+        <v>42.596177817133736</v>
+      </c>
+      <c r="AI3">
+        <f>ABS(Q3-Y3)/Q3*100</f>
+        <v>18.816502094434028</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -674,13 +756,13 @@
         <v>6.78</v>
       </c>
       <c r="L4">
-        <v>1.8447351000000001E-2</v>
+        <v>0.15662000000000001</v>
       </c>
       <c r="M4">
-        <v>0.14243311</v>
+        <v>0.112703</v>
       </c>
       <c r="N4">
-        <v>5.5173764810000003</v>
+        <v>59.199742000000001</v>
       </c>
       <c r="P4">
         <v>0.21931999999999999</v>
@@ -699,7 +781,7 @@
         <v>8.6934715509414673E-2</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V3:V49" si="5">6780000*2*3.1415926*T4*0.000001/U4</f>
+        <f t="shared" ref="V4:V49" si="5">6780000*2*3.1415926*T4*0.000001/U4</f>
         <v>79.123561502886048</v>
       </c>
       <c r="X4">
@@ -712,8 +794,32 @@
         <f t="shared" ref="Z4:Z49" si="6">6780000*2*3.1415926*X4*0.000001/Y4</f>
         <v>60.488955775686705</v>
       </c>
+      <c r="AB4">
+        <f t="shared" ref="AB4:AB48" si="7">ABS(P4-L4)/P4*100</f>
+        <v>28.588364034287789</v>
+      </c>
+      <c r="AC4">
+        <f t="shared" ref="AC4:AC49" si="8">ABS(Q4-M4)/Q4*100</f>
+        <v>18.069933120093047</v>
+      </c>
+      <c r="AE4">
+        <f t="shared" ref="AE4:AE49" si="9">ABS(P4-T4)/P4*100</f>
+        <v>26.377379305058763</v>
+      </c>
+      <c r="AF4">
+        <f t="shared" ref="AF4:AF49" si="10">ABS(Q4-U4)/Q4*100</f>
+        <v>36.802329522088776</v>
+      </c>
+      <c r="AH4">
+        <f t="shared" ref="AH4:AH49" si="11">ABS(P4-X4)/P4*100</f>
+        <v>20.414156359780915</v>
+      </c>
+      <c r="AI4">
+        <f t="shared" ref="AI4:AI49" si="12">ABS(Q4-Y4)/Q4*100</f>
+        <v>10.637489339923293</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -787,8 +893,32 @@
         <f t="shared" si="6"/>
         <v>73.845735323464666</v>
       </c>
+      <c r="AB5">
+        <f t="shared" si="7"/>
+        <v>12.55538395464696</v>
+      </c>
+      <c r="AC5">
+        <f t="shared" si="8"/>
+        <v>15.898569066710754</v>
+      </c>
+      <c r="AE5">
+        <f t="shared" si="9"/>
+        <v>27.443824484470746</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="10"/>
+        <v>26.489567455106638</v>
+      </c>
+      <c r="AH5">
+        <f t="shared" si="11"/>
+        <v>14.328025145498749</v>
+      </c>
+      <c r="AI5">
+        <f t="shared" si="12"/>
+        <v>4.8732140443241283</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -862,8 +992,32 @@
         <f t="shared" si="6"/>
         <v>123.61693336601557</v>
       </c>
+      <c r="AB6">
+        <f t="shared" si="7"/>
+        <v>10.34079191787518</v>
+      </c>
+      <c r="AC6">
+        <f t="shared" si="8"/>
+        <v>16.74820196518753</v>
+      </c>
+      <c r="AE6">
+        <f t="shared" si="9"/>
+        <v>19.980545861336033</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="10"/>
+        <v>2.1956418484642293</v>
+      </c>
+      <c r="AH6">
+        <f t="shared" si="11"/>
+        <v>13.017524848528961</v>
+      </c>
+      <c r="AI6">
+        <f t="shared" si="12"/>
+        <v>25.230066470515126</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -937,8 +1091,32 @@
         <f t="shared" si="6"/>
         <v>96.06964517307199</v>
       </c>
+      <c r="AB7">
+        <f t="shared" si="7"/>
+        <v>7.4506165113799661</v>
+      </c>
+      <c r="AC7">
+        <f t="shared" si="8"/>
+        <v>15.196523447967838</v>
+      </c>
+      <c r="AE7">
+        <f t="shared" si="9"/>
+        <v>10.839727766705144</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="10"/>
+        <v>17.16003913121224</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="11"/>
+        <v>7.0459859281555941</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="12"/>
+        <v>20.571207095065695</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1012,8 +1190,32 @@
         <f t="shared" si="6"/>
         <v>125.18964287226396</v>
       </c>
+      <c r="AB8">
+        <f t="shared" si="7"/>
+        <v>6.6397479333587723</v>
+      </c>
+      <c r="AC8">
+        <f t="shared" si="8"/>
+        <v>9.246349758162026</v>
+      </c>
+      <c r="AE8">
+        <f t="shared" si="9"/>
+        <v>9.2643715476286435</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="10"/>
+        <v>6.9402464067489564</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="11"/>
+        <v>6.3033480294315183</v>
+      </c>
+      <c r="AI8">
+        <f t="shared" si="12"/>
+        <v>5.2677145892215851</v>
+      </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1087,8 +1289,32 @@
         <f t="shared" si="6"/>
         <v>126.35271262872628</v>
       </c>
+      <c r="AB9">
+        <f t="shared" si="7"/>
+        <v>6.3261210478370122</v>
+      </c>
+      <c r="AC9">
+        <f t="shared" si="8"/>
+        <v>9.6468174347981375</v>
+      </c>
+      <c r="AE9">
+        <f t="shared" si="9"/>
+        <v>9.1144715984514857</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="10"/>
+        <v>12.145116985930258</v>
+      </c>
+      <c r="AH9">
+        <f t="shared" si="11"/>
+        <v>4.3329493038062186</v>
+      </c>
+      <c r="AI9">
+        <f t="shared" si="12"/>
+        <v>3.7276485384511719</v>
+      </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1162,8 +1388,32 @@
         <f t="shared" si="6"/>
         <v>103.1091976044388</v>
       </c>
+      <c r="AB10">
+        <f t="shared" si="7"/>
+        <v>6.5910470646425496</v>
+      </c>
+      <c r="AC10">
+        <f t="shared" si="8"/>
+        <v>3.208589999051136</v>
+      </c>
+      <c r="AE10">
+        <f t="shared" si="9"/>
+        <v>10.843908453406764</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="10"/>
+        <v>1.4317546242361723</v>
+      </c>
+      <c r="AH10">
+        <f t="shared" si="11"/>
+        <v>8.297132584882041</v>
+      </c>
+      <c r="AI10">
+        <f t="shared" si="12"/>
+        <v>5.5133190312481775</v>
+      </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1237,8 +1487,32 @@
         <f t="shared" si="6"/>
         <v>85.2921282014794</v>
       </c>
+      <c r="AB11">
+        <f t="shared" si="7"/>
+        <v>27.101478404108427</v>
+      </c>
+      <c r="AC11">
+        <f t="shared" si="8"/>
+        <v>78.44825359088658</v>
+      </c>
+      <c r="AE11">
+        <f t="shared" si="9"/>
+        <v>12.510514591429859</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="10"/>
+        <v>11.504909483261072</v>
+      </c>
+      <c r="AH11">
+        <f t="shared" si="11"/>
+        <v>7.052013602085462</v>
+      </c>
+      <c r="AI11">
+        <f t="shared" si="12"/>
+        <v>5.0807102651157035</v>
+      </c>
     </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1312,8 +1586,32 @@
         <f t="shared" si="6"/>
         <v>104.30115859472703</v>
       </c>
+      <c r="AB12">
+        <f t="shared" si="7"/>
+        <v>8.2197520250368168</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="8"/>
+        <v>4.0801746403786927</v>
+      </c>
+      <c r="AE12">
+        <f t="shared" si="9"/>
+        <v>7.44455354027615</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="10"/>
+        <v>3.5070856505388051</v>
+      </c>
+      <c r="AH12">
+        <f t="shared" si="11"/>
+        <v>11.309758939167198</v>
+      </c>
+      <c r="AI12">
+        <f t="shared" si="12"/>
+        <v>9.5690513918343711</v>
+      </c>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1387,8 +1685,32 @@
         <f t="shared" si="6"/>
         <v>108.4025748000511</v>
       </c>
+      <c r="AB13">
+        <f t="shared" si="7"/>
+        <v>24.696333988732178</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="8"/>
+        <v>84.008394398145867</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="9"/>
+        <v>12.081920668349241</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="10"/>
+        <v>14.767716703250802</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="11"/>
+        <v>5.7685206074991822</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="12"/>
+        <v>3.4114064793596364</v>
+      </c>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1462,8 +1784,32 @@
         <f t="shared" si="6"/>
         <v>119.34276154239784</v>
       </c>
+      <c r="AB14">
+        <f t="shared" si="7"/>
+        <v>6.0041675967596806</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="8"/>
+        <v>11.413465450903926</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="9"/>
+        <v>11.005522730541497</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="10"/>
+        <v>5.046844673428188</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="11"/>
+        <v>7.5179267423202276</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="12"/>
+        <v>3.3461661065616939</v>
+      </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1537,8 +1883,32 @@
         <f t="shared" si="6"/>
         <v>131.18929942431464</v>
       </c>
+      <c r="AB15">
+        <f t="shared" si="7"/>
+        <v>5.9301236894988509</v>
+      </c>
+      <c r="AC15">
+        <f t="shared" si="8"/>
+        <v>11.259286029303674</v>
+      </c>
+      <c r="AE15">
+        <f t="shared" si="9"/>
+        <v>8.4442089289334419</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="10"/>
+        <v>1.2199855770235162</v>
+      </c>
+      <c r="AH15">
+        <f t="shared" si="11"/>
+        <v>6.5431705350238376</v>
+      </c>
+      <c r="AI15">
+        <f t="shared" si="12"/>
+        <v>4.5379638391478911</v>
+      </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -1612,8 +1982,32 @@
         <f t="shared" si="6"/>
         <v>136.55507160516052</v>
       </c>
+      <c r="AB16">
+        <f t="shared" si="7"/>
+        <v>5.0966208925944017</v>
+      </c>
+      <c r="AC16">
+        <f t="shared" si="8"/>
+        <v>7.6703476337903513</v>
+      </c>
+      <c r="AE16">
+        <f t="shared" si="9"/>
+        <v>9.6368214652114901</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="10"/>
+        <v>0.94253733220327085</v>
+      </c>
+      <c r="AH16">
+        <f t="shared" si="11"/>
+        <v>1.9040261605839393</v>
+      </c>
+      <c r="AI16">
+        <f t="shared" si="12"/>
+        <v>4.8704577146088983</v>
+      </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -1687,8 +2081,32 @@
         <f t="shared" si="6"/>
         <v>132.23652323777208</v>
       </c>
+      <c r="AB17">
+        <f t="shared" si="7"/>
+        <v>4.9989251598038535</v>
+      </c>
+      <c r="AC17">
+        <f t="shared" si="8"/>
+        <v>5.7436367236723651</v>
+      </c>
+      <c r="AE17">
+        <f t="shared" si="9"/>
+        <v>6.3479964378177849</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="10"/>
+        <v>10.0162682932417</v>
+      </c>
+      <c r="AH17">
+        <f t="shared" si="11"/>
+        <v>5.4335477399807131</v>
+      </c>
+      <c r="AI17">
+        <f t="shared" si="12"/>
+        <v>7.587413890848925</v>
+      </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -1762,8 +2180,32 @@
         <f t="shared" si="6"/>
         <v>159.90489476481977</v>
       </c>
+      <c r="AB18">
+        <f t="shared" si="7"/>
+        <v>4.2099149472925648</v>
+      </c>
+      <c r="AC18">
+        <f t="shared" si="8"/>
+        <v>8.0360302045183314</v>
+      </c>
+      <c r="AE18">
+        <f t="shared" si="9"/>
+        <v>3.2550073505596875</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="10"/>
+        <v>30.53831723113003</v>
+      </c>
+      <c r="AH18">
+        <f t="shared" si="11"/>
+        <v>4.9654714974619454</v>
+      </c>
+      <c r="AI18">
+        <f t="shared" si="12"/>
+        <v>15.634899493387355</v>
+      </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4</v>
       </c>
@@ -1837,8 +2279,32 @@
         <f t="shared" si="6"/>
         <v>56.894986617585147</v>
       </c>
+      <c r="AB19">
+        <f t="shared" si="7"/>
+        <v>4.7647188388772062</v>
+      </c>
+      <c r="AC19">
+        <f t="shared" si="8"/>
+        <v>15.066874103705938</v>
+      </c>
+      <c r="AE19">
+        <f t="shared" si="9"/>
+        <v>1.4820608261917816</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="10"/>
+        <v>59.563003949322166</v>
+      </c>
+      <c r="AH19">
+        <f t="shared" si="11"/>
+        <v>2.7089421380888417</v>
+      </c>
+      <c r="AI19">
+        <f t="shared" si="12"/>
+        <v>77.857758675136949</v>
+      </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -1912,8 +2378,32 @@
         <f t="shared" si="6"/>
         <v>53.94354233015698</v>
       </c>
+      <c r="AB20">
+        <f t="shared" si="7"/>
+        <v>5.1597752554344796</v>
+      </c>
+      <c r="AC20">
+        <f t="shared" si="8"/>
+        <v>17.883843878787879</v>
+      </c>
+      <c r="AE20">
+        <f t="shared" si="9"/>
+        <v>10.13026354110225</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="10"/>
+        <v>58.671552484685726</v>
+      </c>
+      <c r="AH20">
+        <f t="shared" si="11"/>
+        <v>3.0078692770235747</v>
+      </c>
+      <c r="AI20">
+        <f t="shared" si="12"/>
+        <v>96.639335516727343</v>
+      </c>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4</v>
       </c>
@@ -1987,8 +2477,32 @@
         <f t="shared" si="6"/>
         <v>78.094370455966526</v>
       </c>
+      <c r="AB21">
+        <f t="shared" si="7"/>
+        <v>4.24115539040874</v>
+      </c>
+      <c r="AC21">
+        <f t="shared" si="8"/>
+        <v>5.9708498825539227</v>
+      </c>
+      <c r="AE21">
+        <f t="shared" si="9"/>
+        <v>1.0124546401967298</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="10"/>
+        <v>28.940705583056353</v>
+      </c>
+      <c r="AH21">
+        <f t="shared" si="11"/>
+        <v>3.7909030307840297</v>
+      </c>
+      <c r="AI21">
+        <f t="shared" si="12"/>
+        <v>28.394761511275902</v>
+      </c>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4</v>
       </c>
@@ -2062,8 +2576,32 @@
         <f t="shared" si="6"/>
         <v>104.75051263659994</v>
       </c>
+      <c r="AB22">
+        <f t="shared" si="7"/>
+        <v>3.6510369585172833</v>
+      </c>
+      <c r="AC22">
+        <f t="shared" si="8"/>
+        <v>27.738585587098928</v>
+      </c>
+      <c r="AE22">
+        <f t="shared" si="9"/>
+        <v>6.9468004738851477</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="10"/>
+        <v>55.931357754272057</v>
+      </c>
+      <c r="AH22">
+        <f t="shared" si="11"/>
+        <v>1.7145019126385515</v>
+      </c>
+      <c r="AI22">
+        <f t="shared" si="12"/>
+        <v>22.884191746634023</v>
+      </c>
     </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
@@ -2137,8 +2675,32 @@
         <f t="shared" si="6"/>
         <v>90.460608740819751</v>
       </c>
+      <c r="AB23">
+        <f t="shared" si="7"/>
+        <v>3.7662477752224741</v>
+      </c>
+      <c r="AC23">
+        <f t="shared" si="8"/>
+        <v>18.874153622672829</v>
+      </c>
+      <c r="AE23">
+        <f t="shared" si="9"/>
+        <v>10.709086714619533</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="10"/>
+        <v>37.491669644102778</v>
+      </c>
+      <c r="AH23">
+        <f t="shared" si="11"/>
+        <v>2.5049787463575406</v>
+      </c>
+      <c r="AI23">
+        <f t="shared" si="12"/>
+        <v>36.123724316244484</v>
+      </c>
     </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4</v>
       </c>
@@ -2212,8 +2774,32 @@
         <f t="shared" si="6"/>
         <v>92.779072377486202</v>
       </c>
+      <c r="AB24">
+        <f t="shared" si="7"/>
+        <v>3.8700182309803726</v>
+      </c>
+      <c r="AC24">
+        <f t="shared" si="8"/>
+        <v>18.622274506466983</v>
+      </c>
+      <c r="AE24">
+        <f t="shared" si="9"/>
+        <v>6.8179993897284765</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="10"/>
+        <v>28.686691807434627</v>
+      </c>
+      <c r="AH24">
+        <f t="shared" si="11"/>
+        <v>2.9070640744314749</v>
+      </c>
+      <c r="AI24">
+        <f t="shared" si="12"/>
+        <v>23.459383395623266</v>
+      </c>
     </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4</v>
       </c>
@@ -2287,8 +2873,32 @@
         <f t="shared" si="6"/>
         <v>124.42911766901474</v>
       </c>
+      <c r="AB25">
+        <f t="shared" si="7"/>
+        <v>3.333571561554558</v>
+      </c>
+      <c r="AC25">
+        <f t="shared" si="8"/>
+        <v>3.8276534915302731</v>
+      </c>
+      <c r="AE25">
+        <f t="shared" si="9"/>
+        <v>10.842861462283071</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="10"/>
+        <v>24.549651575932593</v>
+      </c>
+      <c r="AH25">
+        <f t="shared" si="11"/>
+        <v>3.6272006189838635</v>
+      </c>
+      <c r="AI25">
+        <f t="shared" si="12"/>
+        <v>1.3347976637674037</v>
+      </c>
     </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -2362,8 +2972,32 @@
         <f t="shared" si="6"/>
         <v>78.975106222321756</v>
       </c>
+      <c r="AB26">
+        <f t="shared" si="7"/>
+        <v>5.5670046427003035</v>
+      </c>
+      <c r="AC26">
+        <f t="shared" si="8"/>
+        <v>51.846682582848466</v>
+      </c>
+      <c r="AE26">
+        <f t="shared" si="9"/>
+        <v>25.419002336468218</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="10"/>
+        <v>40.917516421161956</v>
+      </c>
+      <c r="AH26">
+        <f t="shared" si="11"/>
+        <v>2.9857465094354811</v>
+      </c>
+      <c r="AI26">
+        <f t="shared" si="12"/>
+        <v>31.87702942159909</v>
+      </c>
     </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -2437,8 +3071,32 @@
         <f t="shared" si="6"/>
         <v>85.749713492701531</v>
       </c>
+      <c r="AB27">
+        <f t="shared" si="7"/>
+        <v>4.7754027436527533</v>
+      </c>
+      <c r="AC27">
+        <f t="shared" si="8"/>
+        <v>10.576503028221776</v>
+      </c>
+      <c r="AE27">
+        <f t="shared" si="9"/>
+        <v>24.799580382675941</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="10"/>
+        <v>22.310016881097688</v>
+      </c>
+      <c r="AH27">
+        <f t="shared" si="11"/>
+        <v>5.7957783052578469</v>
+      </c>
+      <c r="AI27">
+        <f t="shared" si="12"/>
+        <v>7.0360568436709334</v>
+      </c>
     </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -2512,8 +3170,32 @@
         <f t="shared" si="6"/>
         <v>115.79863044329494</v>
       </c>
+      <c r="AB28">
+        <f t="shared" si="7"/>
+        <v>4.1292825652155356</v>
+      </c>
+      <c r="AC28">
+        <f t="shared" si="8"/>
+        <v>9.3694273270283777</v>
+      </c>
+      <c r="AE28">
+        <f t="shared" si="9"/>
+        <v>23.377084539283508</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="10"/>
+        <v>29.096925763006347</v>
+      </c>
+      <c r="AH28">
+        <f t="shared" si="11"/>
+        <v>4.8944341207525381</v>
+      </c>
+      <c r="AI28">
+        <f t="shared" si="12"/>
+        <v>2.3108090495161324</v>
+      </c>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -2587,8 +3269,32 @@
         <f t="shared" si="6"/>
         <v>141.06008801625333</v>
       </c>
+      <c r="AB29">
+        <f t="shared" si="7"/>
+        <v>4.1711175630894726</v>
+      </c>
+      <c r="AC29">
+        <f t="shared" si="8"/>
+        <v>11.894673351330512</v>
+      </c>
+      <c r="AE29">
+        <f t="shared" si="9"/>
+        <v>26.859578374025951</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="10"/>
+        <v>44.776958229456284</v>
+      </c>
+      <c r="AH29">
+        <f t="shared" si="11"/>
+        <v>5.3562049078084657</v>
+      </c>
+      <c r="AI29">
+        <f t="shared" si="12"/>
+        <v>8.1068843108919104</v>
+      </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -2662,8 +3368,32 @@
         <f t="shared" si="6"/>
         <v>130.22495647400189</v>
       </c>
+      <c r="AB30">
+        <f t="shared" si="7"/>
+        <v>4.108458406320378</v>
+      </c>
+      <c r="AC30">
+        <f t="shared" si="8"/>
+        <v>9.4979361646505289</v>
+      </c>
+      <c r="AE30">
+        <f t="shared" si="9"/>
+        <v>21.560831608269584</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="10"/>
+        <v>32.766403331330892</v>
+      </c>
+      <c r="AH30">
+        <f t="shared" si="11"/>
+        <v>2.4135700878091044</v>
+      </c>
+      <c r="AI30">
+        <f t="shared" si="12"/>
+        <v>6.1131106126267989</v>
+      </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -2737,8 +3467,32 @@
         <f t="shared" si="6"/>
         <v>81.058063941426369</v>
       </c>
+      <c r="AB31">
+        <f t="shared" si="7"/>
+        <v>4.1427571444456763</v>
+      </c>
+      <c r="AC31">
+        <f t="shared" si="8"/>
+        <v>1.0708962384233855</v>
+      </c>
+      <c r="AE31">
+        <f t="shared" si="9"/>
+        <v>8.7529129304889004</v>
+      </c>
+      <c r="AF31">
+        <f t="shared" si="10"/>
+        <v>16.975263684238474</v>
+      </c>
+      <c r="AH31">
+        <f t="shared" si="11"/>
+        <v>4.7875550171563797</v>
+      </c>
+      <c r="AI31">
+        <f t="shared" si="12"/>
+        <v>1.2423530682088899</v>
+      </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -2812,8 +3566,32 @@
         <f t="shared" si="6"/>
         <v>127.14180940971868</v>
       </c>
+      <c r="AB32">
+        <f t="shared" si="7"/>
+        <v>4.0636118141049433</v>
+      </c>
+      <c r="AC32">
+        <f t="shared" si="8"/>
+        <v>12.452502537060967</v>
+      </c>
+      <c r="AE32">
+        <f t="shared" si="9"/>
+        <v>24.61332596680775</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" si="10"/>
+        <v>38.80916595838513</v>
+      </c>
+      <c r="AH32">
+        <f t="shared" si="11"/>
+        <v>4.2973903420754187</v>
+      </c>
+      <c r="AI32">
+        <f t="shared" si="12"/>
+        <v>11.690280141195684</v>
+      </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>5</v>
       </c>
@@ -2887,8 +3665,32 @@
         <f t="shared" si="6"/>
         <v>108.97085931062652</v>
       </c>
+      <c r="AB33">
+        <f t="shared" si="7"/>
+        <v>64.403865791268757</v>
+      </c>
+      <c r="AC33">
+        <f t="shared" si="8"/>
+        <v>61.302675656108597</v>
+      </c>
+      <c r="AE33">
+        <f t="shared" si="9"/>
+        <v>23.492001186126245</v>
+      </c>
+      <c r="AF33">
+        <f t="shared" si="10"/>
+        <v>34.186712325428424</v>
+      </c>
+      <c r="AH33">
+        <f t="shared" si="11"/>
+        <v>13.829329231751398</v>
+      </c>
+      <c r="AI33">
+        <f t="shared" si="12"/>
+        <v>7.2609370650209071</v>
+      </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -2962,8 +3764,32 @@
         <f t="shared" si="6"/>
         <v>92.020872099947198</v>
       </c>
+      <c r="AB34">
+        <f t="shared" si="7"/>
+        <v>4.6146258694841285</v>
+      </c>
+      <c r="AC34">
+        <f t="shared" si="8"/>
+        <v>5.8941098486752752</v>
+      </c>
+      <c r="AE34">
+        <f t="shared" si="9"/>
+        <v>24.655021921696225</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="10"/>
+        <v>14.497612780473398</v>
+      </c>
+      <c r="AH34">
+        <f t="shared" si="11"/>
+        <v>4.5792555403731283</v>
+      </c>
+      <c r="AI34">
+        <f t="shared" si="12"/>
+        <v>5.5498829038124056</v>
+      </c>
     </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -3037,8 +3863,32 @@
         <f t="shared" si="6"/>
         <v>81.916148969306022</v>
       </c>
+      <c r="AB35">
+        <f t="shared" si="7"/>
+        <v>4.1841537820301911</v>
+      </c>
+      <c r="AC35">
+        <f t="shared" si="8"/>
+        <v>12.540884875474065</v>
+      </c>
+      <c r="AE35">
+        <f t="shared" si="9"/>
+        <v>28.511549167765793</v>
+      </c>
+      <c r="AF35">
+        <f t="shared" si="10"/>
+        <v>18.102981077175727</v>
+      </c>
+      <c r="AH35">
+        <f t="shared" si="11"/>
+        <v>3.9480781647184915</v>
+      </c>
+      <c r="AI35">
+        <f t="shared" si="12"/>
+        <v>10.755921940231957</v>
+      </c>
     </row>
-    <row r="36" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -3112,8 +3962,32 @@
         <f t="shared" si="6"/>
         <v>87.073665449534516</v>
       </c>
+      <c r="AB36">
+        <f t="shared" si="7"/>
+        <v>4.111652548969329</v>
+      </c>
+      <c r="AC36">
+        <f t="shared" si="8"/>
+        <v>29.215118735809014</v>
+      </c>
+      <c r="AE36">
+        <f t="shared" si="9"/>
+        <v>30.951363947390607</v>
+      </c>
+      <c r="AF36">
+        <f t="shared" si="10"/>
+        <v>19.893654948526454</v>
+      </c>
+      <c r="AH36">
+        <f t="shared" si="11"/>
+        <v>2.626764860084589</v>
+      </c>
+      <c r="AI36">
+        <f t="shared" si="12"/>
+        <v>9.623167545338239</v>
+      </c>
     </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -3187,8 +4061,32 @@
         <f t="shared" si="6"/>
         <v>71.423176056409957</v>
       </c>
+      <c r="AB37">
+        <f t="shared" si="7"/>
+        <v>5.3921708259311494</v>
+      </c>
+      <c r="AC37">
+        <f t="shared" si="8"/>
+        <v>3.2215962646755849</v>
+      </c>
+      <c r="AE37">
+        <f t="shared" si="9"/>
+        <v>0.78932298360599262</v>
+      </c>
+      <c r="AF37">
+        <f t="shared" si="10"/>
+        <v>26.463203468401609</v>
+      </c>
+      <c r="AH37">
+        <f t="shared" si="11"/>
+        <v>4.9698462811849566</v>
+      </c>
+      <c r="AI37">
+        <f t="shared" si="12"/>
+        <v>1.0940541842992144</v>
+      </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -3262,8 +4160,32 @@
         <f t="shared" si="6"/>
         <v>134.89709863030177</v>
       </c>
+      <c r="AB38">
+        <f t="shared" si="7"/>
+        <v>4.1069042972819183</v>
+      </c>
+      <c r="AC38">
+        <f t="shared" si="8"/>
+        <v>8.2463538883684944</v>
+      </c>
+      <c r="AE38">
+        <f t="shared" si="9"/>
+        <v>22.277336927004292</v>
+      </c>
+      <c r="AF38">
+        <f t="shared" si="10"/>
+        <v>36.156979347633332</v>
+      </c>
+      <c r="AH38">
+        <f t="shared" si="11"/>
+        <v>5.2669764603840576</v>
+      </c>
+      <c r="AI38">
+        <f t="shared" si="12"/>
+        <v>5.0674466040966113</v>
+      </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -3337,8 +4259,32 @@
         <f t="shared" si="6"/>
         <v>80.499949174369604</v>
       </c>
+      <c r="AB39">
+        <f t="shared" si="7"/>
+        <v>5.5950694182904614</v>
+      </c>
+      <c r="AC39">
+        <f t="shared" si="8"/>
+        <v>4.375201898579979</v>
+      </c>
+      <c r="AE39">
+        <f t="shared" si="9"/>
+        <v>1.383605972597473</v>
+      </c>
+      <c r="AF39">
+        <f t="shared" si="10"/>
+        <v>21.26794676097624</v>
+      </c>
+      <c r="AH39">
+        <f t="shared" si="11"/>
+        <v>6.6113787200857699</v>
+      </c>
+      <c r="AI39">
+        <f t="shared" si="12"/>
+        <v>1.8912891948441348</v>
+      </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -3412,8 +4358,32 @@
         <f t="shared" si="6"/>
         <v>62.118975973910089</v>
       </c>
+      <c r="AB40">
+        <f t="shared" si="7"/>
+        <v>3.0521090890563718</v>
+      </c>
+      <c r="AC40">
+        <f t="shared" si="8"/>
+        <v>0.1765696303101032</v>
+      </c>
+      <c r="AE40">
+        <f t="shared" si="9"/>
+        <v>2.1437308607093337</v>
+      </c>
+      <c r="AF40">
+        <f t="shared" si="10"/>
+        <v>36.338935149497971</v>
+      </c>
+      <c r="AH40">
+        <f t="shared" si="11"/>
+        <v>4.1023803138491441</v>
+      </c>
+      <c r="AI40">
+        <f t="shared" si="12"/>
+        <v>5.8162440595301304</v>
+      </c>
     </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -3487,8 +4457,32 @@
         <f t="shared" si="6"/>
         <v>95.345934174494772</v>
       </c>
+      <c r="AB41">
+        <f t="shared" si="7"/>
+        <v>3.8151692737918483</v>
+      </c>
+      <c r="AC41">
+        <f t="shared" si="8"/>
+        <v>14.367041283621774</v>
+      </c>
+      <c r="AE41">
+        <f t="shared" si="9"/>
+        <v>36.216276646035425</v>
+      </c>
+      <c r="AF41">
+        <f t="shared" si="10"/>
+        <v>53.857143565652898</v>
+      </c>
+      <c r="AH41">
+        <f t="shared" si="11"/>
+        <v>0.19196763089059499</v>
+      </c>
+      <c r="AI41">
+        <f t="shared" si="12"/>
+        <v>15.97253673706617</v>
+      </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -3562,8 +4556,32 @@
         <f t="shared" si="6"/>
         <v>106.79405149029421</v>
       </c>
+      <c r="AB42">
+        <f t="shared" si="7"/>
+        <v>4.064183722833314</v>
+      </c>
+      <c r="AC42">
+        <f t="shared" si="8"/>
+        <v>1.231517598654859</v>
+      </c>
+      <c r="AE42">
+        <f t="shared" si="9"/>
+        <v>34.584928791029348</v>
+      </c>
+      <c r="AF42">
+        <f t="shared" si="10"/>
+        <v>55.347813977957614</v>
+      </c>
+      <c r="AH42">
+        <f t="shared" si="11"/>
+        <v>4.8623593295980436</v>
+      </c>
+      <c r="AI42">
+        <f t="shared" si="12"/>
+        <v>7.2511582910910786</v>
+      </c>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -3637,8 +4655,32 @@
         <f t="shared" si="6"/>
         <v>105.34807371864109</v>
       </c>
+      <c r="AB43">
+        <f t="shared" si="7"/>
+        <v>4.3835484569684775</v>
+      </c>
+      <c r="AC43">
+        <f t="shared" si="8"/>
+        <v>2.0707287233986746</v>
+      </c>
+      <c r="AE43">
+        <f t="shared" si="9"/>
+        <v>39.769654336446933</v>
+      </c>
+      <c r="AF43">
+        <f t="shared" si="10"/>
+        <v>52.854710365646959</v>
+      </c>
+      <c r="AH43">
+        <f t="shared" si="11"/>
+        <v>7.0686113379033424</v>
+      </c>
+      <c r="AI43">
+        <f t="shared" si="12"/>
+        <v>5.7454628088459696</v>
+      </c>
     </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>7</v>
       </c>
@@ -3712,8 +4754,32 @@
         <f t="shared" si="6"/>
         <v>78.259940099466448</v>
       </c>
+      <c r="AB44">
+        <f t="shared" si="7"/>
+        <v>3.9787767271886918</v>
+      </c>
+      <c r="AC44">
+        <f t="shared" si="8"/>
+        <v>56.834822043922692</v>
+      </c>
+      <c r="AE44">
+        <f t="shared" si="9"/>
+        <v>20.451620646885456</v>
+      </c>
+      <c r="AF44">
+        <f t="shared" si="10"/>
+        <v>26.5748436967733</v>
+      </c>
+      <c r="AH44">
+        <f t="shared" si="11"/>
+        <v>4.1811554832796123</v>
+      </c>
+      <c r="AI44">
+        <f t="shared" si="12"/>
+        <v>51.889487668988501</v>
+      </c>
     </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>7</v>
       </c>
@@ -3787,8 +4853,32 @@
         <f t="shared" si="6"/>
         <v>103.65756131273389</v>
       </c>
+      <c r="AB45">
+        <f t="shared" si="7"/>
+        <v>4.7073043691195764</v>
+      </c>
+      <c r="AC45">
+        <f t="shared" si="8"/>
+        <v>3.2827402662356167</v>
+      </c>
+      <c r="AE45">
+        <f t="shared" si="9"/>
+        <v>22.333335491034482</v>
+      </c>
+      <c r="AF45">
+        <f t="shared" si="10"/>
+        <v>20.888416942912809</v>
+      </c>
+      <c r="AH45">
+        <f t="shared" si="11"/>
+        <v>5.8019507679737607</v>
+      </c>
+      <c r="AI45">
+        <f t="shared" si="12"/>
+        <v>6.6747577875257162</v>
+      </c>
     </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>7</v>
       </c>
@@ -3862,8 +4952,32 @@
         <f t="shared" si="6"/>
         <v>106.09356539094222</v>
       </c>
+      <c r="AB46">
+        <f t="shared" si="7"/>
+        <v>3.8844941859082596</v>
+      </c>
+      <c r="AC46">
+        <f t="shared" si="8"/>
+        <v>10.771184902682798</v>
+      </c>
+      <c r="AE46">
+        <f t="shared" si="9"/>
+        <v>19.789560674626031</v>
+      </c>
+      <c r="AF46">
+        <f t="shared" si="10"/>
+        <v>23.563948146673603</v>
+      </c>
+      <c r="AH46">
+        <f t="shared" si="11"/>
+        <v>4.5655778014917621</v>
+      </c>
+      <c r="AI46">
+        <f t="shared" si="12"/>
+        <v>5.9620710249514079</v>
+      </c>
     </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>7</v>
       </c>
@@ -3937,8 +5051,32 @@
         <f t="shared" si="6"/>
         <v>82.916953368222082</v>
       </c>
+      <c r="AB47">
+        <f t="shared" si="7"/>
+        <v>6.2759463050099438</v>
+      </c>
+      <c r="AC47">
+        <f t="shared" si="8"/>
+        <v>1.0075647763815918</v>
+      </c>
+      <c r="AE47">
+        <f t="shared" si="9"/>
+        <v>4.0719422161798065</v>
+      </c>
+      <c r="AF47">
+        <f t="shared" si="10"/>
+        <v>13.092856260937701</v>
+      </c>
+      <c r="AH47">
+        <f t="shared" si="11"/>
+        <v>5.8791881967495474</v>
+      </c>
+      <c r="AI47">
+        <f t="shared" si="12"/>
+        <v>1.2772511743737713</v>
+      </c>
     </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>7</v>
       </c>
@@ -4012,8 +5150,32 @@
         <f t="shared" si="6"/>
         <v>97.890403074605743</v>
       </c>
+      <c r="AB48">
+        <f t="shared" si="7"/>
+        <v>5.8006759119568931</v>
+      </c>
+      <c r="AC48">
+        <f t="shared" si="8"/>
+        <v>0.66094489918848365</v>
+      </c>
+      <c r="AE48">
+        <f t="shared" si="9"/>
+        <v>0.67198588246695701</v>
+      </c>
+      <c r="AF48">
+        <f t="shared" si="10"/>
+        <v>11.877117296741369</v>
+      </c>
+      <c r="AH48">
+        <f t="shared" si="11"/>
+        <v>6.0561739259893246</v>
+      </c>
+      <c r="AI48">
+        <f t="shared" si="12"/>
+        <v>2.3089283714804698</v>
+      </c>
     </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>7</v>
       </c>
@@ -4049,13 +5211,13 @@
         <v>6.78</v>
       </c>
       <c r="L49">
-        <v>53.814924410000003</v>
+        <v>19.72645</v>
       </c>
       <c r="M49">
-        <v>310.10436390000001</v>
+        <v>48.413511</v>
       </c>
       <c r="N49">
-        <v>7.3927227489999998</v>
+        <v>17.357689000000001</v>
       </c>
       <c r="P49">
         <v>25.117999999999999</v>
@@ -4086,6 +5248,56 @@
       <c r="Z49">
         <f t="shared" si="6"/>
         <v>50.379371363106422</v>
+      </c>
+      <c r="AB49">
+        <f>ABS(P49-L49)/P49*100</f>
+        <v>21.464885739310454</v>
+      </c>
+      <c r="AC49">
+        <f t="shared" si="8"/>
+        <v>1.8976474164133772</v>
+      </c>
+      <c r="AE49">
+        <f t="shared" si="9"/>
+        <v>53.038047591880002</v>
+      </c>
+      <c r="AF49">
+        <f t="shared" si="10"/>
+        <v>88.100589106752039</v>
+      </c>
+      <c r="AH49">
+        <f t="shared" si="11"/>
+        <v>44.213268359913485</v>
+      </c>
+      <c r="AI49">
+        <f t="shared" si="12"/>
+        <v>75.990361114161857</v>
+      </c>
+    </row>
+    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="AB50" s="2">
+        <f>AVERAGE(AB3:AB49)</f>
+        <v>8.4064847937735827</v>
+      </c>
+      <c r="AC50" s="2">
+        <f>AVERAGE(AC3:AC49)</f>
+        <v>15.722195570633666</v>
+      </c>
+      <c r="AE50" s="2">
+        <f>AVERAGE(AE3:AE49)</f>
+        <v>16.681261869728186</v>
+      </c>
+      <c r="AF50" s="2">
+        <f>AVERAGE(AF3:AF49)</f>
+        <v>26.901211649600484</v>
+      </c>
+      <c r="AH50" s="2">
+        <f>AVERAGE(AH3:AH49)</f>
+        <v>7.3697050497056269</v>
+      </c>
+      <c r="AI50" s="2">
+        <f>AVERAGE(AI3:AI49)</f>
+        <v>15.401631173038835</v>
       </c>
     </row>
   </sheetData>

--- a/data_contrast/experiment_data.xlsx
+++ b/data_contrast/experiment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\data_contrast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6250174C-49F5-4FBE-8A3D-073CEA3EFF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_2A211C1DD4FF011C744729514465B8B14E944051" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1365" yWindow="1425" windowWidth="21600" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="仿真数据" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,15 @@
   </si>
   <si>
     <t>模型预测值(未使用特征工程)</t>
+  </si>
+  <si>
+    <t>仿真值相对误差</t>
+  </si>
+  <si>
+    <t>使用特征工程相对误差</t>
+  </si>
+  <si>
+    <t>未使用特征工程相对误差</t>
   </si>
   <si>
     <t>N</t>
@@ -90,24 +99,10 @@
     <t>R[Ω]</t>
   </si>
   <si>
-    <t>仿真值相对误差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>L%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>R%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>使用特征工程相对误差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>未使用特征工程相对误差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -506,7 +501,7 @@
   <dimension ref="A1:AI50"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="15" max="15" width="8.625" customWidth="1"/>
+    <col min="15" max="15" width="8.625" style="1" customWidth="1"/>
     <col min="20" max="20" width="11.125" style="1" customWidth="1"/>
     <col min="21" max="21" width="10.125" style="1" customWidth="1"/>
     <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
@@ -526,99 +521,99 @@
         <v>3</v>
       </c>
       <c r="AB1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="AE1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="AH1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="N2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Q2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="R2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="U2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="X2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AB2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AC2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AF2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.2">
@@ -676,14 +671,14 @@
         <v>88.449435412259007</v>
       </c>
       <c r="T3">
-        <v>0.12408220767974849</v>
+        <v>0.14365708827972409</v>
       </c>
       <c r="U3">
-        <v>7.6971098780632019E-2</v>
+        <v>7.6557964086532593E-2</v>
       </c>
       <c r="V3">
-        <f>6780000*2*3.1415926*T3*0.000001/U3</f>
-        <v>68.673847611413464</v>
+        <f t="shared" ref="V3:V49" si="5">6780000*2*3.1415926*T3*0.000001/U3</f>
+        <v>79.936704295750673</v>
       </c>
       <c r="X3">
         <v>0.1031891107559204</v>
@@ -692,31 +687,31 @@
         <v>7.0287048816680908E-2</v>
       </c>
       <c r="Z3">
-        <f>6780000*2*3.1415926*X3*0.000001/Y3</f>
+        <f t="shared" ref="Z3:Z49" si="6">6780000*2*3.1415926*X3*0.000001/Y3</f>
         <v>62.541474481504522</v>
       </c>
       <c r="AB3">
-        <f>ABS(P3-L3)/P3*100</f>
+        <f t="shared" ref="AB3:AB49" si="7">ABS(P3-L3)/P3*100</f>
         <v>16.775700934579447</v>
       </c>
       <c r="AC3">
-        <f>ABS(Q3-M3)/Q3*100</f>
+        <f t="shared" ref="AC3:AC49" si="8">ABS(Q3-M3)/Q3*100</f>
         <v>8.4790593453302225</v>
       </c>
       <c r="AE3">
-        <f>ABS(P3-T3)/P3*100</f>
-        <v>30.973404717540891</v>
+        <f t="shared" ref="AE3:AE49" si="9">ABS(P3-T3)/P3*100</f>
+        <v>20.083951780304801</v>
       </c>
       <c r="AF3">
-        <f>ABS(Q3-U3)/Q3*100</f>
-        <v>11.096238327713719</v>
+        <f t="shared" ref="AF3:AF49" si="10">ABS(Q3-U3)/Q3*100</f>
+        <v>11.573420399486485</v>
       </c>
       <c r="AH3">
-        <f>ABS(P3-X3)/P3*100</f>
+        <f t="shared" ref="AH3:AH49" si="11">ABS(P3-X3)/P3*100</f>
         <v>42.596177817133736</v>
       </c>
       <c r="AI3">
-        <f>ABS(Q3-Y3)/Q3*100</f>
+        <f t="shared" ref="AI3:AI49" si="12">ABS(Q3-Y3)/Q3*100</f>
         <v>18.816502094434028</v>
       </c>
     </row>
@@ -775,14 +770,14 @@
         <v>67.919679029324811</v>
       </c>
       <c r="T4">
-        <v>0.16146913170814511</v>
+        <v>0.16669690608978269</v>
       </c>
       <c r="U4">
-        <v>8.6934715509414673E-2</v>
+        <v>0.10713550448417659</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V4:V49" si="5">6780000*2*3.1415926*T4*0.000001/U4</f>
-        <v>79.123561502886048</v>
+        <f t="shared" si="5"/>
+        <v>66.283231777213587</v>
       </c>
       <c r="X4">
         <v>0.17454767227172849</v>
@@ -791,31 +786,31 @@
         <v>0.12292706966400151</v>
       </c>
       <c r="Z4">
-        <f t="shared" ref="Z4:Z49" si="6">6780000*2*3.1415926*X4*0.000001/Y4</f>
+        <f t="shared" si="6"/>
         <v>60.488955775686705</v>
       </c>
       <c r="AB4">
-        <f t="shared" ref="AB4:AB48" si="7">ABS(P4-L4)/P4*100</f>
+        <f t="shared" si="7"/>
         <v>28.588364034287789</v>
       </c>
       <c r="AC4">
-        <f t="shared" ref="AC4:AC49" si="8">ABS(Q4-M4)/Q4*100</f>
+        <f t="shared" si="8"/>
         <v>18.069933120093047</v>
       </c>
       <c r="AE4">
-        <f t="shared" ref="AE4:AE49" si="9">ABS(P4-T4)/P4*100</f>
-        <v>26.377379305058763</v>
+        <f t="shared" si="9"/>
+        <v>23.993750642995305</v>
       </c>
       <c r="AF4">
-        <f t="shared" ref="AF4:AF49" si="10">ABS(Q4-U4)/Q4*100</f>
-        <v>36.802329522088776</v>
+        <f t="shared" si="10"/>
+        <v>22.117254664018169</v>
       </c>
       <c r="AH4">
-        <f t="shared" ref="AH4:AH49" si="11">ABS(P4-X4)/P4*100</f>
+        <f t="shared" si="11"/>
         <v>20.414156359780915</v>
       </c>
       <c r="AI4">
-        <f t="shared" ref="AI4:AI49" si="12">ABS(Q4-Y4)/Q4*100</f>
+        <f t="shared" si="12"/>
         <v>10.637489339923293</v>
       </c>
     </row>
@@ -874,14 +869,14 @@
         <v>81.995395457907264</v>
       </c>
       <c r="T5">
-        <v>0.1689397990703583</v>
+        <v>0.19339227676391599</v>
       </c>
       <c r="U5">
-        <v>8.8925570249557495E-2</v>
+        <v>0.1083044707775116</v>
       </c>
       <c r="V5">
         <f t="shared" si="5"/>
-        <v>80.9309930352523</v>
+        <v>76.068052324183654</v>
       </c>
       <c r="X5">
         <v>0.1994786262512207</v>
@@ -903,11 +898,11 @@
       </c>
       <c r="AE5">
         <f t="shared" si="9"/>
-        <v>27.443824484470746</v>
+        <v>16.941987302905002</v>
       </c>
       <c r="AF5">
         <f t="shared" si="10"/>
-        <v>26.489567455106638</v>
+        <v>10.469975384383234</v>
       </c>
       <c r="AH5">
         <f t="shared" si="11"/>
@@ -973,14 +968,14 @@
         <v>106.26082868762136</v>
       </c>
       <c r="T6">
-        <v>0.19643175601959231</v>
+        <v>0.2295880317687988</v>
       </c>
       <c r="U6">
-        <v>9.6252202987670898E-2</v>
+        <v>8.4868520498275757E-2</v>
       </c>
       <c r="V6">
         <f t="shared" si="5"/>
-        <v>86.938186279299558</v>
+        <v>115.24236664664285</v>
       </c>
       <c r="X6">
         <v>0.21352458000183111</v>
@@ -1002,11 +997,11 @@
       </c>
       <c r="AE6">
         <f t="shared" si="9"/>
-        <v>19.980545861336033</v>
+        <v>6.4738342150892958</v>
       </c>
       <c r="AF6">
         <f t="shared" si="10"/>
-        <v>2.1956418484642293</v>
+        <v>13.762896671907415</v>
       </c>
       <c r="AH6">
         <f t="shared" si="11"/>
@@ -1072,14 +1067,14 @@
         <v>82.09108586752015</v>
       </c>
       <c r="T7">
-        <v>0.38469091057777399</v>
+        <v>0.40876591205596918</v>
       </c>
       <c r="U7">
-        <v>0.18547867238521579</v>
+        <v>0.1874705255031586</v>
       </c>
       <c r="V7">
         <f t="shared" si="5"/>
-        <v>88.354261483392563</v>
+        <v>92.886207211339865</v>
       </c>
       <c r="X7">
         <v>0.40105938911437988</v>
@@ -1101,11 +1096,11 @@
       </c>
       <c r="AE7">
         <f t="shared" si="9"/>
-        <v>10.839727766705144</v>
+        <v>5.2598358930215614</v>
       </c>
       <c r="AF7">
         <f t="shared" si="10"/>
-        <v>17.16003913121224</v>
+        <v>16.270421838696471</v>
       </c>
       <c r="AH7">
         <f t="shared" si="11"/>
@@ -1171,14 +1166,14 @@
         <v>126.57336980166569</v>
       </c>
       <c r="T8">
-        <v>0.35672712326049799</v>
+        <v>0.37442409992218018</v>
       </c>
       <c r="U8">
-        <v>0.14150333404541021</v>
+        <v>0.122841864824295</v>
       </c>
       <c r="V8">
         <f t="shared" si="5"/>
-        <v>107.39375155922346</v>
+        <v>129.84551360402327</v>
       </c>
       <c r="X8">
         <v>0.36836838722228998</v>
@@ -1200,11 +1195,11 @@
       </c>
       <c r="AE8">
         <f t="shared" si="9"/>
-        <v>9.2643715476286435</v>
+        <v>4.7630421156860798</v>
       </c>
       <c r="AF8">
         <f t="shared" si="10"/>
-        <v>6.9402464067489564</v>
+        <v>7.1630404894989352</v>
       </c>
       <c r="AH8">
         <f t="shared" si="11"/>
@@ -1270,14 +1265,14 @@
         <v>136.99878560125703</v>
       </c>
       <c r="T9">
-        <v>0.40904849767684942</v>
+        <v>0.42978405952453608</v>
       </c>
       <c r="U9">
-        <v>0.15694709122180939</v>
+        <v>0.13765373826026919</v>
       </c>
       <c r="V9">
         <f t="shared" si="5"/>
-        <v>111.02763414391758</v>
+        <v>133.00618857256072</v>
       </c>
       <c r="X9">
         <v>0.43056869506835938</v>
@@ -1299,11 +1294,11 @@
       </c>
       <c r="AE9">
         <f t="shared" si="9"/>
-        <v>9.1144715984514857</v>
+        <v>4.5072856390036993</v>
       </c>
       <c r="AF9">
         <f t="shared" si="10"/>
-        <v>12.145116985930258</v>
+        <v>1.6407729472888877</v>
       </c>
       <c r="AH9">
         <f t="shared" si="11"/>
@@ -1369,14 +1364,14 @@
         <v>106.23927183097523</v>
       </c>
       <c r="T10">
-        <v>0.46865791082382202</v>
+        <v>0.5143207311630249</v>
       </c>
       <c r="U10">
-        <v>0.213797852396965</v>
+        <v>0.2056942284107208</v>
       </c>
       <c r="V10">
         <f t="shared" si="5"/>
-        <v>93.381784435212921</v>
+        <v>106.51762610269552</v>
       </c>
       <c r="X10">
         <v>0.48204529285430908</v>
@@ -1398,11 +1393,11 @@
       </c>
       <c r="AE10">
         <f t="shared" si="9"/>
-        <v>10.843908453406764</v>
+        <v>2.1571488865378976</v>
       </c>
       <c r="AF10">
         <f t="shared" si="10"/>
-        <v>1.4317546242361723</v>
+        <v>2.4128340398895518</v>
       </c>
       <c r="AH10">
         <f t="shared" si="11"/>
@@ -1468,14 +1463,14 @@
         <v>87.101060954697189</v>
       </c>
       <c r="T11">
-        <v>0.36116534471511841</v>
+        <v>0.37351810932159418</v>
       </c>
       <c r="U11">
-        <v>0.2251284122467041</v>
+        <v>0.18922886252403259</v>
       </c>
       <c r="V11">
         <f t="shared" si="5"/>
-        <v>68.341627617848729</v>
+        <v>84.087964289889413</v>
       </c>
       <c r="X11">
         <v>0.38369858264923101</v>
@@ -1497,11 +1492,11 @@
       </c>
       <c r="AE11">
         <f t="shared" si="9"/>
-        <v>12.510514591429859</v>
+        <v>9.5181537943377883</v>
       </c>
       <c r="AF11">
         <f t="shared" si="10"/>
-        <v>11.504909483261072</v>
+        <v>6.2759472392111952</v>
       </c>
       <c r="AH11">
         <f t="shared" si="11"/>
@@ -1567,14 +1562,14 @@
         <v>106.34825883698332</v>
       </c>
       <c r="T12">
-        <v>0.50276118516921997</v>
+        <v>0.49118733406066889</v>
       </c>
       <c r="U12">
-        <v>0.22522106766700739</v>
+        <v>0.2012996971607208</v>
       </c>
       <c r="V12">
         <f t="shared" si="5"/>
-        <v>95.096007341020382</v>
+        <v>103.94739084262113</v>
       </c>
       <c r="X12">
         <v>0.48176538944244379</v>
@@ -1596,11 +1591,11 @@
       </c>
       <c r="AE12">
         <f t="shared" si="9"/>
-        <v>7.44455354027615</v>
+        <v>9.5752330521596338</v>
       </c>
       <c r="AF12">
         <f t="shared" si="10"/>
-        <v>3.5070856505388051</v>
+        <v>7.4866964654989694</v>
       </c>
       <c r="AH12">
         <f t="shared" si="11"/>
@@ -1666,14 +1661,14 @@
         <v>111.11416589715785</v>
       </c>
       <c r="T13">
-        <v>0.4650338888168335</v>
+        <v>0.48977816104888922</v>
       </c>
       <c r="U13">
-        <v>0.17284254729747769</v>
+        <v>0.18722787499427801</v>
       </c>
       <c r="V13">
         <f t="shared" si="5"/>
-        <v>114.61553855367758</v>
+        <v>111.43932244984357</v>
       </c>
       <c r="X13">
         <v>0.49842798709869379</v>
@@ -1695,11 +1690,11 @@
       </c>
       <c r="AE13">
         <f t="shared" si="9"/>
-        <v>12.081920668349241</v>
+        <v>7.4038338849606298</v>
       </c>
       <c r="AF13">
         <f t="shared" si="10"/>
-        <v>14.767716703250802</v>
+        <v>7.6740100624892689</v>
       </c>
       <c r="AH13">
         <f t="shared" si="11"/>
@@ -1765,14 +1760,14 @@
         <v>124.72617713017445</v>
       </c>
       <c r="T14">
-        <v>0.49436432123184199</v>
+        <v>0.51784181594848633</v>
       </c>
       <c r="U14">
-        <v>0.18015462160110471</v>
+        <v>0.17745104432106021</v>
       </c>
       <c r="V14">
         <f t="shared" si="5"/>
-        <v>116.89912670455033</v>
+        <v>124.31631041848168</v>
       </c>
       <c r="X14">
         <v>0.51373791694641113</v>
@@ -1794,11 +1789,11 @@
       </c>
       <c r="AE14">
         <f t="shared" si="9"/>
-        <v>11.005522730541497</v>
+        <v>6.7791510443768983</v>
       </c>
       <c r="AF14">
         <f t="shared" si="10"/>
-        <v>5.046844673428188</v>
+        <v>6.4718050276391716</v>
       </c>
       <c r="AH14">
         <f t="shared" si="11"/>
@@ -1864,14 +1859,14 @@
         <v>134.00409276942264</v>
       </c>
       <c r="T15">
-        <v>0.58772408962249756</v>
+        <v>0.62052249908447266</v>
       </c>
       <c r="U15">
-        <v>0.20158037543296811</v>
+        <v>0.19075724482536319</v>
       </c>
       <c r="V15">
         <f t="shared" si="5"/>
-        <v>124.20377534801528</v>
+        <v>138.57536991399283</v>
       </c>
       <c r="X15">
         <v>0.59992742538452148</v>
@@ -1893,11 +1888,11 @@
       </c>
       <c r="AE15">
         <f t="shared" si="9"/>
-        <v>8.4442089289334419</v>
+        <v>3.3348653148360947</v>
       </c>
       <c r="AF15">
         <f t="shared" si="10"/>
-        <v>1.2199855770235162</v>
+        <v>6.5236218820193148</v>
       </c>
       <c r="AH15">
         <f t="shared" si="11"/>
@@ -1963,14 +1958,14 @@
         <v>145.98553133207395</v>
       </c>
       <c r="T16">
-        <v>0.70015197992324829</v>
+        <v>0.76420497894287109</v>
       </c>
       <c r="U16">
-        <v>0.2239689230918884</v>
+        <v>0.2232156693935394</v>
       </c>
       <c r="V16">
         <f t="shared" si="5"/>
-        <v>133.17236557427739</v>
+        <v>145.84607286625433</v>
       </c>
       <c r="X16">
         <v>0.76006722450256348</v>
@@ -1992,11 +1987,11 @@
       </c>
       <c r="AE16">
         <f t="shared" si="9"/>
-        <v>9.6368214652114901</v>
+        <v>1.3699983295641387</v>
       </c>
       <c r="AF16">
         <f t="shared" si="10"/>
-        <v>0.94253733220327085</v>
+        <v>1.2756880170104354</v>
       </c>
       <c r="AH16">
         <f t="shared" si="11"/>
@@ -2062,14 +2057,14 @@
         <v>150.44431949239907</v>
       </c>
       <c r="T17">
-        <v>1.0431568622589109</v>
+        <v>0.95735752582550049</v>
       </c>
       <c r="U17">
-        <v>0.30557018518447882</v>
+        <v>0.28461423516273499</v>
       </c>
       <c r="V17">
         <f t="shared" si="5"/>
-        <v>145.42805533834331</v>
+        <v>143.29369863768875</v>
       </c>
       <c r="X17">
         <v>0.92759287357330322</v>
@@ -2091,11 +2086,11 @@
       </c>
       <c r="AE17">
         <f t="shared" si="9"/>
-        <v>6.3479964378177849</v>
+        <v>2.399094105812023</v>
       </c>
       <c r="AF17">
         <f t="shared" si="10"/>
-        <v>10.0162682932417</v>
+        <v>2.4713717957641723</v>
       </c>
       <c r="AH17">
         <f t="shared" si="11"/>
@@ -2161,14 +2156,14 @@
         <v>194.56703501335093</v>
       </c>
       <c r="T18">
-        <v>1.1460273265838621</v>
+        <v>1.084038257598877</v>
       </c>
       <c r="U18">
-        <v>0.31722116470336909</v>
+        <v>0.28206855058670038</v>
       </c>
       <c r="V18">
         <f t="shared" si="5"/>
-        <v>153.9013299436742</v>
+        <v>163.71915610086936</v>
       </c>
       <c r="X18">
         <v>1.05478823184967</v>
@@ -2190,11 +2185,11 @@
       </c>
       <c r="AE18">
         <f t="shared" si="9"/>
-        <v>3.2550073505596875</v>
+        <v>2.3300966214184298</v>
       </c>
       <c r="AF18">
         <f t="shared" si="10"/>
-        <v>30.53831723113003</v>
+        <v>16.07281617493123</v>
       </c>
       <c r="AH18">
         <f t="shared" si="11"/>
@@ -2260,14 +2255,14 @@
         <v>104.00971088235249</v>
       </c>
       <c r="T19">
-        <v>0.63737165927886963</v>
+        <v>0.59301352500915527</v>
       </c>
       <c r="U19">
-        <v>0.42281004786491388</v>
+        <v>0.30579870939254761</v>
       </c>
       <c r="V19">
         <f t="shared" si="5"/>
-        <v>64.218033733229362</v>
+        <v>82.61111905776707</v>
       </c>
       <c r="X19">
         <v>0.62943422794342041</v>
@@ -2289,11 +2284,11 @@
       </c>
       <c r="AE19">
         <f t="shared" si="9"/>
-        <v>1.4820608261917816</v>
+        <v>8.3384560082299846</v>
       </c>
       <c r="AF19">
         <f t="shared" si="10"/>
-        <v>59.563003949322166</v>
+        <v>15.404449163162356</v>
       </c>
       <c r="AH19">
         <f t="shared" si="11"/>
@@ -2359,14 +2354,14 @@
         <v>109.36374157525063</v>
       </c>
       <c r="T20">
-        <v>0.47585126757621771</v>
+        <v>0.47331809997558588</v>
       </c>
       <c r="U20">
-        <v>0.32726007699966431</v>
+        <v>0.25629210472106928</v>
       </c>
       <c r="V20">
         <f t="shared" si="5"/>
-        <v>61.942361309380743</v>
+        <v>78.673313112046657</v>
       </c>
       <c r="X20">
         <v>0.51356363296508789</v>
@@ -2388,11 +2383,11 @@
       </c>
       <c r="AE20">
         <f t="shared" si="9"/>
-        <v>10.13026354110225</v>
+        <v>10.608680055225619</v>
       </c>
       <c r="AF20">
         <f t="shared" si="10"/>
-        <v>58.671552484685726</v>
+        <v>24.262838652639658</v>
       </c>
       <c r="AH20">
         <f t="shared" si="11"/>
@@ -2458,14 +2453,14 @@
         <v>104.2199582569137</v>
       </c>
       <c r="T21">
-        <v>0.79386031627655029</v>
+        <v>0.74426186084747314</v>
       </c>
       <c r="U21">
-        <v>0.42268052697181702</v>
+        <v>0.28875857591629028</v>
       </c>
       <c r="V21">
         <f t="shared" si="5"/>
-        <v>80.009472561073849</v>
+        <v>109.7995165629994</v>
       </c>
       <c r="X21">
         <v>0.77157771587371826</v>
@@ -2487,11 +2482,11 @@
       </c>
       <c r="AE21">
         <f t="shared" si="9"/>
-        <v>1.0124546401967298</v>
+        <v>7.1969549306125939</v>
       </c>
       <c r="AF21">
         <f t="shared" si="10"/>
-        <v>28.940705583056353</v>
+        <v>11.912822697205609</v>
       </c>
       <c r="AH21">
         <f t="shared" si="11"/>
@@ -2557,14 +2552,14 @@
         <v>130.96725692891812</v>
       </c>
       <c r="T22">
-        <v>0.97864878177642822</v>
+        <v>0.85266649723052979</v>
       </c>
       <c r="U22">
-        <v>0.46412968635559082</v>
+        <v>0.30265414714813232</v>
       </c>
       <c r="V22">
         <f t="shared" si="5"/>
-        <v>89.824967197820229</v>
+        <v>120.01682256896</v>
       </c>
       <c r="X22">
         <v>0.89939093589782715</v>
@@ -2586,11 +2581,11 @@
       </c>
       <c r="AE22">
         <f t="shared" si="9"/>
-        <v>6.9468004738851477</v>
+        <v>6.8205515112853758</v>
       </c>
       <c r="AF22">
         <f t="shared" si="10"/>
-        <v>55.931357754272057</v>
+        <v>1.6812185950385681</v>
       </c>
       <c r="AH22">
         <f t="shared" si="11"/>
@@ -2656,14 +2651,14 @@
         <v>126.30219274150836</v>
       </c>
       <c r="T23">
-        <v>1.1072015762329099</v>
+        <v>0.93915039300918579</v>
       </c>
       <c r="U23">
-        <v>0.46378690004348749</v>
+        <v>0.32639533281326288</v>
       </c>
       <c r="V23">
         <f t="shared" si="5"/>
-        <v>101.69925526877898</v>
+        <v>122.57467751663978</v>
       </c>
       <c r="X23">
         <v>0.97504770755767822</v>
@@ -2685,11 +2680,11 @@
       </c>
       <c r="AE23">
         <f t="shared" si="9"/>
-        <v>10.709086714619533</v>
+        <v>6.0943512639550246</v>
       </c>
       <c r="AF23">
         <f t="shared" si="10"/>
-        <v>37.491669644102778</v>
+        <v>3.2386657140807316</v>
       </c>
       <c r="AH23">
         <f t="shared" si="11"/>
@@ -2755,14 +2750,14 @@
         <v>117.97405195907693</v>
       </c>
       <c r="T24">
-        <v>1.042928218841553</v>
+        <v>0.91595757007598877</v>
       </c>
       <c r="U24">
-        <v>0.4536978006362915</v>
+        <v>0.31739947199821472</v>
       </c>
       <c r="V24">
         <f t="shared" si="5"/>
-        <v>97.925838586523</v>
+        <v>122.93589608282936</v>
       </c>
       <c r="X24">
         <v>0.94797658920288086</v>
@@ -2784,11 +2779,11 @@
       </c>
       <c r="AE24">
         <f t="shared" si="9"/>
-        <v>6.8179993897284765</v>
+        <v>6.186491655128358</v>
       </c>
       <c r="AF24">
         <f t="shared" si="10"/>
-        <v>28.686691807434627</v>
+        <v>9.9729203544886715</v>
       </c>
       <c r="AH24">
         <f t="shared" si="11"/>
@@ -2854,14 +2849,14 @@
         <v>130.83566673849759</v>
       </c>
       <c r="T25">
-        <v>1.428875327110291</v>
+        <v>1.2249991893768311</v>
       </c>
       <c r="U25">
-        <v>0.52277225255966187</v>
+        <v>0.37215840816497803</v>
       </c>
       <c r="V25">
         <f t="shared" si="5"/>
-        <v>116.43709556087644</v>
+        <v>140.22244023282394</v>
       </c>
       <c r="X25">
         <v>1.2423417568206789</v>
@@ -2883,11 +2878,11 @@
       </c>
       <c r="AE25">
         <f t="shared" si="9"/>
-        <v>10.842861462283071</v>
+        <v>4.9725242900604192</v>
       </c>
       <c r="AF25">
         <f t="shared" si="10"/>
-        <v>24.549651575932593</v>
+        <v>11.333855534515514</v>
       </c>
       <c r="AH25">
         <f t="shared" si="11"/>
@@ -2953,14 +2948,14 @@
         <v>107.35538368975843</v>
       </c>
       <c r="T26">
-        <v>1.999053478240967</v>
+        <v>1.455916166305542</v>
       </c>
       <c r="U26">
-        <v>0.89127510786056519</v>
+        <v>0.52590095996856689</v>
       </c>
       <c r="V26">
         <f t="shared" si="5"/>
-        <v>95.548129570897459</v>
+        <v>117.93479586693152</v>
       </c>
       <c r="X26">
         <v>1.546310186386108</v>
@@ -2982,11 +2977,11 @@
       </c>
       <c r="AE26">
         <f t="shared" si="9"/>
-        <v>25.419002336468218</v>
+        <v>8.6569943970423537</v>
       </c>
       <c r="AF26">
         <f t="shared" si="10"/>
-        <v>40.917516421161956</v>
+        <v>16.850973948809944</v>
       </c>
       <c r="AH26">
         <f t="shared" si="11"/>
@@ -3052,14 +3047,14 @@
         <v>97.429935119835179</v>
       </c>
       <c r="T27">
-        <v>1.828563451766968</v>
+        <v>1.349621176719666</v>
       </c>
       <c r="U27">
-        <v>0.78356689214706421</v>
+        <v>0.47454282641410828</v>
       </c>
       <c r="V27">
         <f t="shared" si="5"/>
-        <v>99.413076130037794</v>
+        <v>121.15630679733751</v>
       </c>
       <c r="X27">
         <v>1.3802802562713621</v>
@@ -3081,11 +3076,11 @@
       </c>
       <c r="AE27">
         <f t="shared" si="9"/>
-        <v>24.799580382675941</v>
+        <v>7.8882625771453787</v>
       </c>
       <c r="AF27">
         <f t="shared" si="10"/>
-        <v>22.310016881097688</v>
+        <v>25.926756616179404</v>
       </c>
       <c r="AH27">
         <f t="shared" si="11"/>
@@ -3151,14 +3146,14 @@
         <v>124.57159008466202</v>
       </c>
       <c r="T28">
-        <v>2.899238109588623</v>
+        <v>2.1215798854827881</v>
       </c>
       <c r="U28">
-        <v>1.037422895431519</v>
+        <v>0.70574367046356201</v>
       </c>
       <c r="V28">
         <f t="shared" si="5"/>
-        <v>119.05225093650134</v>
+        <v>128.06249306643988</v>
       </c>
       <c r="X28">
         <v>2.234885692596436</v>
@@ -3180,11 +3175,11 @@
       </c>
       <c r="AE28">
         <f t="shared" si="9"/>
-        <v>23.377084539283508</v>
+        <v>9.7161630076689143</v>
       </c>
       <c r="AF28">
         <f t="shared" si="10"/>
-        <v>29.096925763006347</v>
+        <v>12.177243595873316</v>
       </c>
       <c r="AH28">
         <f t="shared" si="11"/>
@@ -3250,14 +3245,14 @@
         <v>161.12589949719245</v>
       </c>
       <c r="T29">
-        <v>2.488350629806519</v>
+        <v>1.778931736946106</v>
       </c>
       <c r="U29">
-        <v>0.75081330537796021</v>
+        <v>0.51291394233703613</v>
       </c>
       <c r="V29">
         <f t="shared" si="5"/>
-        <v>141.18519911817518</v>
+        <v>147.74892630317294</v>
       </c>
       <c r="X29">
         <v>1.856438040733337</v>
@@ -3279,11 +3274,11 @@
       </c>
       <c r="AE29">
         <f t="shared" si="9"/>
-        <v>26.859578374025951</v>
+        <v>9.3075841475347474</v>
       </c>
       <c r="AF29">
         <f t="shared" si="10"/>
-        <v>44.776958229456284</v>
+        <v>1.0964245397153525</v>
       </c>
       <c r="AH29">
         <f t="shared" si="11"/>
@@ -3349,14 +3344,14 @@
         <v>141.60345063636763</v>
       </c>
       <c r="T30">
-        <v>3.400421142578125</v>
+        <v>2.5824847221374512</v>
       </c>
       <c r="U30">
-        <v>1.117282390594482</v>
+        <v>0.79586935043334961</v>
       </c>
       <c r="V30">
         <f t="shared" si="5"/>
-        <v>129.65202631120223</v>
+        <v>138.23102734744018</v>
       </c>
       <c r="X30">
         <v>2.7297852039337158</v>
@@ -3378,11 +3373,11 @@
       </c>
       <c r="AE30">
         <f t="shared" si="9"/>
-        <v>21.560831608269584</v>
+        <v>7.679379325154569</v>
       </c>
       <c r="AF30">
         <f t="shared" si="10"/>
-        <v>32.766403331330892</v>
+        <v>5.4270325316265833</v>
       </c>
       <c r="AH30">
         <f t="shared" si="11"/>
@@ -3448,14 +3443,14 @@
         <v>84.076232483520172</v>
       </c>
       <c r="T31">
-        <v>4.8900747299194336</v>
+        <v>3.9553132057189941</v>
       </c>
       <c r="U31">
-        <v>1.8915525674819951</v>
+        <v>1.532555937767029</v>
       </c>
       <c r="V31">
         <f t="shared" si="5"/>
-        <v>110.13025269997745</v>
+        <v>109.94464947703756</v>
       </c>
       <c r="X31">
         <v>4.2812275886535636</v>
@@ -3477,11 +3472,11 @@
       </c>
       <c r="AE31">
         <f t="shared" si="9"/>
-        <v>8.7529129304889004</v>
+        <v>12.035734332947982</v>
       </c>
       <c r="AF31">
         <f t="shared" si="10"/>
-        <v>16.975263684238474</v>
+        <v>32.732478700477159</v>
       </c>
       <c r="AH31">
         <f t="shared" si="11"/>
@@ -3547,14 +3542,14 @@
         <v>148.38157874051376</v>
       </c>
       <c r="T32">
-        <v>4.3625879287719727</v>
+        <v>3.3243036270141602</v>
       </c>
       <c r="U32">
-        <v>1.395170927047729</v>
+        <v>1.0086877346038821</v>
       </c>
       <c r="V32">
         <f t="shared" si="5"/>
-        <v>133.2067800522955</v>
+        <v>140.39560035459488</v>
       </c>
       <c r="X32">
         <v>3.3504526615142818</v>
@@ -3576,11 +3571,11 @@
       </c>
       <c r="AE32">
         <f t="shared" si="9"/>
-        <v>24.61332596680775</v>
+        <v>5.0443135475403462</v>
       </c>
       <c r="AF32">
         <f t="shared" si="10"/>
-        <v>38.80916595838513</v>
+        <v>0.35695300008774783</v>
       </c>
       <c r="AH32">
         <f t="shared" si="11"/>
@@ -3646,14 +3641,14 @@
         <v>135.64147033128543</v>
       </c>
       <c r="T33">
-        <v>4.344942569732666</v>
+        <v>3.1530828475952148</v>
       </c>
       <c r="U33">
-        <v>1.4827631711959841</v>
+        <v>0.97443211078643799</v>
       </c>
       <c r="V33">
         <f t="shared" si="5"/>
-        <v>124.83081465186743</v>
+        <v>137.84574022520371</v>
       </c>
       <c r="X33">
         <v>3.031828880310059</v>
@@ -3675,11 +3670,11 @@
       </c>
       <c r="AE33">
         <f t="shared" si="9"/>
-        <v>23.492001186126245</v>
+        <v>10.38304776048162</v>
       </c>
       <c r="AF33">
         <f t="shared" si="10"/>
-        <v>34.186712325428424</v>
+        <v>11.816098571363076</v>
       </c>
       <c r="AH33">
         <f t="shared" si="11"/>
@@ -3745,14 +3740,14 @@
         <v>91.084828507187908</v>
       </c>
       <c r="T34">
-        <v>4.2311654090881348</v>
+        <v>3.137900829315186</v>
       </c>
       <c r="U34">
-        <v>1.8176496028900151</v>
+        <v>1.143624901771545</v>
       </c>
       <c r="V34">
         <f t="shared" si="5"/>
-        <v>99.165222912261541</v>
+        <v>116.88671826812764</v>
       </c>
       <c r="X34">
         <v>3.2388663291931148</v>
@@ -3774,11 +3769,11 @@
       </c>
       <c r="AE34">
         <f t="shared" si="9"/>
-        <v>24.655021921696225</v>
+        <v>7.5538158290314321</v>
       </c>
       <c r="AF34">
         <f t="shared" si="10"/>
-        <v>14.497612780473398</v>
+        <v>27.960636108879054</v>
       </c>
       <c r="AH34">
         <f t="shared" si="11"/>
@@ -3844,14 +3839,14 @@
         <v>94.4561902306083</v>
       </c>
       <c r="T35">
-        <v>3.729662179946899</v>
+        <v>2.5194187164306641</v>
       </c>
       <c r="U35">
-        <v>1.5458499193191531</v>
+        <v>0.88799715042114258</v>
       </c>
       <c r="V35">
         <f t="shared" si="5"/>
-        <v>102.78073613644416</v>
+        <v>120.864381518218</v>
       </c>
       <c r="X35">
         <v>2.78761887550354</v>
@@ -3873,11 +3868,11 @@
       </c>
       <c r="AE35">
         <f t="shared" si="9"/>
-        <v>28.511549167765793</v>
+        <v>13.189348892885949</v>
       </c>
       <c r="AF35">
         <f t="shared" si="10"/>
-        <v>18.102981077175727</v>
+        <v>32.156990570620927</v>
       </c>
       <c r="AH35">
         <f t="shared" si="11"/>
@@ -3943,14 +3938,14 @@
         <v>98.027871854575253</v>
       </c>
       <c r="T36">
-        <v>3.4584255218505859</v>
+        <v>2.3340740203857422</v>
       </c>
       <c r="U36">
-        <v>1.3760194778442381</v>
+        <v>0.77784013748168945</v>
       </c>
       <c r="V36">
         <f t="shared" si="5"/>
-        <v>107.06891477891692</v>
+        <v>127.83030643177078</v>
       </c>
       <c r="X36">
         <v>2.571627140045166</v>
@@ -3972,11 +3967,11 @@
       </c>
       <c r="AE36">
         <f t="shared" si="9"/>
-        <v>30.951363947390607</v>
+        <v>11.62158196191813</v>
       </c>
       <c r="AF36">
         <f t="shared" si="10"/>
-        <v>19.893654948526454</v>
+        <v>32.226179534574413</v>
       </c>
       <c r="AH36">
         <f t="shared" si="11"/>
@@ -4042,14 +4037,14 @@
         <v>75.980708729842561</v>
       </c>
       <c r="T37">
-        <v>5.6507425308227539</v>
+        <v>5.1830391883850098</v>
       </c>
       <c r="U37">
-        <v>2.348324060440063</v>
+        <v>2.141948938369751</v>
       </c>
       <c r="V37">
         <f t="shared" si="5"/>
-        <v>102.50783157291923</v>
+        <v>103.08249788537412</v>
       </c>
       <c r="X37">
         <v>5.4126324653625488</v>
@@ -4071,11 +4066,11 @@
       </c>
       <c r="AE37">
         <f t="shared" si="9"/>
-        <v>0.78932298360599262</v>
+        <v>9.0008394335198592</v>
       </c>
       <c r="AF37">
         <f t="shared" si="10"/>
-        <v>26.463203468401609</v>
+        <v>32.925755045727094</v>
       </c>
       <c r="AH37">
         <f t="shared" si="11"/>
@@ -4141,14 +4136,14 @@
         <v>149.61301959775122</v>
       </c>
       <c r="T38">
-        <v>3.788763284683228</v>
+        <v>2.9570603370666499</v>
       </c>
       <c r="U38">
-        <v>1.2012449502944951</v>
+        <v>0.84034085273742676</v>
       </c>
       <c r="V38">
         <f t="shared" si="5"/>
-        <v>134.3616882048486</v>
+        <v>149.90435976451337</v>
       </c>
       <c r="X38">
         <v>2.935302734375</v>
@@ -4170,11 +4165,11 @@
       </c>
       <c r="AE38">
         <f t="shared" si="9"/>
-        <v>22.277336927004292</v>
+        <v>4.5647785358512207</v>
       </c>
       <c r="AF38">
         <f t="shared" si="10"/>
-        <v>36.156979347633332</v>
+        <v>4.7502575531394982</v>
       </c>
       <c r="AH38">
         <f t="shared" si="11"/>
@@ -4240,14 +4235,14 @@
         <v>87.829154013435073</v>
       </c>
       <c r="T39">
-        <v>6.186798095703125</v>
+        <v>5.6930708885192871</v>
       </c>
       <c r="U39">
-        <v>2.3957376480102539</v>
+        <v>2.255557775497437</v>
       </c>
       <c r="V39">
         <f t="shared" si="5"/>
-        <v>110.01103239346604</v>
+        <v>107.52320235589428</v>
       </c>
       <c r="X39">
         <v>5.8588285446166992</v>
@@ -4269,11 +4264,11 @@
       </c>
       <c r="AE39">
         <f t="shared" si="9"/>
-        <v>1.383605972597473</v>
+        <v>9.2535244752727763</v>
       </c>
       <c r="AF39">
         <f t="shared" si="10"/>
-        <v>21.26794676097624</v>
+        <v>25.874732147049293</v>
       </c>
       <c r="AH39">
         <f t="shared" si="11"/>
@@ -4339,14 +4334,14 @@
         <v>68.543898627471719</v>
       </c>
       <c r="T40">
-        <v>6.6462020874023438</v>
+        <v>6.0101585388183594</v>
       </c>
       <c r="U40">
-        <v>2.687197208404541</v>
+        <v>2.5644443035125728</v>
       </c>
       <c r="V40">
         <f t="shared" si="5"/>
-        <v>105.36189125484339</v>
+        <v>99.839457341631515</v>
       </c>
       <c r="X40">
         <v>6.5131745338439941</v>
@@ -4368,11 +4363,11 @@
       </c>
       <c r="AE40">
         <f t="shared" si="9"/>
-        <v>2.1437308607093337</v>
+        <v>11.508605394470402</v>
       </c>
       <c r="AF40">
         <f t="shared" si="10"/>
-        <v>36.338935149497971</v>
+        <v>39.247013728351071</v>
       </c>
       <c r="AH40">
         <f t="shared" si="11"/>
@@ -4438,14 +4433,14 @@
         <v>110.78777520519267</v>
       </c>
       <c r="T41">
-        <v>3.117445707321167</v>
+        <v>2.1273660659790039</v>
       </c>
       <c r="U41">
-        <v>1.3539582490921021</v>
+        <v>0.77036756277084351</v>
       </c>
       <c r="V41">
         <f t="shared" si="5"/>
-        <v>98.085132003700153</v>
+        <v>117.63966909960001</v>
       </c>
       <c r="X41">
         <v>2.284206628799438</v>
@@ -4467,11 +4462,11 @@
       </c>
       <c r="AE41">
         <f t="shared" si="9"/>
-        <v>36.216276646035425</v>
+        <v>7.0450901870574265</v>
       </c>
       <c r="AF41">
         <f t="shared" si="10"/>
-        <v>53.857143565652898</v>
+        <v>12.459226284832726</v>
       </c>
       <c r="AH41">
         <f t="shared" si="11"/>
@@ -4537,14 +4532,14 @@
         <v>120.39173601764369</v>
       </c>
       <c r="T42">
-        <v>2.380269050598145</v>
+        <v>1.6550115346908569</v>
       </c>
       <c r="U42">
-        <v>0.97218215465545654</v>
+        <v>0.53530150651931763</v>
       </c>
       <c r="V42">
         <f t="shared" si="5"/>
-        <v>104.30087687788139</v>
+        <v>131.70798761037321</v>
       </c>
       <c r="X42">
         <v>1.682604312896729</v>
@@ -4566,11 +4561,11 @@
       </c>
       <c r="AE42">
         <f t="shared" si="9"/>
-        <v>34.584928791029348</v>
+        <v>6.4225073679262144</v>
       </c>
       <c r="AF42">
         <f t="shared" si="10"/>
-        <v>55.347813977957614</v>
+        <v>14.462615407341261</v>
       </c>
       <c r="AH42">
         <f t="shared" si="11"/>
@@ -4636,14 +4631,14 @@
         <v>119.87425316438599</v>
       </c>
       <c r="T43">
-        <v>3.051730632781982</v>
+        <v>2.0063304901123051</v>
       </c>
       <c r="U43">
-        <v>1.186030268669128</v>
+        <v>0.61609303951263428</v>
       </c>
       <c r="V43">
         <f t="shared" si="5"/>
-        <v>109.61247375724629</v>
+        <v>138.72851125033984</v>
       </c>
       <c r="X43">
         <v>2.0290639400482182</v>
@@ -4665,11 +4660,11 @@
       </c>
       <c r="AE43">
         <f t="shared" si="9"/>
-        <v>39.769654336446933</v>
+        <v>8.1098062603139454</v>
       </c>
       <c r="AF43">
         <f t="shared" si="10"/>
-        <v>52.854710365646959</v>
+        <v>20.59838133923159</v>
       </c>
       <c r="AH43">
         <f t="shared" si="11"/>
@@ -4735,14 +4730,14 @@
         <v>124.05557869819053</v>
       </c>
       <c r="T44">
-        <v>3.8110892772674561</v>
+        <v>2.7763113975524898</v>
       </c>
       <c r="U44">
-        <v>1.3752356767654419</v>
+        <v>0.94644498825073242</v>
       </c>
       <c r="V44">
         <f t="shared" si="5"/>
-        <v>118.0542283763864</v>
+        <v>124.96326246497807</v>
       </c>
       <c r="X44">
         <v>3.0317082405090332</v>
@@ -4764,11 +4759,11 @@
       </c>
       <c r="AE44">
         <f t="shared" si="9"/>
-        <v>20.451620646885456</v>
+        <v>12.253116385825232</v>
       </c>
       <c r="AF44">
         <f t="shared" si="10"/>
-        <v>26.5748436967733</v>
+        <v>12.890475080466416</v>
       </c>
       <c r="AH44">
         <f t="shared" si="11"/>
@@ -4834,14 +4829,14 @@
         <v>117.38720001137789</v>
       </c>
       <c r="T45">
-        <v>3.5112113952636719</v>
+        <v>2.5184199810028081</v>
       </c>
       <c r="U45">
-        <v>1.2591737508773799</v>
+        <v>0.8334314227104187</v>
       </c>
       <c r="V45">
         <f t="shared" si="5"/>
-        <v>118.79027027152203</v>
+        <v>128.72646426241118</v>
       </c>
       <c r="X45">
         <v>2.7036724090576172</v>
@@ -4863,11 +4858,11 @@
       </c>
       <c r="AE45">
         <f t="shared" si="9"/>
-        <v>22.333335491034482</v>
+        <v>12.256289422242075</v>
       </c>
       <c r="AF45">
         <f t="shared" si="10"/>
-        <v>20.888416942912809</v>
+        <v>19.985462489399133</v>
       </c>
       <c r="AH45">
         <f t="shared" si="11"/>
@@ -4933,14 +4928,14 @@
         <v>117.797055321</v>
       </c>
       <c r="T46">
-        <v>5.0375103950500488</v>
+        <v>3.842908382415771</v>
       </c>
       <c r="U46">
-        <v>1.879160523414612</v>
+        <v>1.3511993885040281</v>
       </c>
       <c r="V46">
         <f t="shared" si="5"/>
-        <v>114.19882350244472</v>
+        <v>121.15745595368126</v>
       </c>
       <c r="X46">
         <v>4.0133037567138672</v>
@@ -4962,11 +4957,11 @@
       </c>
       <c r="AE46">
         <f t="shared" si="9"/>
-        <v>19.789560674626031</v>
+        <v>8.6174973862561348</v>
       </c>
       <c r="AF46">
         <f t="shared" si="10"/>
-        <v>23.563948146673603</v>
+        <v>11.152065458704092</v>
       </c>
       <c r="AH46">
         <f t="shared" si="11"/>
@@ -5032,14 +5027,14 @@
         <v>89.221511714556357</v>
       </c>
       <c r="T47">
-        <v>6.8021421432495117</v>
+        <v>5.9956526756286621</v>
       </c>
       <c r="U47">
-        <v>2.712111234664917</v>
+        <v>2.450353860855103</v>
       </c>
       <c r="V47">
         <f t="shared" si="5"/>
-        <v>106.84341484604528</v>
+        <v>104.23587466976439</v>
       </c>
       <c r="X47">
         <v>6.1517362594604492</v>
@@ -5061,11 +5056,11 @@
       </c>
       <c r="AE47">
         <f t="shared" si="9"/>
-        <v>4.0719422161798065</v>
+        <v>8.267247924898065</v>
       </c>
       <c r="AF47">
         <f t="shared" si="10"/>
-        <v>13.092856260937701</v>
+        <v>21.480633804752038</v>
       </c>
       <c r="AH47">
         <f t="shared" si="11"/>
@@ -5131,14 +5126,14 @@
         <v>101.79507028989894</v>
       </c>
       <c r="T48">
-        <v>6.9928774833679199</v>
+        <v>6.2062931060791016</v>
       </c>
       <c r="U48">
-        <v>2.5616440773010249</v>
+        <v>2.2344808578491211</v>
       </c>
       <c r="V48">
         <f t="shared" si="5"/>
-        <v>116.29115576754151</v>
+        <v>118.32191733937189</v>
       </c>
       <c r="X48">
         <v>6.5255260467529297</v>
@@ -5160,11 +5155,11 @@
       </c>
       <c r="AE48">
         <f t="shared" si="9"/>
-        <v>0.67198588246695701</v>
+        <v>10.651966455341029</v>
       </c>
       <c r="AF48">
         <f t="shared" si="10"/>
-        <v>11.877117296741369</v>
+        <v>23.131829170280323</v>
       </c>
       <c r="AH48">
         <f t="shared" si="11"/>
@@ -5230,14 +5225,14 @@
         <v>21.682405083838052</v>
       </c>
       <c r="T49">
-        <v>11.79590320587158</v>
+        <v>11.740432739257811</v>
       </c>
       <c r="U49">
-        <v>5.8723592758178711</v>
+        <v>6.5917515754699707</v>
       </c>
       <c r="V49">
         <f t="shared" si="5"/>
-        <v>85.571301367411564</v>
+        <v>75.873973399290961</v>
       </c>
       <c r="X49">
         <v>14.01251125335693</v>
@@ -5250,7 +5245,7 @@
         <v>50.379371363106422</v>
       </c>
       <c r="AB49">
-        <f>ABS(P49-L49)/P49*100</f>
+        <f t="shared" si="7"/>
         <v>21.464885739310454</v>
       </c>
       <c r="AC49">
@@ -5259,11 +5254,11 @@
       </c>
       <c r="AE49">
         <f t="shared" si="9"/>
-        <v>53.038047591880002</v>
+        <v>53.258887095876219</v>
       </c>
       <c r="AF49">
         <f t="shared" si="10"/>
-        <v>88.100589106752039</v>
+        <v>86.642853950415457</v>
       </c>
       <c r="AH49">
         <f t="shared" si="11"/>
@@ -5275,6 +5270,8 @@
       </c>
     </row>
     <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="T50"/>
+      <c r="U50"/>
       <c r="AB50" s="2">
         <f>AVERAGE(AB3:AB49)</f>
         <v>8.4064847937735827</v>
@@ -5285,11 +5282,11 @@
       </c>
       <c r="AE50" s="2">
         <f>AVERAGE(AE3:AE49)</f>
-        <v>16.681261869728186</v>
+        <v>9.3913969030150817</v>
       </c>
       <c r="AF50" s="2">
         <f>AVERAGE(AF3:AF49)</f>
-        <v>26.901211649600484</v>
+        <v>15.782944957207679</v>
       </c>
       <c r="AH50" s="2">
         <f>AVERAGE(AH3:AH49)</f>

--- a/data_contrast/experiment_data.xlsx
+++ b/data_contrast/experiment_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\data_contrast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_2A211C1DD4FF011C744729514465B8B14E944051" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_49AD5AC91743D45AF4852F514465B8B14E942036" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data_contrast/experiment_data.xlsx
+++ b/data_contrast/experiment_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\data_contrast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_49AD5AC91743D45AF4852F514465B8B14E942036" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C78CB8-5962-4494-AC49-6F8EA13ADB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="26">
   <si>
     <t>仿真值</t>
   </si>
@@ -43,6 +43,9 @@
   </si>
   <si>
     <t>模型预测值(未使用特征工程)</t>
+  </si>
+  <si>
+    <t>迁移学习模型预测值</t>
   </si>
   <si>
     <t>仿真值相对误差</t>
@@ -103,6 +106,10 @@
   </si>
   <si>
     <t>R%</t>
+  </si>
+  <si>
+    <t>迁移学习相对误差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -498,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AI50"/>
+  <dimension ref="A1:AP50"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="15" max="15" width="8.625" style="1" customWidth="1"/>
@@ -507,7 +514,7 @@
     <col min="23" max="23" width="10.625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="L1" t="s">
         <v>0</v>
       </c>
@@ -523,100 +530,121 @@
       <c r="AB1" t="s">
         <v>4</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>5</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>6</v>
       </c>
+      <c r="AL1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P2" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" t="s">
         <v>21</v>
       </c>
-      <c r="R2" t="s">
-        <v>19</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>22</v>
+      </c>
+      <c r="V2" t="s">
         <v>20</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>21</v>
       </c>
-      <c r="V2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z2" t="s">
         <v>20</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AB2" t="s">
         <v>21</v>
       </c>
-      <c r="Z2" t="s">
-        <v>19</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>22</v>
       </c>
-      <c r="AC2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>22</v>
+      <c r="AD2" t="s">
+        <v>20</v>
       </c>
       <c r="AF2" t="s">
         <v>23</v>
       </c>
-      <c r="AH2" t="s">
-        <v>22</v>
+      <c r="AG2" t="s">
+        <v>24</v>
       </c>
       <c r="AI2" t="s">
         <v>23</v>
       </c>
+      <c r="AJ2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -687,35 +715,53 @@
         <v>7.0287048816680908E-2</v>
       </c>
       <c r="Z3">
-        <f t="shared" ref="Z3:Z49" si="6">6780000*2*3.1415926*X3*0.000001/Y3</f>
+        <f>6780000*2*3.1415926*X3*0.000001/Y3</f>
         <v>62.541474481504522</v>
       </c>
       <c r="AB3">
-        <f t="shared" ref="AB3:AB49" si="7">ABS(P3-L3)/P3*100</f>
+        <v>0.18094408512115481</v>
+      </c>
+      <c r="AC3">
+        <v>9.3563079833984375E-2</v>
+      </c>
+      <c r="AD3">
+        <f>6780000*2*3.1415926*AB3*0.000001/AC3</f>
+        <v>82.385244840350779</v>
+      </c>
+      <c r="AF3">
+        <f t="shared" ref="AF3:AF49" si="6">ABS(P3-L3)/P3*100</f>
         <v>16.775700934579447</v>
       </c>
-      <c r="AC3">
-        <f t="shared" ref="AC3:AC49" si="8">ABS(Q3-M3)/Q3*100</f>
+      <c r="AG3">
+        <f t="shared" ref="AG3:AG49" si="7">ABS(Q3-M3)/Q3*100</f>
         <v>8.4790593453302225</v>
       </c>
-      <c r="AE3">
-        <f t="shared" ref="AE3:AE49" si="9">ABS(P3-T3)/P3*100</f>
+      <c r="AI3">
+        <f t="shared" ref="AI3:AI49" si="8">ABS(P3-T3)/P3*100</f>
         <v>20.083951780304801</v>
       </c>
-      <c r="AF3">
-        <f t="shared" ref="AF3:AF49" si="10">ABS(Q3-U3)/Q3*100</f>
+      <c r="AJ3">
+        <f t="shared" ref="AJ3:AJ49" si="9">ABS(Q3-U3)/Q3*100</f>
         <v>11.573420399486485</v>
       </c>
-      <c r="AH3">
-        <f t="shared" ref="AH3:AH49" si="11">ABS(P3-X3)/P3*100</f>
+      <c r="AL3">
+        <f>ABS(P3-X3)/P3*100</f>
         <v>42.596177817133736</v>
       </c>
-      <c r="AI3">
-        <f t="shared" ref="AI3:AI49" si="12">ABS(Q3-Y3)/Q3*100</f>
+      <c r="AM3">
+        <f>ABS(Q3-Y3)/Q3*100</f>
         <v>18.816502094434028</v>
       </c>
+      <c r="AO3">
+        <f>ABS(P3-AB3)/P3*100</f>
+        <v>0.65870333842612916</v>
+      </c>
+      <c r="AP3">
+        <f>ABS(Q3-AC3)/Q3*100</f>
+        <v>8.0679616461276229</v>
+      </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -786,35 +832,53 @@
         <v>0.12292706966400151</v>
       </c>
       <c r="Z4">
+        <f t="shared" ref="Z3:Z49" si="10">6780000*2*3.1415926*X4*0.000001/Y4</f>
+        <v>60.488955775686705</v>
+      </c>
+      <c r="AB4">
+        <v>0.20330154895782471</v>
+      </c>
+      <c r="AC4">
+        <v>0.1234317123889923</v>
+      </c>
+      <c r="AD4">
+        <f t="shared" ref="AD4:AD49" si="11">6780000*2*3.1415926*AB4*0.000001/AC4</f>
+        <v>70.165478018870672</v>
+      </c>
+      <c r="AF4">
         <f t="shared" si="6"/>
-        <v>60.488955775686705</v>
-      </c>
-      <c r="AB4">
+        <v>28.588364034287789</v>
+      </c>
+      <c r="AG4">
         <f t="shared" si="7"/>
-        <v>28.588364034287789</v>
-      </c>
-      <c r="AC4">
+        <v>18.069933120093047</v>
+      </c>
+      <c r="AI4">
         <f t="shared" si="8"/>
-        <v>18.069933120093047</v>
-      </c>
-      <c r="AE4">
+        <v>23.993750642995305</v>
+      </c>
+      <c r="AJ4">
         <f t="shared" si="9"/>
-        <v>23.993750642995305</v>
-      </c>
-      <c r="AF4">
-        <f t="shared" si="10"/>
         <v>22.117254664018169</v>
       </c>
-      <c r="AH4">
-        <f t="shared" si="11"/>
+      <c r="AL4">
+        <f t="shared" ref="AL3:AL49" si="12">ABS(P4-X4)/P4*100</f>
         <v>20.414156359780915</v>
       </c>
-      <c r="AI4">
-        <f t="shared" si="12"/>
+      <c r="AM4">
+        <f t="shared" ref="AM3:AM49" si="13">ABS(Q4-Y4)/Q4*100</f>
         <v>10.637489339923293</v>
       </c>
+      <c r="AO4">
+        <f t="shared" ref="AO4:AO49" si="14">ABS(P4-AB4)/P4*100</f>
+        <v>7.3036891492683207</v>
+      </c>
+      <c r="AP4">
+        <f t="shared" ref="AP4:AP49" si="15">ABS(Q4-AC4)/Q4*100</f>
+        <v>10.270636530246941</v>
+      </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -885,35 +949,53 @@
         <v>0.1150748729705811</v>
       </c>
       <c r="Z5">
+        <f t="shared" si="10"/>
+        <v>73.845735323464666</v>
+      </c>
+      <c r="AB5">
+        <v>0.22940981388092041</v>
+      </c>
+      <c r="AC5">
+        <v>0.12445616722106929</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="11"/>
+        <v>78.524490131627033</v>
+      </c>
+      <c r="AF5">
         <f t="shared" si="6"/>
-        <v>73.845735323464666</v>
-      </c>
-      <c r="AB5">
+        <v>12.55538395464696</v>
+      </c>
+      <c r="AG5">
         <f t="shared" si="7"/>
-        <v>12.55538395464696</v>
-      </c>
-      <c r="AC5">
+        <v>15.898569066710754</v>
+      </c>
+      <c r="AI5">
         <f t="shared" si="8"/>
-        <v>15.898569066710754</v>
-      </c>
-      <c r="AE5">
+        <v>16.941987302905002</v>
+      </c>
+      <c r="AJ5">
         <f t="shared" si="9"/>
-        <v>16.941987302905002</v>
-      </c>
-      <c r="AF5">
-        <f t="shared" si="10"/>
         <v>10.469975384383234</v>
       </c>
-      <c r="AH5">
-        <f t="shared" si="11"/>
+      <c r="AL5">
+        <f t="shared" si="12"/>
         <v>14.328025145498749</v>
       </c>
-      <c r="AI5">
-        <f t="shared" si="12"/>
+      <c r="AM5">
+        <f t="shared" si="13"/>
         <v>4.8732140443241283</v>
       </c>
+      <c r="AO5">
+        <f t="shared" si="14"/>
+        <v>1.4731945194466507</v>
+      </c>
+      <c r="AP5">
+        <f t="shared" si="15"/>
+        <v>2.8818444416543776</v>
+      </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2</v>
       </c>
@@ -984,35 +1066,53 @@
         <v>7.3583334684371948E-2</v>
       </c>
       <c r="Z6">
+        <f t="shared" si="10"/>
+        <v>123.61693336601557</v>
+      </c>
+      <c r="AB6">
+        <v>0.26487672328948969</v>
+      </c>
+      <c r="AC6">
+        <v>0.10129693150520321</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="11"/>
+        <v>111.39278449839496</v>
+      </c>
+      <c r="AF6">
         <f t="shared" si="6"/>
-        <v>123.61693336601557</v>
-      </c>
-      <c r="AB6">
+        <v>10.34079191787518</v>
+      </c>
+      <c r="AG6">
         <f t="shared" si="7"/>
-        <v>10.34079191787518</v>
-      </c>
-      <c r="AC6">
+        <v>16.74820196518753</v>
+      </c>
+      <c r="AI6">
         <f t="shared" si="8"/>
-        <v>16.74820196518753</v>
-      </c>
-      <c r="AE6">
+        <v>6.4738342150892958</v>
+      </c>
+      <c r="AJ6">
         <f t="shared" si="9"/>
-        <v>6.4738342150892958</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="10"/>
         <v>13.762896671907415</v>
       </c>
-      <c r="AH6">
-        <f t="shared" si="11"/>
+      <c r="AL6">
+        <f t="shared" si="12"/>
         <v>13.017524848528961</v>
       </c>
-      <c r="AI6">
-        <f t="shared" si="12"/>
+      <c r="AM6">
+        <f t="shared" si="13"/>
         <v>25.230066470515126</v>
       </c>
+      <c r="AO6">
+        <f t="shared" si="14"/>
+        <v>7.9015493276395983</v>
+      </c>
+      <c r="AP6">
+        <f t="shared" si="15"/>
+        <v>2.9304375491075416</v>
+      </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1083,35 +1183,53 @@
         <v>0.17784106731414789</v>
       </c>
       <c r="Z7">
+        <f t="shared" si="10"/>
+        <v>96.06964517307199</v>
+      </c>
+      <c r="AB7">
+        <v>0.43945407867431641</v>
+      </c>
+      <c r="AC7">
+        <v>0.2010308504104614</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="11"/>
+        <v>93.1237260565414</v>
+      </c>
+      <c r="AF7">
         <f t="shared" si="6"/>
-        <v>96.06964517307199</v>
-      </c>
-      <c r="AB7">
+        <v>7.4506165113799661</v>
+      </c>
+      <c r="AG7">
         <f t="shared" si="7"/>
-        <v>7.4506165113799661</v>
-      </c>
-      <c r="AC7">
+        <v>15.196523447967838</v>
+      </c>
+      <c r="AI7">
         <f t="shared" si="8"/>
-        <v>15.196523447967838</v>
-      </c>
-      <c r="AE7">
+        <v>5.2598358930215614</v>
+      </c>
+      <c r="AJ7">
         <f t="shared" si="9"/>
-        <v>5.2598358930215614</v>
-      </c>
-      <c r="AF7">
-        <f t="shared" si="10"/>
         <v>16.270421838696471</v>
       </c>
-      <c r="AH7">
-        <f t="shared" si="11"/>
+      <c r="AL7">
+        <f t="shared" si="12"/>
         <v>7.0459859281555941</v>
       </c>
-      <c r="AI7">
-        <f t="shared" si="12"/>
+      <c r="AM7">
+        <f t="shared" si="13"/>
         <v>20.571207095065695</v>
       </c>
+      <c r="AO7">
+        <f t="shared" si="14"/>
+        <v>1.8527971710741196</v>
+      </c>
+      <c r="AP7">
+        <f t="shared" si="15"/>
+        <v>10.214001603188294</v>
+      </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2</v>
       </c>
@@ -1182,35 +1300,53 @@
         <v>0.12534976005554199</v>
       </c>
       <c r="Z8">
+        <f t="shared" si="10"/>
+        <v>125.18964287226396</v>
+      </c>
+      <c r="AB8">
+        <v>0.4061812162399292</v>
+      </c>
+      <c r="AC8">
+        <v>0.1378190219402313</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="11"/>
+        <v>125.55101468412542</v>
+      </c>
+      <c r="AF8">
         <f t="shared" si="6"/>
-        <v>125.18964287226396</v>
-      </c>
-      <c r="AB8">
+        <v>6.6397479333587723</v>
+      </c>
+      <c r="AG8">
         <f t="shared" si="7"/>
-        <v>6.6397479333587723</v>
-      </c>
-      <c r="AC8">
+        <v>9.246349758162026</v>
+      </c>
+      <c r="AI8">
         <f t="shared" si="8"/>
-        <v>9.246349758162026</v>
-      </c>
-      <c r="AE8">
+        <v>4.7630421156860798</v>
+      </c>
+      <c r="AJ8">
         <f t="shared" si="9"/>
-        <v>4.7630421156860798</v>
-      </c>
-      <c r="AF8">
-        <f t="shared" si="10"/>
         <v>7.1630404894989352</v>
       </c>
-      <c r="AH8">
-        <f t="shared" si="11"/>
+      <c r="AL8">
+        <f t="shared" si="12"/>
         <v>6.3033480294315183</v>
       </c>
-      <c r="AI8">
-        <f t="shared" si="12"/>
+      <c r="AM8">
+        <f t="shared" si="13"/>
         <v>5.2677145892215851</v>
       </c>
+      <c r="AO8">
+        <f t="shared" si="14"/>
+        <v>3.3145660027799053</v>
+      </c>
+      <c r="AP8">
+        <f t="shared" si="15"/>
+        <v>4.1558509221820605</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>2</v>
       </c>
@@ -1281,35 +1417,53 @@
         <v>0.14516684412956241</v>
       </c>
       <c r="Z9">
+        <f t="shared" si="10"/>
+        <v>126.35271262872628</v>
+      </c>
+      <c r="AB9">
+        <v>0.46019577980041498</v>
+      </c>
+      <c r="AC9">
+        <v>0.15207195281982419</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="11"/>
+        <v>128.91488441418622</v>
+      </c>
+      <c r="AF9">
         <f t="shared" si="6"/>
-        <v>126.35271262872628</v>
-      </c>
-      <c r="AB9">
+        <v>6.3261210478370122</v>
+      </c>
+      <c r="AG9">
         <f t="shared" si="7"/>
-        <v>6.3261210478370122</v>
-      </c>
-      <c r="AC9">
+        <v>9.6468174347981375</v>
+      </c>
+      <c r="AI9">
         <f t="shared" si="8"/>
-        <v>9.6468174347981375</v>
-      </c>
-      <c r="AE9">
+        <v>4.5072856390036993</v>
+      </c>
+      <c r="AJ9">
         <f t="shared" si="9"/>
-        <v>4.5072856390036993</v>
-      </c>
-      <c r="AF9">
-        <f t="shared" si="10"/>
         <v>1.6407729472888877</v>
       </c>
-      <c r="AH9">
-        <f t="shared" si="11"/>
+      <c r="AL9">
+        <f t="shared" si="12"/>
         <v>4.3329493038062186</v>
       </c>
-      <c r="AI9">
-        <f t="shared" si="12"/>
+      <c r="AM9">
+        <f t="shared" si="13"/>
         <v>3.7276485384511719</v>
       </c>
+      <c r="AO9">
+        <f t="shared" si="14"/>
+        <v>2.2498233164652071</v>
+      </c>
+      <c r="AP9">
+        <f t="shared" si="15"/>
+        <v>8.6616311681487677</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2</v>
       </c>
@@ -1380,35 +1534,53 @@
         <v>0.19915902614593509</v>
       </c>
       <c r="Z10">
+        <f t="shared" si="10"/>
+        <v>103.1091976044388</v>
+      </c>
+      <c r="AB10">
+        <v>0.54251551628112793</v>
+      </c>
+      <c r="AC10">
+        <v>0.21839013695716861</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="11"/>
+        <v>105.82510253849645</v>
+      </c>
+      <c r="AF10">
         <f t="shared" si="6"/>
-        <v>103.1091976044388</v>
-      </c>
-      <c r="AB10">
+        <v>6.5910470646425496</v>
+      </c>
+      <c r="AG10">
         <f t="shared" si="7"/>
-        <v>6.5910470646425496</v>
-      </c>
-      <c r="AC10">
+        <v>3.208589999051136</v>
+      </c>
+      <c r="AI10">
         <f t="shared" si="8"/>
-        <v>3.208589999051136</v>
-      </c>
-      <c r="AE10">
+        <v>2.1571488865378976</v>
+      </c>
+      <c r="AJ10">
         <f t="shared" si="9"/>
-        <v>2.1571488865378976</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="10"/>
         <v>2.4128340398895518</v>
       </c>
-      <c r="AH10">
-        <f t="shared" si="11"/>
+      <c r="AL10">
+        <f t="shared" si="12"/>
         <v>8.297132584882041</v>
       </c>
-      <c r="AI10">
-        <f t="shared" si="12"/>
+      <c r="AM10">
+        <f t="shared" si="13"/>
         <v>5.5133190312481775</v>
       </c>
+      <c r="AO10">
+        <f t="shared" si="14"/>
+        <v>3.2065434465487033</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="15"/>
+        <v>3.610464444998867</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>3</v>
       </c>
@@ -1479,35 +1651,53 @@
         <v>0.19164204597473139</v>
       </c>
       <c r="Z11">
+        <f t="shared" si="10"/>
+        <v>85.2921282014794</v>
+      </c>
+      <c r="AB11">
+        <v>0.40494430065155029</v>
+      </c>
+      <c r="AC11">
+        <v>0.20291003584861761</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="11"/>
+        <v>85.016127351867141</v>
+      </c>
+      <c r="AF11">
         <f t="shared" si="6"/>
-        <v>85.2921282014794</v>
-      </c>
-      <c r="AB11">
+        <v>27.101478404108427</v>
+      </c>
+      <c r="AG11">
         <f t="shared" si="7"/>
-        <v>27.101478404108427</v>
-      </c>
-      <c r="AC11">
+        <v>78.44825359088658</v>
+      </c>
+      <c r="AI11">
         <f t="shared" si="8"/>
-        <v>78.44825359088658</v>
-      </c>
-      <c r="AE11">
+        <v>9.5181537943377883</v>
+      </c>
+      <c r="AJ11">
         <f t="shared" si="9"/>
-        <v>9.5181537943377883</v>
-      </c>
-      <c r="AF11">
-        <f t="shared" si="10"/>
         <v>6.2759472392111952</v>
       </c>
-      <c r="AH11">
-        <f t="shared" si="11"/>
+      <c r="AL11">
+        <f t="shared" si="12"/>
         <v>7.052013602085462</v>
       </c>
-      <c r="AI11">
-        <f t="shared" si="12"/>
+      <c r="AM11">
+        <f t="shared" si="13"/>
         <v>5.0807102651157035</v>
       </c>
+      <c r="AO11">
+        <f t="shared" si="14"/>
+        <v>1.9054042655094878</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="15"/>
+        <v>0.50026540298049182</v>
+      </c>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>3</v>
       </c>
@@ -1578,35 +1768,53 @@
         <v>0.1967687010765076</v>
       </c>
       <c r="Z12">
+        <f t="shared" si="10"/>
+        <v>104.30115859472703</v>
+      </c>
+      <c r="AB12">
+        <v>0.51990699768066406</v>
+      </c>
+      <c r="AC12">
+        <v>0.2141865789890289</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="11"/>
+        <v>103.40533915458242</v>
+      </c>
+      <c r="AF12">
         <f t="shared" si="6"/>
-        <v>104.30115859472703</v>
-      </c>
-      <c r="AB12">
+        <v>8.2197520250368168</v>
+      </c>
+      <c r="AG12">
         <f t="shared" si="7"/>
-        <v>8.2197520250368168</v>
-      </c>
-      <c r="AC12">
+        <v>4.0801746403786927</v>
+      </c>
+      <c r="AI12">
         <f t="shared" si="8"/>
-        <v>4.0801746403786927</v>
-      </c>
-      <c r="AE12">
+        <v>9.5752330521596338</v>
+      </c>
+      <c r="AJ12">
         <f t="shared" si="9"/>
-        <v>9.5752330521596338</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="10"/>
         <v>7.4866964654989694</v>
       </c>
-      <c r="AH12">
-        <f t="shared" si="11"/>
+      <c r="AL12">
+        <f t="shared" si="12"/>
         <v>11.309758939167198</v>
       </c>
-      <c r="AI12">
-        <f t="shared" si="12"/>
+      <c r="AM12">
+        <f t="shared" si="13"/>
         <v>9.5690513918343711</v>
       </c>
+      <c r="AO12">
+        <f t="shared" si="14"/>
+        <v>4.2881079380220832</v>
+      </c>
+      <c r="AP12">
+        <f t="shared" si="15"/>
+        <v>1.5641440373965267</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>3</v>
       </c>
@@ -1677,35 +1885,53 @@
         <v>0.19587200880050659</v>
       </c>
       <c r="Z13">
+        <f t="shared" si="10"/>
+        <v>108.4025748000511</v>
+      </c>
+      <c r="AB13">
+        <v>0.51855742931365967</v>
+      </c>
+      <c r="AC13">
+        <v>0.20038458704948431</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="11"/>
+        <v>110.24073538496873</v>
+      </c>
+      <c r="AF13">
         <f t="shared" si="6"/>
-        <v>108.4025748000511</v>
-      </c>
-      <c r="AB13">
+        <v>24.696333988732178</v>
+      </c>
+      <c r="AG13">
         <f t="shared" si="7"/>
-        <v>24.696333988732178</v>
-      </c>
-      <c r="AC13">
+        <v>84.008394398145867</v>
+      </c>
+      <c r="AI13">
         <f t="shared" si="8"/>
-        <v>84.008394398145867</v>
-      </c>
-      <c r="AE13">
+        <v>7.4038338849606298</v>
+      </c>
+      <c r="AJ13">
         <f t="shared" si="9"/>
-        <v>7.4038338849606298</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="10"/>
         <v>7.6740100624892689</v>
       </c>
-      <c r="AH13">
-        <f t="shared" si="11"/>
+      <c r="AL13">
+        <f t="shared" si="12"/>
         <v>5.7685206074991822</v>
       </c>
-      <c r="AI13">
-        <f t="shared" si="12"/>
+      <c r="AM13">
+        <f t="shared" si="13"/>
         <v>3.4114064793596364</v>
       </c>
+      <c r="AO13">
+        <f t="shared" si="14"/>
+        <v>1.9629014040042914</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="15"/>
+        <v>1.1861595495417376</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>3</v>
       </c>
@@ -1776,35 +2002,53 @@
         <v>0.18338131904602051</v>
       </c>
       <c r="Z14">
+        <f t="shared" si="10"/>
+        <v>119.34276154239784</v>
+      </c>
+      <c r="AB14">
+        <v>0.54602009057998657</v>
+      </c>
+      <c r="AC14">
+        <v>0.19066014885902399</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="11"/>
+        <v>121.9995558903878</v>
+      </c>
+      <c r="AF14">
         <f t="shared" si="6"/>
-        <v>119.34276154239784</v>
-      </c>
-      <c r="AB14">
+        <v>6.0041675967596806</v>
+      </c>
+      <c r="AG14">
         <f t="shared" si="7"/>
-        <v>6.0041675967596806</v>
-      </c>
-      <c r="AC14">
+        <v>11.413465450903926</v>
+      </c>
+      <c r="AI14">
         <f t="shared" si="8"/>
-        <v>11.413465450903926</v>
-      </c>
-      <c r="AE14">
+        <v>6.7791510443768983</v>
+      </c>
+      <c r="AJ14">
         <f t="shared" si="9"/>
-        <v>6.7791510443768983</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="10"/>
         <v>6.4718050276391716</v>
       </c>
-      <c r="AH14">
-        <f t="shared" si="11"/>
+      <c r="AL14">
+        <f t="shared" si="12"/>
         <v>7.5179267423202276</v>
       </c>
-      <c r="AI14">
-        <f t="shared" si="12"/>
+      <c r="AM14">
+        <f t="shared" si="13"/>
         <v>3.3461661065616939</v>
       </c>
+      <c r="AO14">
+        <f t="shared" si="14"/>
+        <v>1.7065543510375196</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="15"/>
+        <v>0.49024870027090212</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>3</v>
       </c>
@@ -1875,35 +2119,53 @@
         <v>0.1948093771934509</v>
       </c>
       <c r="Z15">
+        <f t="shared" si="10"/>
+        <v>131.18929942431464</v>
+      </c>
+      <c r="AB15">
+        <v>0.64625465869903564</v>
+      </c>
+      <c r="AC15">
+        <v>0.20320022106170649</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="11"/>
+        <v>135.4843292463172</v>
+      </c>
+      <c r="AF15">
         <f t="shared" si="6"/>
-        <v>131.18929942431464</v>
-      </c>
-      <c r="AB15">
+        <v>5.9301236894988509</v>
+      </c>
+      <c r="AG15">
         <f t="shared" si="7"/>
-        <v>5.9301236894988509</v>
-      </c>
-      <c r="AC15">
+        <v>11.259286029303674</v>
+      </c>
+      <c r="AI15">
         <f t="shared" si="8"/>
-        <v>11.259286029303674</v>
-      </c>
-      <c r="AE15">
+        <v>3.3348653148360947</v>
+      </c>
+      <c r="AJ15">
         <f t="shared" si="9"/>
-        <v>3.3348653148360947</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="10"/>
         <v>6.5236218820193148</v>
       </c>
-      <c r="AH15">
-        <f t="shared" si="11"/>
+      <c r="AL15">
+        <f t="shared" si="12"/>
         <v>6.5431705350238376</v>
       </c>
-      <c r="AI15">
-        <f t="shared" si="12"/>
+      <c r="AM15">
+        <f t="shared" si="13"/>
         <v>4.5379638391478911</v>
       </c>
+      <c r="AO15">
+        <f t="shared" si="14"/>
+        <v>0.67369630630063149</v>
+      </c>
+      <c r="AP15">
+        <f t="shared" si="15"/>
+        <v>0.42621597407434403</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>3</v>
       </c>
@@ -1974,35 +2236,53 @@
         <v>0.23711210489273071</v>
       </c>
       <c r="Z16">
+        <f t="shared" si="10"/>
+        <v>136.55507160516052</v>
+      </c>
+      <c r="AB16">
+        <v>0.7864534854888916</v>
+      </c>
+      <c r="AC16">
+        <v>0.23431894183158869</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="11"/>
+        <v>142.97996911215265</v>
+      </c>
+      <c r="AF16">
         <f t="shared" si="6"/>
-        <v>136.55507160516052</v>
-      </c>
-      <c r="AB16">
+        <v>5.0966208925944017</v>
+      </c>
+      <c r="AG16">
         <f t="shared" si="7"/>
-        <v>5.0966208925944017</v>
-      </c>
-      <c r="AC16">
+        <v>7.6703476337903513</v>
+      </c>
+      <c r="AI16">
         <f t="shared" si="8"/>
-        <v>7.6703476337903513</v>
-      </c>
-      <c r="AE16">
+        <v>1.3699983295641387</v>
+      </c>
+      <c r="AJ16">
         <f t="shared" si="9"/>
-        <v>1.3699983295641387</v>
-      </c>
-      <c r="AF16">
-        <f t="shared" si="10"/>
         <v>1.2756880170104354</v>
       </c>
-      <c r="AH16">
-        <f t="shared" si="11"/>
+      <c r="AL16">
+        <f t="shared" si="12"/>
         <v>1.9040261605839393</v>
       </c>
-      <c r="AI16">
-        <f t="shared" si="12"/>
+      <c r="AM16">
+        <f t="shared" si="13"/>
         <v>4.8704577146088983</v>
       </c>
+      <c r="AO16">
+        <f t="shared" si="14"/>
+        <v>1.5014436241826035</v>
+      </c>
+      <c r="AP16">
+        <f t="shared" si="15"/>
+        <v>3.6350914779251191</v>
+      </c>
     </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>3</v>
       </c>
@@ -2073,35 +2353,53 @@
         <v>0.29882404208183289</v>
       </c>
       <c r="Z17">
+        <f t="shared" si="10"/>
+        <v>132.23652323777208</v>
+      </c>
+      <c r="AB17">
+        <v>0.97482526302337646</v>
+      </c>
+      <c r="AC17">
+        <v>0.29356756806373602</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="11"/>
+        <v>141.45824160364646</v>
+      </c>
+      <c r="AF17">
         <f t="shared" si="6"/>
-        <v>132.23652323777208</v>
-      </c>
-      <c r="AB17">
+        <v>4.9989251598038535</v>
+      </c>
+      <c r="AG17">
         <f t="shared" si="7"/>
-        <v>4.9989251598038535</v>
-      </c>
-      <c r="AC17">
+        <v>5.7436367236723651</v>
+      </c>
+      <c r="AI17">
         <f t="shared" si="8"/>
-        <v>5.7436367236723651</v>
-      </c>
-      <c r="AE17">
+        <v>2.399094105812023</v>
+      </c>
+      <c r="AJ17">
         <f t="shared" si="9"/>
-        <v>2.399094105812023</v>
-      </c>
-      <c r="AF17">
-        <f t="shared" si="10"/>
         <v>2.4713717957641723</v>
       </c>
-      <c r="AH17">
-        <f t="shared" si="11"/>
+      <c r="AL17">
+        <f t="shared" si="12"/>
         <v>5.4335477399807131</v>
       </c>
-      <c r="AI17">
-        <f t="shared" si="12"/>
+      <c r="AM17">
+        <f t="shared" si="13"/>
         <v>7.587413890848925</v>
       </c>
+      <c r="AO17">
+        <f t="shared" si="14"/>
+        <v>0.61828920435763179</v>
+      </c>
+      <c r="AP17">
+        <f t="shared" si="15"/>
+        <v>5.6948939923442019</v>
+      </c>
     </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3</v>
       </c>
@@ -2172,35 +2470,53 @@
         <v>0.28100436925888062</v>
       </c>
       <c r="Z18">
+        <f t="shared" si="10"/>
+        <v>159.90489476481977</v>
+      </c>
+      <c r="AB18">
+        <v>1.0985369682312009</v>
+      </c>
+      <c r="AC18">
+        <v>0.29043430089950562</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="11"/>
+        <v>161.12996959955231</v>
+      </c>
+      <c r="AF18">
         <f t="shared" si="6"/>
-        <v>159.90489476481977</v>
-      </c>
-      <c r="AB18">
+        <v>4.2099149472925648</v>
+      </c>
+      <c r="AG18">
         <f t="shared" si="7"/>
-        <v>4.2099149472925648</v>
-      </c>
-      <c r="AC18">
+        <v>8.0360302045183314</v>
+      </c>
+      <c r="AI18">
         <f t="shared" si="8"/>
-        <v>8.0360302045183314</v>
-      </c>
-      <c r="AE18">
+        <v>2.3300966214184298</v>
+      </c>
+      <c r="AJ18">
         <f t="shared" si="9"/>
-        <v>2.3300966214184298</v>
-      </c>
-      <c r="AF18">
-        <f t="shared" si="10"/>
         <v>16.07281617493123</v>
       </c>
-      <c r="AH18">
-        <f t="shared" si="11"/>
+      <c r="AL18">
+        <f t="shared" si="12"/>
         <v>4.9654714974619454</v>
       </c>
-      <c r="AI18">
-        <f t="shared" si="12"/>
+      <c r="AM18">
+        <f t="shared" si="13"/>
         <v>15.634899493387355</v>
       </c>
+      <c r="AO18">
+        <f t="shared" si="14"/>
+        <v>1.0237887889719035</v>
+      </c>
+      <c r="AP18">
+        <f t="shared" si="15"/>
+        <v>19.515370108022555</v>
+      </c>
     </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>4</v>
       </c>
@@ -2271,35 +2587,53 @@
         <v>0.47128748893737787</v>
       </c>
       <c r="Z19">
+        <f t="shared" si="10"/>
+        <v>56.894986617585147</v>
+      </c>
+      <c r="AB19">
+        <v>0.62023019790649414</v>
+      </c>
+      <c r="AC19">
+        <v>0.31761860847473139</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="11"/>
+        <v>83.18720324171025</v>
+      </c>
+      <c r="AF19">
         <f t="shared" si="6"/>
-        <v>56.894986617585147</v>
-      </c>
-      <c r="AB19">
+        <v>4.7647188388772062</v>
+      </c>
+      <c r="AG19">
         <f t="shared" si="7"/>
-        <v>4.7647188388772062</v>
-      </c>
-      <c r="AC19">
+        <v>15.066874103705938</v>
+      </c>
+      <c r="AI19">
         <f t="shared" si="8"/>
-        <v>15.066874103705938</v>
-      </c>
-      <c r="AE19">
+        <v>8.3384560082299846</v>
+      </c>
+      <c r="AJ19">
         <f t="shared" si="9"/>
-        <v>8.3384560082299846</v>
-      </c>
-      <c r="AF19">
-        <f t="shared" si="10"/>
         <v>15.404449163162356</v>
       </c>
-      <c r="AH19">
-        <f t="shared" si="11"/>
+      <c r="AL19">
+        <f t="shared" si="12"/>
         <v>2.7089421380888417</v>
       </c>
-      <c r="AI19">
-        <f t="shared" si="12"/>
+      <c r="AM19">
+        <f t="shared" si="13"/>
         <v>77.857758675136949</v>
       </c>
+      <c r="AO19">
+        <f t="shared" si="14"/>
+        <v>4.1316004225154321</v>
+      </c>
+      <c r="AP19">
+        <f t="shared" si="15"/>
+        <v>19.865125094245375</v>
+      </c>
     </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>4</v>
       </c>
@@ -2370,35 +2704,53 @@
         <v>0.40556862950325012</v>
       </c>
       <c r="Z20">
+        <f t="shared" si="10"/>
+        <v>53.94354233015698</v>
+      </c>
+      <c r="AB20">
+        <v>0.50306236743927002</v>
+      </c>
+      <c r="AC20">
+        <v>0.26915031671524048</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="11"/>
+        <v>79.622624744236433</v>
+      </c>
+      <c r="AF20">
         <f t="shared" si="6"/>
-        <v>53.94354233015698</v>
-      </c>
-      <c r="AB20">
+        <v>5.1597752554344796</v>
+      </c>
+      <c r="AG20">
         <f t="shared" si="7"/>
-        <v>5.1597752554344796</v>
-      </c>
-      <c r="AC20">
+        <v>17.883843878787879</v>
+      </c>
+      <c r="AI20">
         <f t="shared" si="8"/>
-        <v>17.883843878787879</v>
-      </c>
-      <c r="AE20">
+        <v>10.608680055225619</v>
+      </c>
+      <c r="AJ20">
         <f t="shared" si="9"/>
-        <v>10.608680055225619</v>
-      </c>
-      <c r="AF20">
-        <f t="shared" si="10"/>
         <v>24.262838652639658</v>
       </c>
-      <c r="AH20">
-        <f t="shared" si="11"/>
+      <c r="AL20">
+        <f t="shared" si="12"/>
         <v>3.0078692770235747</v>
       </c>
-      <c r="AI20">
-        <f t="shared" si="12"/>
+      <c r="AM20">
+        <f t="shared" si="13"/>
         <v>96.639335516727343</v>
       </c>
+      <c r="AO20">
+        <f t="shared" si="14"/>
+        <v>4.9911485695159481</v>
+      </c>
+      <c r="AP20">
+        <f t="shared" si="15"/>
+        <v>30.497123255874182</v>
+      </c>
     </row>
-    <row r="21" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4</v>
       </c>
@@ -2469,35 +2821,53 @@
         <v>0.42089086771011353</v>
       </c>
       <c r="Z21">
+        <f t="shared" si="10"/>
+        <v>78.094370455966526</v>
+      </c>
+      <c r="AB21">
+        <v>0.7668534517288208</v>
+      </c>
+      <c r="AC21">
+        <v>0.29896694421768188</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="11"/>
+        <v>109.26945050035495</v>
+      </c>
+      <c r="AF21">
         <f t="shared" si="6"/>
-        <v>78.094370455966526</v>
-      </c>
-      <c r="AB21">
+        <v>4.24115539040874</v>
+      </c>
+      <c r="AG21">
         <f t="shared" si="7"/>
-        <v>4.24115539040874</v>
-      </c>
-      <c r="AC21">
+        <v>5.9708498825539227</v>
+      </c>
+      <c r="AI21">
         <f t="shared" si="8"/>
-        <v>5.9708498825539227</v>
-      </c>
-      <c r="AE21">
+        <v>7.1969549306125939</v>
+      </c>
+      <c r="AJ21">
         <f t="shared" si="9"/>
-        <v>7.1969549306125939</v>
-      </c>
-      <c r="AF21">
-        <f t="shared" si="10"/>
         <v>11.912822697205609</v>
       </c>
-      <c r="AH21">
-        <f t="shared" si="11"/>
+      <c r="AL21">
+        <f t="shared" si="12"/>
         <v>3.7909030307840297</v>
       </c>
-      <c r="AI21">
-        <f t="shared" si="12"/>
+      <c r="AM21">
+        <f t="shared" si="13"/>
         <v>28.394761511275902</v>
       </c>
+      <c r="AO21">
+        <f t="shared" si="14"/>
+        <v>4.3799780881292838</v>
+      </c>
+      <c r="AP21">
+        <f t="shared" si="15"/>
+        <v>8.7987113823001444</v>
+      </c>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>4</v>
       </c>
@@ -2568,35 +2938,53 @@
         <v>0.3657647967338562</v>
       </c>
       <c r="Z22">
+        <f t="shared" si="10"/>
+        <v>104.75051263659994</v>
+      </c>
+      <c r="AB22">
+        <v>0.87247419357299805</v>
+      </c>
+      <c r="AC22">
+        <v>0.31184810400009161</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="11"/>
+        <v>119.18429639120367</v>
+      </c>
+      <c r="AF22">
         <f t="shared" si="6"/>
-        <v>104.75051263659994</v>
-      </c>
-      <c r="AB22">
+        <v>3.6510369585172833</v>
+      </c>
+      <c r="AG22">
         <f t="shared" si="7"/>
-        <v>3.6510369585172833</v>
-      </c>
-      <c r="AC22">
+        <v>27.738585587098928</v>
+      </c>
+      <c r="AI22">
         <f t="shared" si="8"/>
-        <v>27.738585587098928</v>
-      </c>
-      <c r="AE22">
+        <v>6.8205515112853758</v>
+      </c>
+      <c r="AJ22">
         <f t="shared" si="9"/>
-        <v>6.8205515112853758</v>
-      </c>
-      <c r="AF22">
-        <f t="shared" si="10"/>
         <v>1.6812185950385681</v>
       </c>
-      <c r="AH22">
-        <f t="shared" si="11"/>
+      <c r="AL22">
+        <f t="shared" si="12"/>
         <v>1.7145019126385515</v>
       </c>
-      <c r="AI22">
-        <f t="shared" si="12"/>
+      <c r="AM22">
+        <f t="shared" si="13"/>
         <v>22.884191746634023</v>
       </c>
+      <c r="AO22">
+        <f t="shared" si="14"/>
+        <v>4.6559652081787339</v>
+      </c>
+      <c r="AP22">
+        <f t="shared" si="15"/>
+        <v>4.7700668570776354</v>
+      </c>
     </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>4</v>
       </c>
@@ -2667,35 +3055,53 @@
         <v>0.45917254686355591</v>
       </c>
       <c r="Z23">
+        <f t="shared" si="10"/>
+        <v>90.460608740819751</v>
+      </c>
+      <c r="AB23">
+        <v>0.95693659782409668</v>
+      </c>
+      <c r="AC23">
+        <v>0.33479788899421692</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="11"/>
+        <v>121.76150522585313</v>
+      </c>
+      <c r="AF23">
         <f t="shared" si="6"/>
-        <v>90.460608740819751</v>
-      </c>
-      <c r="AB23">
+        <v>3.7662477752224741</v>
+      </c>
+      <c r="AG23">
         <f t="shared" si="7"/>
-        <v>3.7662477752224741</v>
-      </c>
-      <c r="AC23">
+        <v>18.874153622672829</v>
+      </c>
+      <c r="AI23">
         <f t="shared" si="8"/>
-        <v>18.874153622672829</v>
-      </c>
-      <c r="AE23">
+        <v>6.0943512639550246</v>
+      </c>
+      <c r="AJ23">
         <f t="shared" si="9"/>
-        <v>6.0943512639550246</v>
-      </c>
-      <c r="AF23">
-        <f t="shared" si="10"/>
         <v>3.2386657140807316</v>
       </c>
-      <c r="AH23">
-        <f t="shared" si="11"/>
+      <c r="AL23">
+        <f t="shared" si="12"/>
         <v>2.5049787463575406</v>
       </c>
-      <c r="AI23">
-        <f t="shared" si="12"/>
+      <c r="AM23">
+        <f t="shared" si="13"/>
         <v>36.123724316244484</v>
       </c>
+      <c r="AO23">
+        <f t="shared" si="14"/>
+        <v>4.3159086267276585</v>
+      </c>
+      <c r="AP23">
+        <f t="shared" si="15"/>
+        <v>0.74769091835144363</v>
+      </c>
     </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>4</v>
       </c>
@@ -2766,35 +3172,53 @@
         <v>0.43526840209960938</v>
       </c>
       <c r="Z24">
+        <f t="shared" si="10"/>
+        <v>92.779072377486202</v>
+      </c>
+      <c r="AB24">
+        <v>0.93430107831954956</v>
+      </c>
+      <c r="AC24">
+        <v>0.32606536149978638</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="11"/>
+        <v>122.06516415830635</v>
+      </c>
+      <c r="AF24">
         <f t="shared" si="6"/>
-        <v>92.779072377486202</v>
-      </c>
-      <c r="AB24">
+        <v>3.8700182309803726</v>
+      </c>
+      <c r="AG24">
         <f t="shared" si="7"/>
-        <v>3.8700182309803726</v>
-      </c>
-      <c r="AC24">
+        <v>18.622274506466983</v>
+      </c>
+      <c r="AI24">
         <f t="shared" si="8"/>
-        <v>18.622274506466983</v>
-      </c>
-      <c r="AE24">
+        <v>6.186491655128358</v>
+      </c>
+      <c r="AJ24">
         <f t="shared" si="9"/>
-        <v>6.186491655128358</v>
-      </c>
-      <c r="AF24">
-        <f t="shared" si="10"/>
         <v>9.9729203544886715</v>
       </c>
-      <c r="AH24">
-        <f t="shared" si="11"/>
+      <c r="AL24">
+        <f t="shared" si="12"/>
         <v>2.9070640744314749</v>
       </c>
-      <c r="AI24">
-        <f t="shared" si="12"/>
+      <c r="AM24">
+        <f t="shared" si="13"/>
         <v>23.459383395623266</v>
       </c>
+      <c r="AO24">
+        <f t="shared" si="14"/>
+        <v>4.3077268303136593</v>
+      </c>
+      <c r="AP24">
+        <f t="shared" si="15"/>
+        <v>7.5149303665230347</v>
+      </c>
     </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4</v>
       </c>
@@ -2865,35 +3289,53 @@
         <v>0.42533254623413091</v>
       </c>
       <c r="Z25">
+        <f t="shared" si="10"/>
+        <v>124.42911766901474</v>
+      </c>
+      <c r="AB25">
+        <v>1.235687851905823</v>
+      </c>
+      <c r="AC25">
+        <v>0.37804639339447021</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="11"/>
+        <v>139.24295547618894</v>
+      </c>
+      <c r="AF25">
         <f t="shared" si="6"/>
-        <v>124.42911766901474</v>
-      </c>
-      <c r="AB25">
+        <v>3.333571561554558</v>
+      </c>
+      <c r="AG25">
         <f t="shared" si="7"/>
-        <v>3.333571561554558</v>
-      </c>
-      <c r="AC25">
+        <v>3.8276534915302731</v>
+      </c>
+      <c r="AI25">
         <f t="shared" si="8"/>
-        <v>3.8276534915302731</v>
-      </c>
-      <c r="AE25">
+        <v>4.9725242900604192</v>
+      </c>
+      <c r="AJ25">
         <f t="shared" si="9"/>
-        <v>4.9725242900604192</v>
-      </c>
-      <c r="AF25">
-        <f t="shared" si="10"/>
         <v>11.333855534515514</v>
       </c>
-      <c r="AH25">
-        <f t="shared" si="11"/>
+      <c r="AL25">
+        <f t="shared" si="12"/>
         <v>3.6272006189838635</v>
       </c>
-      <c r="AI25">
-        <f t="shared" si="12"/>
+      <c r="AM25">
+        <f t="shared" si="13"/>
         <v>1.3347976637674037</v>
       </c>
+      <c r="AO25">
+        <f t="shared" si="14"/>
+        <v>4.1433673178323591</v>
+      </c>
+      <c r="AP25">
+        <f t="shared" si="15"/>
+        <v>9.9310524874394908</v>
+      </c>
     </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>5</v>
       </c>
@@ -2964,35 +3406,53 @@
         <v>0.83409583568572998</v>
       </c>
       <c r="Z26">
+        <f t="shared" si="10"/>
+        <v>78.975106222321756</v>
+      </c>
+      <c r="AB26">
+        <v>1.4664642810821531</v>
+      </c>
+      <c r="AC26">
+        <v>0.53264981508255005</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="11"/>
+        <v>117.28413346787153</v>
+      </c>
+      <c r="AF26">
         <f t="shared" si="6"/>
-        <v>78.975106222321756</v>
-      </c>
-      <c r="AB26">
+        <v>5.5670046427003035</v>
+      </c>
+      <c r="AG26">
         <f t="shared" si="7"/>
-        <v>5.5670046427003035</v>
-      </c>
-      <c r="AC26">
+        <v>51.846682582848466</v>
+      </c>
+      <c r="AI26">
         <f t="shared" si="8"/>
-        <v>51.846682582848466</v>
-      </c>
-      <c r="AE26">
+        <v>8.6569943970423537</v>
+      </c>
+      <c r="AJ26">
         <f t="shared" si="9"/>
-        <v>8.6569943970423537</v>
-      </c>
-      <c r="AF26">
-        <f t="shared" si="10"/>
         <v>16.850973948809944</v>
       </c>
-      <c r="AH26">
-        <f t="shared" si="11"/>
+      <c r="AL26">
+        <f t="shared" si="12"/>
         <v>2.9857465094354811</v>
       </c>
-      <c r="AI26">
-        <f t="shared" si="12"/>
+      <c r="AM26">
+        <f t="shared" si="13"/>
         <v>31.87702942159909</v>
       </c>
+      <c r="AO26">
+        <f t="shared" si="14"/>
+        <v>7.9952141864512827</v>
+      </c>
+      <c r="AP26">
+        <f t="shared" si="15"/>
+        <v>15.783927541969705</v>
+      </c>
     </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>5</v>
       </c>
@@ -3063,35 +3523,53 @@
         <v>0.68571579456329346</v>
       </c>
       <c r="Z27">
+        <f t="shared" si="10"/>
+        <v>85.749713492701531</v>
+      </c>
+      <c r="AB27">
+        <v>1.360906839370728</v>
+      </c>
+      <c r="AC27">
+        <v>0.481172114610672</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="11"/>
+        <v>120.48625363986935</v>
+      </c>
+      <c r="AF27">
         <f t="shared" si="6"/>
-        <v>85.749713492701531</v>
-      </c>
-      <c r="AB27">
+        <v>4.7754027436527533</v>
+      </c>
+      <c r="AG27">
         <f t="shared" si="7"/>
-        <v>4.7754027436527533</v>
-      </c>
-      <c r="AC27">
+        <v>10.576503028221776</v>
+      </c>
+      <c r="AI27">
         <f t="shared" si="8"/>
-        <v>10.576503028221776</v>
-      </c>
-      <c r="AE27">
+        <v>7.8882625771453787</v>
+      </c>
+      <c r="AJ27">
         <f t="shared" si="9"/>
-        <v>7.8882625771453787</v>
-      </c>
-      <c r="AF27">
-        <f t="shared" si="10"/>
         <v>25.926756616179404</v>
       </c>
-      <c r="AH27">
-        <f t="shared" si="11"/>
+      <c r="AL27">
+        <f t="shared" si="12"/>
         <v>5.7957783052578469</v>
       </c>
-      <c r="AI27">
-        <f t="shared" si="12"/>
+      <c r="AM27">
+        <f t="shared" si="13"/>
         <v>7.0360568436709334</v>
       </c>
+      <c r="AO27">
+        <f t="shared" si="14"/>
+        <v>7.11801533096315</v>
+      </c>
+      <c r="AP27">
+        <f t="shared" si="15"/>
+        <v>24.891965126955544</v>
+      </c>
     </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>5</v>
       </c>
@@ -3162,35 +3640,53 @@
         <v>0.82216966152191162</v>
       </c>
       <c r="Z28">
+        <f t="shared" si="10"/>
+        <v>115.79863044329494</v>
+      </c>
+      <c r="AB28">
+        <v>2.1348543167114258</v>
+      </c>
+      <c r="AC28">
+        <v>0.71792900562286377</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="11"/>
+        <v>126.67657095035092</v>
+      </c>
+      <c r="AF28">
         <f t="shared" si="6"/>
-        <v>115.79863044329494</v>
-      </c>
-      <c r="AB28">
+        <v>4.1292825652155356</v>
+      </c>
+      <c r="AG28">
         <f t="shared" si="7"/>
-        <v>4.1292825652155356</v>
-      </c>
-      <c r="AC28">
+        <v>9.3694273270283777</v>
+      </c>
+      <c r="AI28">
         <f t="shared" si="8"/>
-        <v>9.3694273270283777</v>
-      </c>
-      <c r="AE28">
+        <v>9.7161630076689143</v>
+      </c>
+      <c r="AJ28">
         <f t="shared" si="9"/>
-        <v>9.7161630076689143</v>
-      </c>
-      <c r="AF28">
-        <f t="shared" si="10"/>
         <v>12.177243595873316</v>
       </c>
-      <c r="AH28">
-        <f t="shared" si="11"/>
+      <c r="AL28">
+        <f t="shared" si="12"/>
         <v>4.8944341207525381</v>
       </c>
-      <c r="AI28">
-        <f t="shared" si="12"/>
+      <c r="AM28">
+        <f t="shared" si="13"/>
         <v>2.3108090495161324</v>
       </c>
+      <c r="AO28">
+        <f t="shared" si="14"/>
+        <v>9.1512695556650971</v>
+      </c>
+      <c r="AP28">
+        <f t="shared" si="15"/>
+        <v>10.660900246034871</v>
+      </c>
     </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>5</v>
       </c>
@@ -3261,35 +3757,53 @@
         <v>0.5606423020362854</v>
       </c>
       <c r="Z29">
+        <f t="shared" si="10"/>
+        <v>141.06008801625333</v>
+      </c>
+      <c r="AB29">
+        <v>1.78692090511322</v>
+      </c>
+      <c r="AC29">
+        <v>0.52000439167022705</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="11"/>
+        <v>146.38880750782934</v>
+      </c>
+      <c r="AF29">
         <f t="shared" si="6"/>
-        <v>141.06008801625333</v>
-      </c>
-      <c r="AB29">
+        <v>4.1711175630894726</v>
+      </c>
+      <c r="AG29">
         <f t="shared" si="7"/>
-        <v>4.1711175630894726</v>
-      </c>
-      <c r="AC29">
+        <v>11.894673351330512</v>
+      </c>
+      <c r="AI29">
         <f t="shared" si="8"/>
-        <v>11.894673351330512</v>
-      </c>
-      <c r="AE29">
+        <v>9.3075841475347474</v>
+      </c>
+      <c r="AJ29">
         <f t="shared" si="9"/>
-        <v>9.3075841475347474</v>
-      </c>
-      <c r="AF29">
-        <f t="shared" si="10"/>
         <v>1.0964245397153525</v>
       </c>
-      <c r="AH29">
-        <f t="shared" si="11"/>
+      <c r="AL29">
+        <f t="shared" si="12"/>
         <v>5.3562049078084657</v>
       </c>
-      <c r="AI29">
-        <f t="shared" si="12"/>
+      <c r="AM29">
+        <f t="shared" si="13"/>
         <v>8.1068843108919104</v>
       </c>
+      <c r="AO29">
+        <f t="shared" si="14"/>
+        <v>8.9002852351149642</v>
+      </c>
+      <c r="AP29">
+        <f t="shared" si="15"/>
+        <v>0.27080440999365618</v>
+      </c>
     </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>5</v>
       </c>
@@ -3360,35 +3874,53 @@
         <v>0.89298427104949951</v>
       </c>
       <c r="Z30">
+        <f t="shared" si="10"/>
+        <v>130.22495647400189</v>
+      </c>
+      <c r="AB30">
+        <v>2.603691577911377</v>
+      </c>
+      <c r="AC30">
+        <v>0.81541800498962402</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="11"/>
+        <v>136.02501935188423</v>
+      </c>
+      <c r="AF30">
         <f t="shared" si="6"/>
-        <v>130.22495647400189</v>
-      </c>
-      <c r="AB30">
+        <v>4.108458406320378</v>
+      </c>
+      <c r="AG30">
         <f t="shared" si="7"/>
-        <v>4.108458406320378</v>
-      </c>
-      <c r="AC30">
+        <v>9.4979361646505289</v>
+      </c>
+      <c r="AI30">
         <f t="shared" si="8"/>
-        <v>9.4979361646505289</v>
-      </c>
-      <c r="AE30">
+        <v>7.679379325154569</v>
+      </c>
+      <c r="AJ30">
         <f t="shared" si="9"/>
-        <v>7.679379325154569</v>
-      </c>
-      <c r="AF30">
-        <f t="shared" si="10"/>
         <v>5.4270325316265833</v>
       </c>
-      <c r="AH30">
-        <f t="shared" si="11"/>
+      <c r="AL30">
+        <f t="shared" si="12"/>
         <v>2.4135700878091044</v>
       </c>
-      <c r="AI30">
-        <f t="shared" si="12"/>
+      <c r="AM30">
+        <f t="shared" si="13"/>
         <v>6.1131106126267989</v>
       </c>
+      <c r="AO30">
+        <f t="shared" si="14"/>
+        <v>6.9212605758632595</v>
+      </c>
+      <c r="AP30">
+        <f t="shared" si="15"/>
+        <v>3.1040705148152119</v>
+      </c>
     </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>5</v>
       </c>
@@ -3459,35 +3991,53 @@
         <v>2.2499954700469971</v>
       </c>
       <c r="Z31">
+        <f t="shared" si="10"/>
+        <v>81.058063941426369</v>
+      </c>
+      <c r="AB31">
+        <v>3.99755859375</v>
+      </c>
+      <c r="AC31">
+        <v>1.5723417997360229</v>
+      </c>
+      <c r="AD31">
+        <f t="shared" si="11"/>
+        <v>108.3072260477627</v>
+      </c>
+      <c r="AF31">
         <f t="shared" si="6"/>
-        <v>81.058063941426369</v>
-      </c>
-      <c r="AB31">
+        <v>4.1427571444456763</v>
+      </c>
+      <c r="AG31">
         <f t="shared" si="7"/>
-        <v>4.1427571444456763</v>
-      </c>
-      <c r="AC31">
+        <v>1.0708962384233855</v>
+      </c>
+      <c r="AI31">
         <f t="shared" si="8"/>
-        <v>1.0708962384233855</v>
-      </c>
-      <c r="AE31">
+        <v>12.035734332947982</v>
+      </c>
+      <c r="AJ31">
         <f t="shared" si="9"/>
-        <v>12.035734332947982</v>
-      </c>
-      <c r="AF31">
-        <f t="shared" si="10"/>
         <v>32.732478700477159</v>
       </c>
-      <c r="AH31">
-        <f t="shared" si="11"/>
+      <c r="AL31">
+        <f t="shared" si="12"/>
         <v>4.7875550171563797</v>
       </c>
-      <c r="AI31">
-        <f t="shared" si="12"/>
+      <c r="AM31">
+        <f t="shared" si="13"/>
         <v>1.2423530682088899</v>
       </c>
+      <c r="AO31">
+        <f t="shared" si="14"/>
+        <v>11.096217196708555</v>
+      </c>
+      <c r="AP31">
+        <f t="shared" si="15"/>
+        <v>30.986182691655056</v>
+      </c>
     </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>5</v>
       </c>
@@ -3558,35 +4108,53 @@
         <v>1.1225990056991579</v>
       </c>
       <c r="Z32">
+        <f t="shared" si="10"/>
+        <v>127.14180940971868</v>
+      </c>
+      <c r="AB32">
+        <v>3.3571081161499019</v>
+      </c>
+      <c r="AC32">
+        <v>1.039155960083008</v>
+      </c>
+      <c r="AD32">
+        <f t="shared" si="11"/>
+        <v>137.62399164152825</v>
+      </c>
+      <c r="AF32">
         <f t="shared" si="6"/>
-        <v>127.14180940971868</v>
-      </c>
-      <c r="AB32">
+        <v>4.0636118141049433</v>
+      </c>
+      <c r="AG32">
         <f t="shared" si="7"/>
-        <v>4.0636118141049433</v>
-      </c>
-      <c r="AC32">
+        <v>12.452502537060967</v>
+      </c>
+      <c r="AI32">
         <f t="shared" si="8"/>
-        <v>12.452502537060967</v>
-      </c>
-      <c r="AE32">
+        <v>5.0443135475403462</v>
+      </c>
+      <c r="AJ32">
         <f t="shared" si="9"/>
-        <v>5.0443135475403462</v>
-      </c>
-      <c r="AF32">
-        <f t="shared" si="10"/>
         <v>0.35695300008774783</v>
       </c>
-      <c r="AH32">
-        <f t="shared" si="11"/>
+      <c r="AL32">
+        <f t="shared" si="12"/>
         <v>4.2973903420754187</v>
       </c>
-      <c r="AI32">
-        <f t="shared" si="12"/>
+      <c r="AM32">
+        <f t="shared" si="13"/>
         <v>11.690280141195684</v>
       </c>
+      <c r="AO32">
+        <f t="shared" si="14"/>
+        <v>4.1072833799908084</v>
+      </c>
+      <c r="AP32">
+        <f t="shared" si="15"/>
+        <v>3.3883155987471816</v>
+      </c>
     </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>5</v>
       </c>
@@ -3657,35 +4225,53 @@
         <v>1.185233354568481</v>
       </c>
       <c r="Z33">
+        <f t="shared" si="10"/>
+        <v>108.97085931062652</v>
+      </c>
+      <c r="AB33">
+        <v>3.1831469535827641</v>
+      </c>
+      <c r="AC33">
+        <v>1.002339124679565</v>
+      </c>
+      <c r="AD33">
+        <f t="shared" si="11"/>
+        <v>135.2855965174318</v>
+      </c>
+      <c r="AF33">
         <f t="shared" si="6"/>
-        <v>108.97085931062652</v>
-      </c>
-      <c r="AB33">
+        <v>64.403865791268757</v>
+      </c>
+      <c r="AG33">
         <f t="shared" si="7"/>
-        <v>64.403865791268757</v>
-      </c>
-      <c r="AC33">
+        <v>61.302675656108597</v>
+      </c>
+      <c r="AI33">
         <f t="shared" si="8"/>
-        <v>61.302675656108597</v>
-      </c>
-      <c r="AE33">
+        <v>10.38304776048162</v>
+      </c>
+      <c r="AJ33">
         <f t="shared" si="9"/>
-        <v>10.38304776048162</v>
-      </c>
-      <c r="AF33">
-        <f t="shared" si="10"/>
         <v>11.816098571363076</v>
       </c>
-      <c r="AH33">
-        <f t="shared" si="11"/>
+      <c r="AL33">
+        <f t="shared" si="12"/>
         <v>13.829329231751398</v>
       </c>
-      <c r="AI33">
-        <f t="shared" si="12"/>
+      <c r="AM33">
+        <f t="shared" si="13"/>
         <v>7.2609370650209071</v>
       </c>
+      <c r="AO33">
+        <f t="shared" si="14"/>
+        <v>9.5285654393257175</v>
+      </c>
+      <c r="AP33">
+        <f t="shared" si="15"/>
+        <v>9.2905769520755666</v>
+      </c>
     </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>6</v>
       </c>
@@ -3756,35 +4342,53 @@
         <v>1.499395608901978</v>
       </c>
       <c r="Z34">
+        <f t="shared" si="10"/>
+        <v>92.020872099947198</v>
+      </c>
+      <c r="AB34">
+        <v>3.166686058044434</v>
+      </c>
+      <c r="AC34">
+        <v>1.170584559440613</v>
+      </c>
+      <c r="AD34">
+        <f t="shared" si="11"/>
+        <v>115.24226184998859</v>
+      </c>
+      <c r="AF34">
         <f t="shared" si="6"/>
-        <v>92.020872099947198</v>
-      </c>
-      <c r="AB34">
+        <v>4.6146258694841285</v>
+      </c>
+      <c r="AG34">
         <f t="shared" si="7"/>
-        <v>4.6146258694841285</v>
-      </c>
-      <c r="AC34">
+        <v>5.8941098486752752</v>
+      </c>
+      <c r="AI34">
         <f t="shared" si="8"/>
-        <v>5.8941098486752752</v>
-      </c>
-      <c r="AE34">
+        <v>7.5538158290314321</v>
+      </c>
+      <c r="AJ34">
         <f t="shared" si="9"/>
-        <v>7.5538158290314321</v>
-      </c>
-      <c r="AF34">
-        <f t="shared" si="10"/>
         <v>27.960636108879054</v>
       </c>
-      <c r="AH34">
-        <f t="shared" si="11"/>
+      <c r="AL34">
+        <f t="shared" si="12"/>
         <v>4.5792555403731283</v>
       </c>
-      <c r="AI34">
-        <f t="shared" si="12"/>
+      <c r="AM34">
+        <f t="shared" si="13"/>
         <v>5.5498829038124056</v>
       </c>
+      <c r="AO34">
+        <f t="shared" si="14"/>
+        <v>6.7057697302997914</v>
+      </c>
+      <c r="AP34">
+        <f t="shared" si="15"/>
+        <v>26.262389956496811</v>
+      </c>
     </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>6</v>
       </c>
@@ -3855,35 +4459,53 @@
         <v>1.449684262275696</v>
       </c>
       <c r="Z35">
+        <f t="shared" si="10"/>
+        <v>81.916148969306022</v>
+      </c>
+      <c r="AB35">
+        <v>2.5394806861877441</v>
+      </c>
+      <c r="AC35">
+        <v>0.90659594535827637</v>
+      </c>
+      <c r="AD35">
+        <f t="shared" si="11"/>
+        <v>119.32754250002912</v>
+      </c>
+      <c r="AF35">
         <f t="shared" si="6"/>
-        <v>81.916148969306022</v>
-      </c>
-      <c r="AB35">
+        <v>4.1841537820301911</v>
+      </c>
+      <c r="AG35">
         <f t="shared" si="7"/>
-        <v>4.1841537820301911</v>
-      </c>
-      <c r="AC35">
+        <v>12.540884875474065</v>
+      </c>
+      <c r="AI35">
         <f t="shared" si="8"/>
-        <v>12.540884875474065</v>
-      </c>
-      <c r="AE35">
+        <v>13.189348892885949</v>
+      </c>
+      <c r="AJ35">
         <f t="shared" si="9"/>
-        <v>13.189348892885949</v>
-      </c>
-      <c r="AF35">
-        <f t="shared" si="10"/>
         <v>32.156990570620927</v>
       </c>
-      <c r="AH35">
-        <f t="shared" si="11"/>
+      <c r="AL35">
+        <f t="shared" si="12"/>
         <v>3.9480781647184915</v>
       </c>
-      <c r="AI35">
-        <f t="shared" si="12"/>
+      <c r="AM35">
+        <f t="shared" si="13"/>
         <v>10.755921940231957</v>
       </c>
+      <c r="AO35">
+        <f t="shared" si="14"/>
+        <v>12.498081242238852</v>
+      </c>
+      <c r="AP35">
+        <f t="shared" si="15"/>
+        <v>30.736042069044512</v>
+      </c>
     </row>
-    <row r="36" spans="1:35" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>6</v>
       </c>
@@ -3954,35 +4576,53 @@
         <v>1.2581450939178469</v>
       </c>
       <c r="Z36">
+        <f t="shared" si="10"/>
+        <v>87.073665449534516</v>
+      </c>
+      <c r="AB36">
+        <v>2.3517355918884282</v>
+      </c>
+      <c r="AC36">
+        <v>0.79409676790237427</v>
+      </c>
+      <c r="AD36">
+        <f t="shared" si="11"/>
+        <v>126.16085349792556</v>
+      </c>
+      <c r="AF36">
         <f t="shared" si="6"/>
-        <v>87.073665449534516</v>
-      </c>
-      <c r="AB36">
+        <v>4.111652548969329</v>
+      </c>
+      <c r="AG36">
         <f t="shared" si="7"/>
-        <v>4.111652548969329</v>
-      </c>
-      <c r="AC36">
+        <v>29.215118735809014</v>
+      </c>
+      <c r="AI36">
         <f t="shared" si="8"/>
-        <v>29.215118735809014</v>
-      </c>
-      <c r="AE36">
+        <v>11.62158196191813</v>
+      </c>
+      <c r="AJ36">
         <f t="shared" si="9"/>
-        <v>11.62158196191813</v>
-      </c>
-      <c r="AF36">
-        <f t="shared" si="10"/>
         <v>32.226179534574413</v>
       </c>
-      <c r="AH36">
-        <f t="shared" si="11"/>
+      <c r="AL36">
+        <f t="shared" si="12"/>
         <v>2.626764860084589</v>
       </c>
-      <c r="AI36">
-        <f t="shared" si="12"/>
+      <c r="AM36">
+        <f t="shared" si="13"/>
         <v>9.623167545338239</v>
       </c>
+      <c r="AO36">
+        <f t="shared" si="14"/>
+        <v>10.95283635409208</v>
+      </c>
+      <c r="AP36">
+        <f t="shared" si="15"/>
+        <v>30.809726592108188</v>
+      </c>
     </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>6</v>
       </c>
@@ -4053,35 +4693,53 @@
         <v>3.2283375263214111</v>
       </c>
       <c r="Z37">
+        <f t="shared" si="10"/>
+        <v>71.423176056409957</v>
+      </c>
+      <c r="AB37">
+        <v>5.2448768615722656</v>
+      </c>
+      <c r="AC37">
+        <v>2.2004528045654301</v>
+      </c>
+      <c r="AD37">
+        <f t="shared" si="11"/>
+        <v>101.53897918449526</v>
+      </c>
+      <c r="AF37">
         <f t="shared" si="6"/>
-        <v>71.423176056409957</v>
-      </c>
-      <c r="AB37">
+        <v>5.3921708259311494</v>
+      </c>
+      <c r="AG37">
         <f t="shared" si="7"/>
-        <v>5.3921708259311494</v>
-      </c>
-      <c r="AC37">
+        <v>3.2215962646755849</v>
+      </c>
+      <c r="AI37">
         <f t="shared" si="8"/>
-        <v>3.2215962646755849</v>
-      </c>
-      <c r="AE37">
+        <v>9.0008394335198592</v>
+      </c>
+      <c r="AJ37">
         <f t="shared" si="9"/>
-        <v>9.0008394335198592</v>
-      </c>
-      <c r="AF37">
-        <f t="shared" si="10"/>
         <v>32.925755045727094</v>
       </c>
-      <c r="AH37">
-        <f t="shared" si="11"/>
+      <c r="AL37">
+        <f t="shared" si="12"/>
         <v>4.9698462811849566</v>
       </c>
-      <c r="AI37">
-        <f t="shared" si="12"/>
+      <c r="AM37">
+        <f t="shared" si="13"/>
         <v>1.0940541842992144</v>
       </c>
+      <c r="AO37">
+        <f t="shared" si="14"/>
+        <v>7.9151489444271066</v>
+      </c>
+      <c r="AP37">
+        <f t="shared" si="15"/>
+        <v>31.093730676851315</v>
+      </c>
     </row>
-    <row r="38" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>6</v>
       </c>
@@ -4152,35 +4810,53 @@
         <v>0.92695754766464233</v>
       </c>
       <c r="Z38">
+        <f t="shared" si="10"/>
+        <v>134.89709863030177</v>
+      </c>
+      <c r="AB38">
+        <v>2.984399795532227</v>
+      </c>
+      <c r="AC38">
+        <v>0.8655896782875061</v>
+      </c>
+      <c r="AD38">
+        <f t="shared" si="11"/>
+        <v>146.87723469273169</v>
+      </c>
+      <c r="AF38">
         <f t="shared" si="6"/>
-        <v>134.89709863030177</v>
-      </c>
-      <c r="AB38">
+        <v>4.1069042972819183</v>
+      </c>
+      <c r="AG38">
         <f t="shared" si="7"/>
-        <v>4.1069042972819183</v>
-      </c>
-      <c r="AC38">
+        <v>8.2463538883684944</v>
+      </c>
+      <c r="AI38">
         <f t="shared" si="8"/>
-        <v>8.2463538883684944</v>
-      </c>
-      <c r="AE38">
+        <v>4.5647785358512207</v>
+      </c>
+      <c r="AJ38">
         <f t="shared" si="9"/>
-        <v>4.5647785358512207</v>
-      </c>
-      <c r="AF38">
-        <f t="shared" si="10"/>
         <v>4.7502575531394982</v>
       </c>
-      <c r="AH38">
-        <f t="shared" si="11"/>
+      <c r="AL38">
+        <f t="shared" si="12"/>
         <v>5.2669764603840576</v>
       </c>
-      <c r="AI38">
-        <f t="shared" si="12"/>
+      <c r="AM38">
+        <f t="shared" si="13"/>
         <v>5.0674466040966113</v>
       </c>
+      <c r="AO38">
+        <f t="shared" si="14"/>
+        <v>3.6824335797248029</v>
+      </c>
+      <c r="AP38">
+        <f t="shared" si="15"/>
+        <v>1.8883901062617032</v>
+      </c>
     </row>
-    <row r="39" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -4251,35 +4927,53 @@
         <v>3.1004500389099121</v>
       </c>
       <c r="Z39">
+        <f t="shared" si="10"/>
+        <v>80.499949174369604</v>
+      </c>
+      <c r="AB39">
+        <v>5.7626638412475586</v>
+      </c>
+      <c r="AC39">
+        <v>2.3213567733764648</v>
+      </c>
+      <c r="AD39">
+        <f t="shared" si="11"/>
+        <v>105.75257427881903</v>
+      </c>
+      <c r="AF39">
         <f t="shared" si="6"/>
-        <v>80.499949174369604</v>
-      </c>
-      <c r="AB39">
+        <v>5.5950694182904614</v>
+      </c>
+      <c r="AG39">
         <f t="shared" si="7"/>
-        <v>5.5950694182904614</v>
-      </c>
-      <c r="AC39">
+        <v>4.375201898579979</v>
+      </c>
+      <c r="AI39">
         <f t="shared" si="8"/>
-        <v>4.375201898579979</v>
-      </c>
-      <c r="AE39">
+        <v>9.2535244752727763</v>
+      </c>
+      <c r="AJ39">
         <f t="shared" si="9"/>
-        <v>9.2535244752727763</v>
-      </c>
-      <c r="AF39">
-        <f t="shared" si="10"/>
         <v>25.874732147049293</v>
       </c>
-      <c r="AH39">
-        <f t="shared" si="11"/>
+      <c r="AL39">
+        <f t="shared" si="12"/>
         <v>6.6113787200857699</v>
       </c>
-      <c r="AI39">
-        <f t="shared" si="12"/>
+      <c r="AM39">
+        <f t="shared" si="13"/>
         <v>1.8912891948441348</v>
       </c>
+      <c r="AO39">
+        <f t="shared" si="14"/>
+        <v>8.1442259428787533</v>
+      </c>
+      <c r="AP39">
+        <f t="shared" si="15"/>
+        <v>23.71235422207549</v>
+      </c>
     </row>
-    <row r="40" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>6</v>
       </c>
@@ -4350,35 +5044,53 @@
         <v>4.4666094779968262</v>
       </c>
       <c r="Z40">
+        <f t="shared" si="10"/>
+        <v>62.118975973910089</v>
+      </c>
+      <c r="AB40">
+        <v>6.0847935676574707</v>
+      </c>
+      <c r="AC40">
+        <v>2.63520336151123</v>
+      </c>
+      <c r="AD40">
+        <f t="shared" si="11"/>
+        <v>98.365152130502977</v>
+      </c>
+      <c r="AF40">
         <f t="shared" si="6"/>
-        <v>62.118975973910089</v>
-      </c>
-      <c r="AB40">
+        <v>3.0521090890563718</v>
+      </c>
+      <c r="AG40">
         <f t="shared" si="7"/>
-        <v>3.0521090890563718</v>
-      </c>
-      <c r="AC40">
+        <v>0.1765696303101032</v>
+      </c>
+      <c r="AI40">
         <f t="shared" si="8"/>
-        <v>0.1765696303101032</v>
-      </c>
-      <c r="AE40">
+        <v>11.508605394470402</v>
+      </c>
+      <c r="AJ40">
         <f t="shared" si="9"/>
-        <v>11.508605394470402</v>
-      </c>
-      <c r="AF40">
-        <f t="shared" si="10"/>
         <v>39.247013728351071</v>
       </c>
-      <c r="AH40">
-        <f t="shared" si="11"/>
+      <c r="AL40">
+        <f t="shared" si="12"/>
         <v>4.1023803138491441</v>
       </c>
-      <c r="AI40">
-        <f t="shared" si="12"/>
+      <c r="AM40">
+        <f t="shared" si="13"/>
         <v>5.8162440595301304</v>
       </c>
+      <c r="AO40">
+        <f t="shared" si="14"/>
+        <v>10.409706297925874</v>
+      </c>
+      <c r="AP40">
+        <f t="shared" si="15"/>
+        <v>37.570695754395061</v>
+      </c>
     </row>
-    <row r="41" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>7</v>
       </c>
@@ -4449,35 +5161,53 @@
         <v>1.020569920539856</v>
       </c>
       <c r="Z41">
+        <f t="shared" si="10"/>
+        <v>95.345934174494772</v>
+      </c>
+      <c r="AB41">
+        <v>2.1406707763671879</v>
+      </c>
+      <c r="AC41">
+        <v>0.7827262282371521</v>
+      </c>
+      <c r="AD41">
+        <f t="shared" si="11"/>
+        <v>116.50633706187578</v>
+      </c>
+      <c r="AF41">
         <f t="shared" si="6"/>
-        <v>95.345934174494772</v>
-      </c>
-      <c r="AB41">
+        <v>3.8151692737918483</v>
+      </c>
+      <c r="AG41">
         <f t="shared" si="7"/>
-        <v>3.8151692737918483</v>
-      </c>
-      <c r="AC41">
+        <v>14.367041283621774</v>
+      </c>
+      <c r="AI41">
         <f t="shared" si="8"/>
-        <v>14.367041283621774</v>
-      </c>
-      <c r="AE41">
+        <v>7.0450901870574265</v>
+      </c>
+      <c r="AJ41">
         <f t="shared" si="9"/>
-        <v>7.0450901870574265</v>
-      </c>
-      <c r="AF41">
-        <f t="shared" si="10"/>
         <v>12.459226284832726</v>
       </c>
-      <c r="AH41">
-        <f t="shared" si="11"/>
+      <c r="AL41">
+        <f t="shared" si="12"/>
         <v>0.19196763089059499</v>
       </c>
-      <c r="AI41">
-        <f t="shared" si="12"/>
+      <c r="AM41">
+        <f t="shared" si="13"/>
         <v>15.97253673706617</v>
       </c>
+      <c r="AO41">
+        <f t="shared" si="14"/>
+        <v>6.4637430583244004</v>
+      </c>
+      <c r="AP41">
+        <f t="shared" si="15"/>
+        <v>11.05484844068225</v>
+      </c>
     </row>
-    <row r="42" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>7</v>
       </c>
@@ -4548,35 +5278,53 @@
         <v>0.67118847370147705</v>
       </c>
       <c r="Z42">
+        <f t="shared" si="10"/>
+        <v>106.79405149029421</v>
+      </c>
+      <c r="AB42">
+        <v>1.6614412069320681</v>
+      </c>
+      <c r="AC42">
+        <v>0.5406913161277771</v>
+      </c>
+      <c r="AD42">
+        <f t="shared" si="11"/>
+        <v>130.90165513455233</v>
+      </c>
+      <c r="AF42">
         <f t="shared" si="6"/>
-        <v>106.79405149029421</v>
-      </c>
-      <c r="AB42">
+        <v>4.064183722833314</v>
+      </c>
+      <c r="AG42">
         <f t="shared" si="7"/>
-        <v>4.064183722833314</v>
-      </c>
-      <c r="AC42">
+        <v>1.231517598654859</v>
+      </c>
+      <c r="AI42">
         <f t="shared" si="8"/>
-        <v>1.231517598654859</v>
-      </c>
-      <c r="AE42">
+        <v>6.4225073679262144</v>
+      </c>
+      <c r="AJ42">
         <f t="shared" si="9"/>
-        <v>6.4225073679262144</v>
-      </c>
-      <c r="AF42">
-        <f t="shared" si="10"/>
         <v>14.462615407341261</v>
       </c>
-      <c r="AH42">
-        <f t="shared" si="11"/>
+      <c r="AL42">
+        <f t="shared" si="12"/>
         <v>4.8623593295980436</v>
       </c>
-      <c r="AI42">
-        <f t="shared" si="12"/>
+      <c r="AM42">
+        <f t="shared" si="13"/>
         <v>7.2511582910910786</v>
       </c>
+      <c r="AO42">
+        <f t="shared" si="14"/>
+        <v>6.0589614988087677</v>
+      </c>
+      <c r="AP42">
+        <f t="shared" si="15"/>
+        <v>13.601362054333247</v>
+      </c>
     </row>
-    <row r="43" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>7</v>
       </c>
@@ -4647,35 +5395,53 @@
         <v>0.82050019502639771</v>
       </c>
       <c r="Z43">
+        <f t="shared" si="10"/>
+        <v>105.34807371864109</v>
+      </c>
+      <c r="AB43">
+        <v>2.018890380859375</v>
+      </c>
+      <c r="AC43">
+        <v>0.62754464149475098</v>
+      </c>
+      <c r="AD43">
+        <f t="shared" si="11"/>
+        <v>137.04956710281931</v>
+      </c>
+      <c r="AF43">
         <f t="shared" si="6"/>
-        <v>105.34807371864109</v>
-      </c>
-      <c r="AB43">
+        <v>4.3835484569684775</v>
+      </c>
+      <c r="AG43">
         <f t="shared" si="7"/>
-        <v>4.3835484569684775</v>
-      </c>
-      <c r="AC43">
+        <v>2.0707287233986746</v>
+      </c>
+      <c r="AI43">
         <f t="shared" si="8"/>
-        <v>2.0707287233986746</v>
-      </c>
-      <c r="AE43">
+        <v>8.1098062603139454</v>
+      </c>
+      <c r="AJ43">
         <f t="shared" si="9"/>
-        <v>8.1098062603139454</v>
-      </c>
-      <c r="AF43">
-        <f t="shared" si="10"/>
         <v>20.59838133923159</v>
       </c>
-      <c r="AH43">
-        <f t="shared" si="11"/>
+      <c r="AL43">
+        <f t="shared" si="12"/>
         <v>7.0686113379033424</v>
       </c>
-      <c r="AI43">
-        <f t="shared" si="12"/>
+      <c r="AM43">
+        <f t="shared" si="13"/>
         <v>5.7454628088459696</v>
       </c>
+      <c r="AO43">
+        <f t="shared" si="14"/>
+        <v>7.5345616534132454</v>
+      </c>
+      <c r="AP43">
+        <f t="shared" si="15"/>
+        <v>19.12250728235502</v>
+      </c>
     </row>
-    <row r="44" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>7</v>
       </c>
@@ -4746,35 +5512,53 @@
         <v>1.65027928352356</v>
       </c>
       <c r="Z44">
+        <f t="shared" si="10"/>
+        <v>78.259940099466448</v>
+      </c>
+      <c r="AB44">
+        <v>2.799170970916748</v>
+      </c>
+      <c r="AC44">
+        <v>0.96773171424865723</v>
+      </c>
+      <c r="AD44">
+        <f t="shared" si="11"/>
+        <v>123.22079502585675</v>
+      </c>
+      <c r="AF44">
         <f t="shared" si="6"/>
-        <v>78.259940099466448</v>
-      </c>
-      <c r="AB44">
+        <v>3.9787767271886918</v>
+      </c>
+      <c r="AG44">
         <f t="shared" si="7"/>
-        <v>3.9787767271886918</v>
-      </c>
-      <c r="AC44">
+        <v>56.834822043922692</v>
+      </c>
+      <c r="AI44">
         <f t="shared" si="8"/>
-        <v>56.834822043922692</v>
-      </c>
-      <c r="AE44">
+        <v>12.253116385825232</v>
+      </c>
+      <c r="AJ44">
         <f t="shared" si="9"/>
-        <v>12.253116385825232</v>
-      </c>
-      <c r="AF44">
-        <f t="shared" si="10"/>
         <v>12.890475080466416</v>
       </c>
-      <c r="AH44">
-        <f t="shared" si="11"/>
+      <c r="AL44">
+        <f t="shared" si="12"/>
         <v>4.1811554832796123</v>
       </c>
-      <c r="AI44">
-        <f t="shared" si="12"/>
+      <c r="AM44">
+        <f t="shared" si="13"/>
         <v>51.889487668988501</v>
       </c>
+      <c r="AO44">
+        <f t="shared" si="14"/>
+        <v>11.530626709331608</v>
+      </c>
+      <c r="AP44">
+        <f t="shared" si="15"/>
+        <v>10.931273423961601</v>
+      </c>
     </row>
-    <row r="45" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>7</v>
       </c>
@@ -4845,35 +5629,53 @@
         <v>1.1111242771148679</v>
       </c>
       <c r="Z45">
+        <f t="shared" si="10"/>
+        <v>103.65756131273389</v>
+      </c>
+      <c r="AB45">
+        <v>2.5378062725067139</v>
+      </c>
+      <c r="AC45">
+        <v>0.85136544704437256</v>
+      </c>
+      <c r="AD45">
+        <f t="shared" si="11"/>
+        <v>126.98487654141421</v>
+      </c>
+      <c r="AF45">
         <f t="shared" si="6"/>
-        <v>103.65756131273389</v>
-      </c>
-      <c r="AB45">
+        <v>4.7073043691195764</v>
+      </c>
+      <c r="AG45">
         <f t="shared" si="7"/>
-        <v>4.7073043691195764</v>
-      </c>
-      <c r="AC45">
+        <v>3.2827402662356167</v>
+      </c>
+      <c r="AI45">
         <f t="shared" si="8"/>
-        <v>3.2827402662356167</v>
-      </c>
-      <c r="AE45">
+        <v>12.256289422242075</v>
+      </c>
+      <c r="AJ45">
         <f t="shared" si="9"/>
-        <v>12.256289422242075</v>
-      </c>
-      <c r="AF45">
-        <f t="shared" si="10"/>
         <v>19.985462489399133</v>
       </c>
-      <c r="AH45">
-        <f t="shared" si="11"/>
+      <c r="AL45">
+        <f t="shared" si="12"/>
         <v>5.8019507679737607</v>
       </c>
-      <c r="AI45">
-        <f t="shared" si="12"/>
+      <c r="AM45">
+        <f t="shared" si="13"/>
         <v>6.6747577875257162</v>
       </c>
+      <c r="AO45">
+        <f t="shared" si="14"/>
+        <v>11.580855950570907</v>
+      </c>
+      <c r="AP45">
+        <f t="shared" si="15"/>
+        <v>18.263685959641656</v>
+      </c>
     </row>
-    <row r="46" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>7</v>
       </c>
@@ -4944,35 +5746,53 @@
         <v>1.6114711761474609</v>
       </c>
       <c r="Z46">
+        <f t="shared" si="10"/>
+        <v>106.09356539094222</v>
+      </c>
+      <c r="AB46">
+        <v>3.882563591003418</v>
+      </c>
+      <c r="AC46">
+        <v>1.3884246349334719</v>
+      </c>
+      <c r="AD46">
+        <f t="shared" si="11"/>
+        <v>119.12579764822063</v>
+      </c>
+      <c r="AF46">
         <f t="shared" si="6"/>
-        <v>106.09356539094222</v>
-      </c>
-      <c r="AB46">
+        <v>3.8844941859082596</v>
+      </c>
+      <c r="AG46">
         <f t="shared" si="7"/>
-        <v>3.8844941859082596</v>
-      </c>
-      <c r="AC46">
+        <v>10.771184902682798</v>
+      </c>
+      <c r="AI46">
         <f t="shared" si="8"/>
-        <v>10.771184902682798</v>
-      </c>
-      <c r="AE46">
+        <v>8.6174973862561348</v>
+      </c>
+      <c r="AJ46">
         <f t="shared" si="9"/>
-        <v>8.6174973862561348</v>
-      </c>
-      <c r="AF46">
-        <f t="shared" si="10"/>
         <v>11.152065458704092</v>
       </c>
-      <c r="AH46">
-        <f t="shared" si="11"/>
+      <c r="AL46">
+        <f t="shared" si="12"/>
         <v>4.5655778014917621</v>
       </c>
-      <c r="AI46">
-        <f t="shared" si="12"/>
+      <c r="AM46">
+        <f t="shared" si="13"/>
         <v>5.9620710249514079</v>
       </c>
+      <c r="AO46">
+        <f t="shared" si="14"/>
+        <v>7.6745157062892604</v>
+      </c>
+      <c r="AP46">
+        <f t="shared" si="15"/>
+        <v>8.7043243731278288</v>
+      </c>
     </row>
-    <row r="47" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>7</v>
       </c>
@@ -5043,35 +5863,53 @@
         <v>3.1605591773986821</v>
       </c>
       <c r="Z47">
+        <f t="shared" si="10"/>
+        <v>82.916953368222082</v>
+      </c>
+      <c r="AB47">
+        <v>6.0695581436157227</v>
+      </c>
+      <c r="AC47">
+        <v>2.520357608795166</v>
+      </c>
+      <c r="AD47">
+        <f t="shared" si="11"/>
+        <v>102.58986647354102</v>
+      </c>
+      <c r="AF47">
         <f t="shared" si="6"/>
-        <v>82.916953368222082</v>
-      </c>
-      <c r="AB47">
+        <v>6.2759463050099438</v>
+      </c>
+      <c r="AG47">
         <f t="shared" si="7"/>
-        <v>6.2759463050099438</v>
-      </c>
-      <c r="AC47">
+        <v>1.0075647763815918</v>
+      </c>
+      <c r="AI47">
         <f t="shared" si="8"/>
-        <v>1.0075647763815918</v>
-      </c>
-      <c r="AE47">
+        <v>8.267247924898065</v>
+      </c>
+      <c r="AJ47">
         <f t="shared" si="9"/>
-        <v>8.267247924898065</v>
-      </c>
-      <c r="AF47">
-        <f t="shared" si="10"/>
         <v>21.480633804752038</v>
       </c>
-      <c r="AH47">
-        <f t="shared" si="11"/>
+      <c r="AL47">
+        <f t="shared" si="12"/>
         <v>5.8791881967495474</v>
       </c>
-      <c r="AI47">
-        <f t="shared" si="12"/>
+      <c r="AM47">
+        <f t="shared" si="13"/>
         <v>1.2772511743737713</v>
       </c>
+      <c r="AO47">
+        <f t="shared" si="14"/>
+        <v>7.1365033106529534</v>
+      </c>
+      <c r="AP47">
+        <f t="shared" si="15"/>
+        <v>19.237427218407209</v>
+      </c>
     </row>
-    <row r="48" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>7</v>
       </c>
@@ -5142,35 +5980,53 @@
         <v>2.839781761169434</v>
       </c>
       <c r="Z48">
+        <f t="shared" si="10"/>
+        <v>97.890403074605743</v>
+      </c>
+      <c r="AB48">
+        <v>6.284492015838623</v>
+      </c>
+      <c r="AC48">
+        <v>2.3081881999969478</v>
+      </c>
+      <c r="AD48">
+        <f t="shared" si="11"/>
+        <v>115.98678676862052</v>
+      </c>
+      <c r="AF48">
         <f t="shared" si="6"/>
-        <v>97.890403074605743</v>
-      </c>
-      <c r="AB48">
+        <v>5.8006759119568931</v>
+      </c>
+      <c r="AG48">
         <f t="shared" si="7"/>
-        <v>5.8006759119568931</v>
-      </c>
-      <c r="AC48">
+        <v>0.66094489918848365</v>
+      </c>
+      <c r="AI48">
         <f t="shared" si="8"/>
-        <v>0.66094489918848365</v>
-      </c>
-      <c r="AE48">
+        <v>10.651966455341029</v>
+      </c>
+      <c r="AJ48">
         <f t="shared" si="9"/>
-        <v>10.651966455341029</v>
-      </c>
-      <c r="AF48">
-        <f t="shared" si="10"/>
         <v>23.131829170280323</v>
       </c>
-      <c r="AH48">
-        <f t="shared" si="11"/>
+      <c r="AL48">
+        <f t="shared" si="12"/>
         <v>6.0561739259893246</v>
       </c>
-      <c r="AI48">
-        <f t="shared" si="12"/>
+      <c r="AM48">
+        <f t="shared" si="13"/>
         <v>2.3089283714804698</v>
       </c>
+      <c r="AO48">
+        <f t="shared" si="14"/>
+        <v>9.5261867519129453</v>
+      </c>
+      <c r="AP48">
+        <f t="shared" si="15"/>
+        <v>20.596229660568032</v>
+      </c>
     </row>
-    <row r="49" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>7</v>
       </c>
@@ -5241,60 +6097,86 @@
         <v>11.848756790161129</v>
       </c>
       <c r="Z49">
+        <f t="shared" si="10"/>
+        <v>50.379371363106422</v>
+      </c>
+      <c r="AB49">
+        <v>11.912270545959471</v>
+      </c>
+      <c r="AC49">
+        <v>6.7560234069824219</v>
+      </c>
+      <c r="AD49">
+        <f t="shared" si="11"/>
+        <v>75.112628086294393</v>
+      </c>
+      <c r="AF49">
         <f t="shared" si="6"/>
-        <v>50.379371363106422</v>
-      </c>
-      <c r="AB49">
+        <v>21.464885739310454</v>
+      </c>
+      <c r="AG49">
         <f t="shared" si="7"/>
-        <v>21.464885739310454</v>
-      </c>
-      <c r="AC49">
+        <v>1.8976474164133772</v>
+      </c>
+      <c r="AI49">
         <f t="shared" si="8"/>
-        <v>1.8976474164133772</v>
-      </c>
-      <c r="AE49">
+        <v>53.258887095876219</v>
+      </c>
+      <c r="AJ49">
         <f t="shared" si="9"/>
-        <v>53.258887095876219</v>
-      </c>
-      <c r="AF49">
-        <f t="shared" si="10"/>
         <v>86.642853950415457</v>
       </c>
-      <c r="AH49">
-        <f t="shared" si="11"/>
+      <c r="AL49">
+        <f t="shared" si="12"/>
         <v>44.213268359913485</v>
       </c>
-      <c r="AI49">
-        <f t="shared" si="12"/>
+      <c r="AM49">
+        <f t="shared" si="13"/>
         <v>75.990361114161857</v>
       </c>
+      <c r="AO49">
+        <f t="shared" si="14"/>
+        <v>52.574764925712749</v>
+      </c>
+      <c r="AP49">
+        <f t="shared" si="15"/>
+        <v>86.30998296457463</v>
+      </c>
     </row>
-    <row r="50" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:42" x14ac:dyDescent="0.2">
       <c r="T50"/>
       <c r="U50"/>
-      <c r="AB50" s="2">
-        <f>AVERAGE(AB3:AB49)</f>
-        <v>8.4064847937735827</v>
-      </c>
-      <c r="AC50" s="2">
-        <f>AVERAGE(AC3:AC49)</f>
-        <v>15.722195570633666</v>
-      </c>
-      <c r="AE50" s="2">
-        <f>AVERAGE(AE3:AE49)</f>
-        <v>9.3913969030150817</v>
-      </c>
       <c r="AF50" s="2">
         <f>AVERAGE(AF3:AF49)</f>
-        <v>15.782944957207679</v>
-      </c>
-      <c r="AH50" s="2">
-        <f>AVERAGE(AH3:AH49)</f>
-        <v>7.3697050497056269</v>
+        <v>8.4064847937735827</v>
+      </c>
+      <c r="AG50" s="2">
+        <f>AVERAGE(AG3:AG49)</f>
+        <v>15.722195570633666</v>
       </c>
       <c r="AI50" s="2">
         <f>AVERAGE(AI3:AI49)</f>
+        <v>9.3913969030150817</v>
+      </c>
+      <c r="AJ50" s="2">
+        <f>AVERAGE(AJ3:AJ49)</f>
+        <v>15.782944957207679</v>
+      </c>
+      <c r="AL50" s="2">
+        <f>AVERAGE(AL3:AL49)</f>
+        <v>7.3697050497056269</v>
+      </c>
+      <c r="AM50" s="2">
+        <f>AVERAGE(AM3:AM49)</f>
         <v>15.401631173038835</v>
+      </c>
+      <c r="AO50" s="2">
+        <f>AVERAGE(AO3:AO49)</f>
+        <v>6.7611442505092523</v>
+      </c>
+      <c r="AP50" s="2">
+        <f>AVERAGE(AP3:AP49)</f>
+        <v>13.919183654194741</v>
       </c>
     </row>
   </sheetData>

--- a/data_contrast/experiment_data.xlsx
+++ b/data_contrast/experiment_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\86153\Desktop\diploma_project\data_contrast\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3C78CB8-5962-4494-AC49-6F8EA13ADB44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_5B9DBAD71723DC3934E626514465B8B14E9444D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>未使用特征工程相对误差</t>
+  </si>
+  <si>
+    <t>迁移学习相对误差</t>
   </si>
   <si>
     <t>N</t>
@@ -106,10 +109,6 @@
   </si>
   <si>
     <t>R%</t>
-  </si>
-  <si>
-    <t>迁移学习相对误差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -540,108 +539,108 @@
         <v>7</v>
       </c>
       <c r="AO1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="T2" t="s">
         <v>22</v>
       </c>
-      <c r="R2" t="s">
-        <v>20</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" t="s">
         <v>21</v>
       </c>
-      <c r="U2" t="s">
+      <c r="X2" t="s">
         <v>22</v>
       </c>
-      <c r="V2" t="s">
-        <v>20</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z2" t="s">
         <v>21</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="AB2" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AD2" t="s">
         <v>21</v>
       </c>
-      <c r="AC2" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>20</v>
-      </c>
       <c r="AF2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AI2" t="s">
         <v>24</v>
       </c>
-      <c r="AI2" t="s">
-        <v>23</v>
-      </c>
       <c r="AJ2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL2" t="s">
         <v>24</v>
       </c>
-      <c r="AL2" t="s">
-        <v>23</v>
-      </c>
       <c r="AM2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AO2" t="s">
         <v>24</v>
       </c>
-      <c r="AO2" t="s">
-        <v>23</v>
-      </c>
       <c r="AP2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.2">
@@ -715,50 +714,50 @@
         <v>7.0287048816680908E-2</v>
       </c>
       <c r="Z3">
-        <f>6780000*2*3.1415926*X3*0.000001/Y3</f>
+        <f t="shared" ref="Z3:Z49" si="6">6780000*2*3.1415926*X3*0.000001/Y3</f>
         <v>62.541474481504522</v>
       </c>
       <c r="AB3">
-        <v>0.18094408512115481</v>
+        <v>0.17951631546020511</v>
       </c>
       <c r="AC3">
-        <v>9.3563079833984375E-2</v>
+        <v>9.3129992485046387E-2</v>
       </c>
       <c r="AD3">
-        <f>6780000*2*3.1415926*AB3*0.000001/AC3</f>
-        <v>82.385244840350779</v>
+        <f t="shared" ref="AD3:AD49" si="7">6780000*2*3.1415926*AB3*0.000001/AC3</f>
+        <v>82.115267646067764</v>
       </c>
       <c r="AF3">
-        <f t="shared" ref="AF3:AF49" si="6">ABS(P3-L3)/P3*100</f>
+        <f t="shared" ref="AF3:AF49" si="8">ABS(P3-L3)/P3*100</f>
         <v>16.775700934579447</v>
       </c>
       <c r="AG3">
-        <f t="shared" ref="AG3:AG49" si="7">ABS(Q3-M3)/Q3*100</f>
+        <f t="shared" ref="AG3:AG49" si="9">ABS(Q3-M3)/Q3*100</f>
         <v>8.4790593453302225</v>
       </c>
       <c r="AI3">
-        <f t="shared" ref="AI3:AI49" si="8">ABS(P3-T3)/P3*100</f>
+        <f t="shared" ref="AI3:AI49" si="10">ABS(P3-T3)/P3*100</f>
         <v>20.083951780304801</v>
       </c>
       <c r="AJ3">
-        <f t="shared" ref="AJ3:AJ49" si="9">ABS(Q3-U3)/Q3*100</f>
+        <f t="shared" ref="AJ3:AJ49" si="11">ABS(Q3-U3)/Q3*100</f>
         <v>11.573420399486485</v>
       </c>
       <c r="AL3">
-        <f>ABS(P3-X3)/P3*100</f>
+        <f t="shared" ref="AL3:AL49" si="12">ABS(P3-X3)/P3*100</f>
         <v>42.596177817133736</v>
       </c>
       <c r="AM3">
-        <f>ABS(Q3-Y3)/Q3*100</f>
+        <f t="shared" ref="AM3:AM49" si="13">ABS(Q3-Y3)/Q3*100</f>
         <v>18.816502094434028</v>
       </c>
       <c r="AO3">
-        <f>ABS(P3-AB3)/P3*100</f>
-        <v>0.65870333842612916</v>
+        <f t="shared" ref="AO3:AO49" si="14">ABS(P3-AB3)/P3*100</f>
+        <v>0.13556104794998733</v>
       </c>
       <c r="AP3">
-        <f>ABS(Q3-AC3)/Q3*100</f>
-        <v>8.0679616461276229</v>
+        <f t="shared" ref="AP3:AP49" si="15">ABS(Q3-AC3)/Q3*100</f>
+        <v>7.5677337026108074</v>
       </c>
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.2">
@@ -832,50 +831,50 @@
         <v>0.12292706966400151</v>
       </c>
       <c r="Z4">
-        <f t="shared" ref="Z3:Z49" si="10">6780000*2*3.1415926*X4*0.000001/Y4</f>
+        <f t="shared" si="6"/>
         <v>60.488955775686705</v>
       </c>
       <c r="AB4">
-        <v>0.20330154895782471</v>
+        <v>0.20203375816345209</v>
       </c>
       <c r="AC4">
-        <v>0.1234317123889923</v>
+        <v>0.1231200098991394</v>
       </c>
       <c r="AD4">
-        <f t="shared" ref="AD4:AD49" si="11">6780000*2*3.1415926*AB4*0.000001/AC4</f>
-        <v>70.165478018870672</v>
+        <f t="shared" si="7"/>
+        <v>69.904455231761432</v>
       </c>
       <c r="AF4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>28.588364034287789</v>
       </c>
       <c r="AG4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>18.069933120093047</v>
       </c>
       <c r="AI4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>23.993750642995305</v>
       </c>
       <c r="AJ4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>22.117254664018169</v>
       </c>
       <c r="AL4">
-        <f t="shared" ref="AL3:AL49" si="12">ABS(P4-X4)/P4*100</f>
+        <f t="shared" si="12"/>
         <v>20.414156359780915</v>
       </c>
       <c r="AM4">
-        <f t="shared" ref="AM3:AM49" si="13">ABS(Q4-Y4)/Q4*100</f>
+        <f t="shared" si="13"/>
         <v>10.637489339923293</v>
       </c>
       <c r="AO4">
-        <f t="shared" ref="AO4:AO49" si="14">ABS(P4-AB4)/P4*100</f>
-        <v>7.3036891492683207</v>
+        <f t="shared" si="14"/>
+        <v>7.8817444084205253</v>
       </c>
       <c r="AP4">
-        <f t="shared" ref="AP4:AP49" si="15">ABS(Q4-AC4)/Q4*100</f>
-        <v>10.270636530246941</v>
+        <f t="shared" si="15"/>
+        <v>10.497230372826829</v>
       </c>
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.2">
@@ -949,33 +948,33 @@
         <v>0.1150748729705811</v>
       </c>
       <c r="Z5">
+        <f t="shared" si="6"/>
+        <v>73.845735323464666</v>
+      </c>
+      <c r="AB5">
+        <v>0.2281389236450195</v>
+      </c>
+      <c r="AC5">
+        <v>0.1241274476051331</v>
+      </c>
+      <c r="AD5">
+        <f t="shared" si="7"/>
+        <v>78.29627808958864</v>
+      </c>
+      <c r="AF5">
+        <f t="shared" si="8"/>
+        <v>12.55538395464696</v>
+      </c>
+      <c r="AG5">
+        <f t="shared" si="9"/>
+        <v>15.898569066710754</v>
+      </c>
+      <c r="AI5">
         <f t="shared" si="10"/>
-        <v>73.845735323464666</v>
-      </c>
-      <c r="AB5">
-        <v>0.22940981388092041</v>
-      </c>
-      <c r="AC5">
-        <v>0.12445616722106929</v>
-      </c>
-      <c r="AD5">
+        <v>16.941987302905002</v>
+      </c>
+      <c r="AJ5">
         <f t="shared" si="11"/>
-        <v>78.524490131627033</v>
-      </c>
-      <c r="AF5">
-        <f t="shared" si="6"/>
-        <v>12.55538395464696</v>
-      </c>
-      <c r="AG5">
-        <f t="shared" si="7"/>
-        <v>15.898569066710754</v>
-      </c>
-      <c r="AI5">
-        <f t="shared" si="8"/>
-        <v>16.941987302905002</v>
-      </c>
-      <c r="AJ5">
-        <f t="shared" si="9"/>
         <v>10.469975384383234</v>
       </c>
       <c r="AL5">
@@ -988,11 +987,11 @@
       </c>
       <c r="AO5">
         <f t="shared" si="14"/>
-        <v>1.4731945194466507</v>
+        <v>2.0190157855095725</v>
       </c>
       <c r="AP5">
         <f t="shared" si="15"/>
-        <v>2.8818444416543776</v>
+        <v>2.6101079648946883</v>
       </c>
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.2">
@@ -1066,33 +1065,33 @@
         <v>7.3583334684371948E-2</v>
       </c>
       <c r="Z6">
+        <f t="shared" si="6"/>
+        <v>123.61693336601557</v>
+      </c>
+      <c r="AB6">
+        <v>0.26345419883728027</v>
+      </c>
+      <c r="AC6">
+        <v>0.10082051157951349</v>
+      </c>
+      <c r="AD6">
+        <f t="shared" si="7"/>
+        <v>111.31809936484808</v>
+      </c>
+      <c r="AF6">
+        <f t="shared" si="8"/>
+        <v>10.34079191787518</v>
+      </c>
+      <c r="AG6">
+        <f t="shared" si="9"/>
+        <v>16.74820196518753</v>
+      </c>
+      <c r="AI6">
         <f t="shared" si="10"/>
-        <v>123.61693336601557</v>
-      </c>
-      <c r="AB6">
-        <v>0.26487672328948969</v>
-      </c>
-      <c r="AC6">
-        <v>0.10129693150520321</v>
-      </c>
-      <c r="AD6">
+        <v>6.4738342150892958</v>
+      </c>
+      <c r="AJ6">
         <f t="shared" si="11"/>
-        <v>111.39278449839496</v>
-      </c>
-      <c r="AF6">
-        <f t="shared" si="6"/>
-        <v>10.34079191787518</v>
-      </c>
-      <c r="AG6">
-        <f t="shared" si="7"/>
-        <v>16.74820196518753</v>
-      </c>
-      <c r="AI6">
-        <f t="shared" si="8"/>
-        <v>6.4738342150892958</v>
-      </c>
-      <c r="AJ6">
-        <f t="shared" si="9"/>
         <v>13.762896671907415</v>
       </c>
       <c r="AL6">
@@ -1105,11 +1104,11 @@
       </c>
       <c r="AO6">
         <f t="shared" si="14"/>
-        <v>7.9015493276395983</v>
+        <v>7.3220624235295215</v>
       </c>
       <c r="AP6">
         <f t="shared" si="15"/>
-        <v>2.9304375491075416</v>
+        <v>2.446334914608328</v>
       </c>
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.2">
@@ -1183,33 +1182,33 @@
         <v>0.17784106731414789</v>
       </c>
       <c r="Z7">
+        <f t="shared" si="6"/>
+        <v>96.06964517307199</v>
+      </c>
+      <c r="AB7">
+        <v>0.43852066993713379</v>
+      </c>
+      <c r="AC7">
+        <v>0.2008648216724396</v>
+      </c>
+      <c r="AD7">
+        <f t="shared" si="7"/>
+        <v>93.002739249444716</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="8"/>
+        <v>7.4506165113799661</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="9"/>
+        <v>15.196523447967838</v>
+      </c>
+      <c r="AI7">
         <f t="shared" si="10"/>
-        <v>96.06964517307199</v>
-      </c>
-      <c r="AB7">
-        <v>0.43945407867431641</v>
-      </c>
-      <c r="AC7">
-        <v>0.2010308504104614</v>
-      </c>
-      <c r="AD7">
+        <v>5.2598358930215614</v>
+      </c>
+      <c r="AJ7">
         <f t="shared" si="11"/>
-        <v>93.1237260565414</v>
-      </c>
-      <c r="AF7">
-        <f t="shared" si="6"/>
-        <v>7.4506165113799661</v>
-      </c>
-      <c r="AG7">
-        <f t="shared" si="7"/>
-        <v>15.196523447967838</v>
-      </c>
-      <c r="AI7">
-        <f t="shared" si="8"/>
-        <v>5.2598358930215614</v>
-      </c>
-      <c r="AJ7">
-        <f t="shared" si="9"/>
         <v>16.270421838696471</v>
       </c>
       <c r="AL7">
@@ -1222,11 +1221,11 @@
       </c>
       <c r="AO7">
         <f t="shared" si="14"/>
-        <v>1.8527971710741196</v>
+        <v>1.636459912189723</v>
       </c>
       <c r="AP7">
         <f t="shared" si="15"/>
-        <v>10.214001603188294</v>
+        <v>10.288154679571409</v>
       </c>
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.2">
@@ -1300,33 +1299,33 @@
         <v>0.12534976005554199</v>
       </c>
       <c r="Z8">
+        <f t="shared" si="6"/>
+        <v>125.18964287226396</v>
+      </c>
+      <c r="AB8">
+        <v>0.40489709377288818</v>
+      </c>
+      <c r="AC8">
+        <v>0.13737738132476809</v>
+      </c>
+      <c r="AD8">
+        <f t="shared" si="7"/>
+        <v>125.55643636178606</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="8"/>
+        <v>6.6397479333587723</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="9"/>
+        <v>9.246349758162026</v>
+      </c>
+      <c r="AI8">
         <f t="shared" si="10"/>
-        <v>125.18964287226396</v>
-      </c>
-      <c r="AB8">
-        <v>0.4061812162399292</v>
-      </c>
-      <c r="AC8">
-        <v>0.1378190219402313</v>
-      </c>
-      <c r="AD8">
+        <v>4.7630421156860798</v>
+      </c>
+      <c r="AJ8">
         <f t="shared" si="11"/>
-        <v>125.55101468412542</v>
-      </c>
-      <c r="AF8">
-        <f t="shared" si="6"/>
-        <v>6.6397479333587723</v>
-      </c>
-      <c r="AG8">
-        <f t="shared" si="7"/>
-        <v>9.246349758162026</v>
-      </c>
-      <c r="AI8">
-        <f t="shared" si="8"/>
-        <v>4.7630421156860798</v>
-      </c>
-      <c r="AJ8">
-        <f t="shared" si="9"/>
         <v>7.1630404894989352</v>
       </c>
       <c r="AL8">
@@ -1339,11 +1338,11 @@
       </c>
       <c r="AO8">
         <f t="shared" si="14"/>
-        <v>3.3145660027799053</v>
+        <v>2.98794194910039</v>
       </c>
       <c r="AP8">
         <f t="shared" si="15"/>
-        <v>4.1558509221820605</v>
+        <v>3.8220838306893148</v>
       </c>
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.2">
@@ -1417,33 +1416,33 @@
         <v>0.14516684412956241</v>
       </c>
       <c r="Z9">
+        <f t="shared" si="6"/>
+        <v>126.35271262872628</v>
+      </c>
+      <c r="AB9">
+        <v>0.45896708965301508</v>
+      </c>
+      <c r="AC9">
+        <v>0.1516456604003906</v>
+      </c>
+      <c r="AD9">
+        <f t="shared" si="7"/>
+        <v>128.93211697480956</v>
+      </c>
+      <c r="AF9">
+        <f t="shared" si="8"/>
+        <v>6.3261210478370122</v>
+      </c>
+      <c r="AG9">
+        <f t="shared" si="9"/>
+        <v>9.6468174347981375</v>
+      </c>
+      <c r="AI9">
         <f t="shared" si="10"/>
-        <v>126.35271262872628</v>
-      </c>
-      <c r="AB9">
-        <v>0.46019577980041498</v>
-      </c>
-      <c r="AC9">
-        <v>0.15207195281982419</v>
-      </c>
-      <c r="AD9">
+        <v>4.5072856390036993</v>
+      </c>
+      <c r="AJ9">
         <f t="shared" si="11"/>
-        <v>128.91488441418622</v>
-      </c>
-      <c r="AF9">
-        <f t="shared" si="6"/>
-        <v>6.3261210478370122</v>
-      </c>
-      <c r="AG9">
-        <f t="shared" si="7"/>
-        <v>9.6468174347981375</v>
-      </c>
-      <c r="AI9">
-        <f t="shared" si="8"/>
-        <v>4.5072856390036993</v>
-      </c>
-      <c r="AJ9">
-        <f t="shared" si="9"/>
         <v>1.6407729472888877</v>
       </c>
       <c r="AL9">
@@ -1456,11 +1455,11 @@
       </c>
       <c r="AO9">
         <f t="shared" si="14"/>
-        <v>2.2498233164652071</v>
+        <v>1.9768235281211934</v>
       </c>
       <c r="AP9">
         <f t="shared" si="15"/>
-        <v>8.6616311681487677</v>
+        <v>8.3570277959204056</v>
       </c>
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.2">
@@ -1534,33 +1533,33 @@
         <v>0.19915902614593509</v>
       </c>
       <c r="Z10">
+        <f t="shared" si="6"/>
+        <v>103.1091976044388</v>
+      </c>
+      <c r="AB10">
+        <v>0.5416337251663208</v>
+      </c>
+      <c r="AC10">
+        <v>0.21820878982543951</v>
+      </c>
+      <c r="AD10">
+        <f t="shared" si="7"/>
+        <v>105.7409023609294</v>
+      </c>
+      <c r="AF10">
+        <f t="shared" si="8"/>
+        <v>6.5910470646425496</v>
+      </c>
+      <c r="AG10">
+        <f t="shared" si="9"/>
+        <v>3.208589999051136</v>
+      </c>
+      <c r="AI10">
         <f t="shared" si="10"/>
-        <v>103.1091976044388</v>
-      </c>
-      <c r="AB10">
-        <v>0.54251551628112793</v>
-      </c>
-      <c r="AC10">
-        <v>0.21839013695716861</v>
-      </c>
-      <c r="AD10">
+        <v>2.1571488865378976</v>
+      </c>
+      <c r="AJ10">
         <f t="shared" si="11"/>
-        <v>105.82510253849645</v>
-      </c>
-      <c r="AF10">
-        <f t="shared" si="6"/>
-        <v>6.5910470646425496</v>
-      </c>
-      <c r="AG10">
-        <f t="shared" si="7"/>
-        <v>3.208589999051136</v>
-      </c>
-      <c r="AI10">
-        <f t="shared" si="8"/>
-        <v>2.1571488865378976</v>
-      </c>
-      <c r="AJ10">
-        <f t="shared" si="9"/>
         <v>2.4128340398895518</v>
       </c>
       <c r="AL10">
@@ -1573,11 +1572,11 @@
       </c>
       <c r="AO10">
         <f t="shared" si="14"/>
-        <v>3.2065434465487033</v>
+        <v>3.0387941190733141</v>
       </c>
       <c r="AP10">
         <f t="shared" si="15"/>
-        <v>3.610464444998867</v>
+        <v>3.5244282310653352</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -1651,33 +1650,33 @@
         <v>0.19164204597473139</v>
       </c>
       <c r="Z11">
+        <f t="shared" si="6"/>
+        <v>85.2921282014794</v>
+      </c>
+      <c r="AB11">
+        <v>0.40403127670288091</v>
+      </c>
+      <c r="AC11">
+        <v>0.20277965068817139</v>
+      </c>
+      <c r="AD11">
+        <f t="shared" si="7"/>
+        <v>84.878983537152635</v>
+      </c>
+      <c r="AF11">
+        <f t="shared" si="8"/>
+        <v>27.101478404108427</v>
+      </c>
+      <c r="AG11">
+        <f t="shared" si="9"/>
+        <v>78.44825359088658</v>
+      </c>
+      <c r="AI11">
         <f t="shared" si="10"/>
-        <v>85.2921282014794</v>
-      </c>
-      <c r="AB11">
-        <v>0.40494430065155029</v>
-      </c>
-      <c r="AC11">
-        <v>0.20291003584861761</v>
-      </c>
-      <c r="AD11">
+        <v>9.5181537943377883</v>
+      </c>
+      <c r="AJ11">
         <f t="shared" si="11"/>
-        <v>85.016127351867141</v>
-      </c>
-      <c r="AF11">
-        <f t="shared" si="6"/>
-        <v>27.101478404108427</v>
-      </c>
-      <c r="AG11">
-        <f t="shared" si="7"/>
-        <v>78.44825359088658</v>
-      </c>
-      <c r="AI11">
-        <f t="shared" si="8"/>
-        <v>9.5181537943377883</v>
-      </c>
-      <c r="AJ11">
-        <f t="shared" si="9"/>
         <v>6.2759472392111952</v>
       </c>
       <c r="AL11">
@@ -1690,11 +1689,11 @@
       </c>
       <c r="AO11">
         <f t="shared" si="14"/>
-        <v>1.9054042655094878</v>
+        <v>2.1265771897771604</v>
       </c>
       <c r="AP11">
         <f t="shared" si="15"/>
-        <v>0.50026540298049182</v>
+        <v>0.43568632400762286</v>
       </c>
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.2">
@@ -1768,33 +1767,33 @@
         <v>0.1967687010765076</v>
       </c>
       <c r="Z12">
+        <f t="shared" si="6"/>
+        <v>104.30115859472703</v>
+      </c>
+      <c r="AB12">
+        <v>0.51900899410247803</v>
+      </c>
+      <c r="AC12">
+        <v>0.21400395035743711</v>
+      </c>
+      <c r="AD12">
+        <f t="shared" si="7"/>
+        <v>103.31482599859461</v>
+      </c>
+      <c r="AF12">
+        <f t="shared" si="8"/>
+        <v>8.2197520250368168</v>
+      </c>
+      <c r="AG12">
+        <f t="shared" si="9"/>
+        <v>4.0801746403786927</v>
+      </c>
+      <c r="AI12">
         <f t="shared" si="10"/>
-        <v>104.30115859472703</v>
-      </c>
-      <c r="AB12">
-        <v>0.51990699768066406</v>
-      </c>
-      <c r="AC12">
-        <v>0.2141865789890289</v>
-      </c>
-      <c r="AD12">
+        <v>9.5752330521596338</v>
+      </c>
+      <c r="AJ12">
         <f t="shared" si="11"/>
-        <v>103.40533915458242</v>
-      </c>
-      <c r="AF12">
-        <f t="shared" si="6"/>
-        <v>8.2197520250368168</v>
-      </c>
-      <c r="AG12">
-        <f t="shared" si="7"/>
-        <v>4.0801746403786927</v>
-      </c>
-      <c r="AI12">
-        <f t="shared" si="8"/>
-        <v>9.5752330521596338</v>
-      </c>
-      <c r="AJ12">
-        <f t="shared" si="9"/>
         <v>7.4866964654989694</v>
       </c>
       <c r="AL12">
@@ -1807,11 +1806,11 @@
       </c>
       <c r="AO12">
         <f t="shared" si="14"/>
-        <v>4.2881079380220832</v>
+        <v>4.4534252388663456</v>
       </c>
       <c r="AP12">
         <f t="shared" si="15"/>
-        <v>1.5641440373965267</v>
+        <v>1.6480764936637253</v>
       </c>
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.2">
@@ -1885,33 +1884,33 @@
         <v>0.19587200880050659</v>
       </c>
       <c r="Z13">
+        <f t="shared" si="6"/>
+        <v>108.4025748000511</v>
+      </c>
+      <c r="AB13">
+        <v>0.51757586002349854</v>
+      </c>
+      <c r="AC13">
+        <v>0.2001320421695709</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="7"/>
+        <v>110.17091091275492</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="8"/>
+        <v>24.696333988732178</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="9"/>
+        <v>84.008394398145867</v>
+      </c>
+      <c r="AI13">
         <f t="shared" si="10"/>
-        <v>108.4025748000511</v>
-      </c>
-      <c r="AB13">
-        <v>0.51855742931365967</v>
-      </c>
-      <c r="AC13">
-        <v>0.20038458704948431</v>
-      </c>
-      <c r="AD13">
+        <v>7.4038338849606298</v>
+      </c>
+      <c r="AJ13">
         <f t="shared" si="11"/>
-        <v>110.24073538496873</v>
-      </c>
-      <c r="AF13">
-        <f t="shared" si="6"/>
-        <v>24.696333988732178</v>
-      </c>
-      <c r="AG13">
-        <f t="shared" si="7"/>
-        <v>84.008394398145867</v>
-      </c>
-      <c r="AI13">
-        <f t="shared" si="8"/>
-        <v>7.4038338849606298</v>
-      </c>
-      <c r="AJ13">
-        <f t="shared" si="9"/>
         <v>7.6740100624892689</v>
       </c>
       <c r="AL13">
@@ -1924,11 +1923,11 @@
       </c>
       <c r="AO13">
         <f t="shared" si="14"/>
-        <v>1.9629014040042914</v>
+        <v>2.1484743026621982</v>
       </c>
       <c r="AP13">
         <f t="shared" si="15"/>
-        <v>1.1861595495417376</v>
+        <v>1.3106947238173001</v>
       </c>
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.2">
@@ -2002,33 +2001,33 @@
         <v>0.18338131904602051</v>
       </c>
       <c r="Z14">
+        <f t="shared" si="6"/>
+        <v>119.34276154239784</v>
+      </c>
+      <c r="AB14">
+        <v>0.54496908187866211</v>
+      </c>
+      <c r="AC14">
+        <v>0.19033339619636541</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="7"/>
+        <v>121.97376280058538</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="8"/>
+        <v>6.0041675967596806</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="9"/>
+        <v>11.413465450903926</v>
+      </c>
+      <c r="AI14">
         <f t="shared" si="10"/>
-        <v>119.34276154239784</v>
-      </c>
-      <c r="AB14">
-        <v>0.54602009057998657</v>
-      </c>
-      <c r="AC14">
-        <v>0.19066014885902399</v>
-      </c>
-      <c r="AD14">
+        <v>6.7791510443768983</v>
+      </c>
+      <c r="AJ14">
         <f t="shared" si="11"/>
-        <v>121.9995558903878</v>
-      </c>
-      <c r="AF14">
-        <f t="shared" si="6"/>
-        <v>6.0041675967596806</v>
-      </c>
-      <c r="AG14">
-        <f t="shared" si="7"/>
-        <v>11.413465450903926</v>
-      </c>
-      <c r="AI14">
-        <f t="shared" si="8"/>
-        <v>6.7791510443768983</v>
-      </c>
-      <c r="AJ14">
-        <f t="shared" si="9"/>
         <v>6.4718050276391716</v>
       </c>
       <c r="AL14">
@@ -2041,11 +2040,11 @@
       </c>
       <c r="AO14">
         <f t="shared" si="14"/>
-        <v>1.7065543510375196</v>
+        <v>1.8957548373245516</v>
       </c>
       <c r="AP14">
         <f t="shared" si="15"/>
-        <v>0.49024870027090212</v>
+        <v>0.31802888123407064</v>
       </c>
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.2">
@@ -2119,33 +2118,33 @@
         <v>0.1948093771934509</v>
       </c>
       <c r="Z15">
+        <f t="shared" si="6"/>
+        <v>131.18929942431464</v>
+      </c>
+      <c r="AB15">
+        <v>0.64522397518157959</v>
+      </c>
+      <c r="AC15">
+        <v>0.2028327286243439</v>
+      </c>
+      <c r="AD15">
+        <f t="shared" si="7"/>
+        <v>135.51333025149384</v>
+      </c>
+      <c r="AF15">
+        <f t="shared" si="8"/>
+        <v>5.9301236894988509</v>
+      </c>
+      <c r="AG15">
+        <f t="shared" si="9"/>
+        <v>11.259286029303674</v>
+      </c>
+      <c r="AI15">
         <f t="shared" si="10"/>
-        <v>131.18929942431464</v>
-      </c>
-      <c r="AB15">
-        <v>0.64625465869903564</v>
-      </c>
-      <c r="AC15">
-        <v>0.20320022106170649</v>
-      </c>
-      <c r="AD15">
+        <v>3.3348653148360947</v>
+      </c>
+      <c r="AJ15">
         <f t="shared" si="11"/>
-        <v>135.4843292463172</v>
-      </c>
-      <c r="AF15">
-        <f t="shared" si="6"/>
-        <v>5.9301236894988509</v>
-      </c>
-      <c r="AG15">
-        <f t="shared" si="7"/>
-        <v>11.259286029303674</v>
-      </c>
-      <c r="AI15">
-        <f t="shared" si="8"/>
-        <v>3.3348653148360947</v>
-      </c>
-      <c r="AJ15">
-        <f t="shared" si="9"/>
         <v>6.5236218820193148</v>
       </c>
       <c r="AL15">
@@ -2158,11 +2157,11 @@
       </c>
       <c r="AO15">
         <f t="shared" si="14"/>
-        <v>0.67369630630063149</v>
+        <v>0.51313619578140757</v>
       </c>
       <c r="AP15">
         <f t="shared" si="15"/>
-        <v>0.42621597407434403</v>
+        <v>0.60629753303087253</v>
       </c>
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.2">
@@ -2236,33 +2235,33 @@
         <v>0.23711210489273071</v>
       </c>
       <c r="Z16">
+        <f t="shared" si="6"/>
+        <v>136.55507160516052</v>
+      </c>
+      <c r="AB16">
+        <v>0.7855302095413208</v>
+      </c>
+      <c r="AC16">
+        <v>0.2339606583118439</v>
+      </c>
+      <c r="AD16">
+        <f t="shared" si="7"/>
+        <v>143.03081447785019</v>
+      </c>
+      <c r="AF16">
+        <f t="shared" si="8"/>
+        <v>5.0966208925944017</v>
+      </c>
+      <c r="AG16">
+        <f t="shared" si="9"/>
+        <v>7.6703476337903513</v>
+      </c>
+      <c r="AI16">
         <f t="shared" si="10"/>
-        <v>136.55507160516052</v>
-      </c>
-      <c r="AB16">
-        <v>0.7864534854888916</v>
-      </c>
-      <c r="AC16">
-        <v>0.23431894183158869</v>
-      </c>
-      <c r="AD16">
+        <v>1.3699983295641387</v>
+      </c>
+      <c r="AJ16">
         <f t="shared" si="11"/>
-        <v>142.97996911215265</v>
-      </c>
-      <c r="AF16">
-        <f t="shared" si="6"/>
-        <v>5.0966208925944017</v>
-      </c>
-      <c r="AG16">
-        <f t="shared" si="7"/>
-        <v>7.6703476337903513</v>
-      </c>
-      <c r="AI16">
-        <f t="shared" si="8"/>
-        <v>1.3699983295641387</v>
-      </c>
-      <c r="AJ16">
-        <f t="shared" si="9"/>
         <v>1.2756880170104354</v>
       </c>
       <c r="AL16">
@@ -2275,11 +2274,11 @@
       </c>
       <c r="AO16">
         <f t="shared" si="14"/>
-        <v>1.5014436241826035</v>
+        <v>1.382283567966863</v>
       </c>
       <c r="AP16">
         <f t="shared" si="15"/>
-        <v>3.6350914779251191</v>
+        <v>3.4766290631773131</v>
       </c>
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.2">
@@ -2353,33 +2352,33 @@
         <v>0.29882404208183289</v>
       </c>
       <c r="Z17">
+        <f t="shared" si="6"/>
+        <v>132.23652323777208</v>
+      </c>
+      <c r="AB17">
+        <v>0.97414505481719971</v>
+      </c>
+      <c r="AC17">
+        <v>0.29330429434776312</v>
+      </c>
+      <c r="AD17">
+        <f t="shared" si="7"/>
+        <v>141.48642179211612</v>
+      </c>
+      <c r="AF17">
+        <f t="shared" si="8"/>
+        <v>4.9989251598038535</v>
+      </c>
+      <c r="AG17">
+        <f t="shared" si="9"/>
+        <v>5.7436367236723651</v>
+      </c>
+      <c r="AI17">
         <f t="shared" si="10"/>
-        <v>132.23652323777208</v>
-      </c>
-      <c r="AB17">
-        <v>0.97482526302337646</v>
-      </c>
-      <c r="AC17">
-        <v>0.29356756806373602</v>
-      </c>
-      <c r="AD17">
+        <v>2.399094105812023</v>
+      </c>
+      <c r="AJ17">
         <f t="shared" si="11"/>
-        <v>141.45824160364646</v>
-      </c>
-      <c r="AF17">
-        <f t="shared" si="6"/>
-        <v>4.9989251598038535</v>
-      </c>
-      <c r="AG17">
-        <f t="shared" si="7"/>
-        <v>5.7436367236723651</v>
-      </c>
-      <c r="AI17">
-        <f t="shared" si="8"/>
-        <v>2.399094105812023</v>
-      </c>
-      <c r="AJ17">
-        <f t="shared" si="9"/>
         <v>2.4713717957641723</v>
       </c>
       <c r="AL17">
@@ -2392,11 +2391,11 @@
       </c>
       <c r="AO17">
         <f t="shared" si="14"/>
-        <v>0.61828920435763179</v>
+        <v>0.68763522747712102</v>
       </c>
       <c r="AP17">
         <f t="shared" si="15"/>
-        <v>5.6948939923442019</v>
+        <v>5.6001059757923031</v>
       </c>
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.2">
@@ -2470,33 +2469,33 @@
         <v>0.28100436925888062</v>
       </c>
       <c r="Z18">
+        <f t="shared" si="6"/>
+        <v>159.90489476481977</v>
+      </c>
+      <c r="AB18">
+        <v>1.097770214080811</v>
+      </c>
+      <c r="AC18">
+        <v>0.29002615809440607</v>
+      </c>
+      <c r="AD18">
+        <f t="shared" si="7"/>
+        <v>161.24409831993952</v>
+      </c>
+      <c r="AF18">
+        <f t="shared" si="8"/>
+        <v>4.2099149472925648</v>
+      </c>
+      <c r="AG18">
+        <f t="shared" si="9"/>
+        <v>8.0360302045183314</v>
+      </c>
+      <c r="AI18">
         <f t="shared" si="10"/>
-        <v>159.90489476481977</v>
-      </c>
-      <c r="AB18">
-        <v>1.0985369682312009</v>
-      </c>
-      <c r="AC18">
-        <v>0.29043430089950562</v>
-      </c>
-      <c r="AD18">
+        <v>2.3300966214184298</v>
+      </c>
+      <c r="AJ18">
         <f t="shared" si="11"/>
-        <v>161.12996959955231</v>
-      </c>
-      <c r="AF18">
-        <f t="shared" si="6"/>
-        <v>4.2099149472925648</v>
-      </c>
-      <c r="AG18">
-        <f t="shared" si="7"/>
-        <v>8.0360302045183314</v>
-      </c>
-      <c r="AI18">
-        <f t="shared" si="8"/>
-        <v>2.3300966214184298</v>
-      </c>
-      <c r="AJ18">
-        <f t="shared" si="9"/>
         <v>16.07281617493123</v>
       </c>
       <c r="AL18">
@@ -2509,11 +2508,11 @@
       </c>
       <c r="AO18">
         <f t="shared" si="14"/>
-        <v>1.0237887889719035</v>
+        <v>1.0928719631668724</v>
       </c>
       <c r="AP18">
         <f t="shared" si="15"/>
-        <v>19.515370108022555</v>
+        <v>19.34741701757379</v>
       </c>
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.2">
@@ -2587,33 +2586,33 @@
         <v>0.47128748893737787</v>
       </c>
       <c r="Z19">
+        <f t="shared" si="6"/>
+        <v>56.894986617585147</v>
+      </c>
+      <c r="AB19">
+        <v>0.61960685253143311</v>
+      </c>
+      <c r="AC19">
+        <v>0.31762078404426569</v>
+      </c>
+      <c r="AD19">
+        <f t="shared" si="7"/>
+        <v>83.103028996327481</v>
+      </c>
+      <c r="AF19">
+        <f t="shared" si="8"/>
+        <v>4.7647188388772062</v>
+      </c>
+      <c r="AG19">
+        <f t="shared" si="9"/>
+        <v>15.066874103705938</v>
+      </c>
+      <c r="AI19">
         <f t="shared" si="10"/>
-        <v>56.894986617585147</v>
-      </c>
-      <c r="AB19">
-        <v>0.62023019790649414</v>
-      </c>
-      <c r="AC19">
-        <v>0.31761860847473139</v>
-      </c>
-      <c r="AD19">
+        <v>8.3384560082299846</v>
+      </c>
+      <c r="AJ19">
         <f t="shared" si="11"/>
-        <v>83.18720324171025</v>
-      </c>
-      <c r="AF19">
-        <f t="shared" si="6"/>
-        <v>4.7647188388772062</v>
-      </c>
-      <c r="AG19">
-        <f t="shared" si="7"/>
-        <v>15.066874103705938</v>
-      </c>
-      <c r="AI19">
-        <f t="shared" si="8"/>
-        <v>8.3384560082299846</v>
-      </c>
-      <c r="AJ19">
-        <f t="shared" si="9"/>
         <v>15.404449163162356</v>
       </c>
       <c r="AL19">
@@ -2626,11 +2625,11 @@
       </c>
       <c r="AO19">
         <f t="shared" si="14"/>
-        <v>4.1316004225154321</v>
+        <v>4.2279503321019654</v>
       </c>
       <c r="AP19">
         <f t="shared" si="15"/>
-        <v>19.865125094245375</v>
+        <v>19.86594612584561</v>
       </c>
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.2">
@@ -2704,33 +2703,33 @@
         <v>0.40556862950325012</v>
       </c>
       <c r="Z20">
+        <f t="shared" si="6"/>
+        <v>53.94354233015698</v>
+      </c>
+      <c r="AB20">
+        <v>0.50231289863586426</v>
+      </c>
+      <c r="AC20">
+        <v>0.26910996437072748</v>
+      </c>
+      <c r="AD20">
+        <f t="shared" si="7"/>
+        <v>79.51592335080484</v>
+      </c>
+      <c r="AF20">
+        <f t="shared" si="8"/>
+        <v>5.1597752554344796</v>
+      </c>
+      <c r="AG20">
+        <f t="shared" si="9"/>
+        <v>17.883843878787879</v>
+      </c>
+      <c r="AI20">
         <f t="shared" si="10"/>
-        <v>53.94354233015698</v>
-      </c>
-      <c r="AB20">
-        <v>0.50306236743927002</v>
-      </c>
-      <c r="AC20">
-        <v>0.26915031671524048</v>
-      </c>
-      <c r="AD20">
+        <v>10.608680055225619</v>
+      </c>
+      <c r="AJ20">
         <f t="shared" si="11"/>
-        <v>79.622624744236433</v>
-      </c>
-      <c r="AF20">
-        <f t="shared" si="6"/>
-        <v>5.1597752554344796</v>
-      </c>
-      <c r="AG20">
-        <f t="shared" si="7"/>
-        <v>17.883843878787879</v>
-      </c>
-      <c r="AI20">
-        <f t="shared" si="8"/>
-        <v>10.608680055225619</v>
-      </c>
-      <c r="AJ20">
-        <f t="shared" si="9"/>
         <v>24.262838652639658</v>
       </c>
       <c r="AL20">
@@ -2743,11 +2742,11 @@
       </c>
       <c r="AO20">
         <f t="shared" si="14"/>
-        <v>4.9911485695159481</v>
+        <v>5.1326939817816681</v>
       </c>
       <c r="AP20">
         <f t="shared" si="15"/>
-        <v>30.497123255874182</v>
+        <v>30.477558482776967</v>
       </c>
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.2">
@@ -2821,33 +2820,33 @@
         <v>0.42089086771011353</v>
       </c>
       <c r="Z21">
+        <f t="shared" si="6"/>
+        <v>78.094370455966526</v>
+      </c>
+      <c r="AB21">
+        <v>0.76624619960784912</v>
+      </c>
+      <c r="AC21">
+        <v>0.29888585209846502</v>
+      </c>
+      <c r="AD21">
+        <f t="shared" si="7"/>
+        <v>109.21254567769661</v>
+      </c>
+      <c r="AF21">
+        <f t="shared" si="8"/>
+        <v>4.24115539040874</v>
+      </c>
+      <c r="AG21">
+        <f t="shared" si="9"/>
+        <v>5.9708498825539227</v>
+      </c>
+      <c r="AI21">
         <f t="shared" si="10"/>
-        <v>78.094370455966526</v>
-      </c>
-      <c r="AB21">
-        <v>0.7668534517288208</v>
-      </c>
-      <c r="AC21">
-        <v>0.29896694421768188</v>
-      </c>
-      <c r="AD21">
+        <v>7.1969549306125939</v>
+      </c>
+      <c r="AJ21">
         <f t="shared" si="11"/>
-        <v>109.26945050035495</v>
-      </c>
-      <c r="AF21">
-        <f t="shared" si="6"/>
-        <v>4.24115539040874</v>
-      </c>
-      <c r="AG21">
-        <f t="shared" si="7"/>
-        <v>5.9708498825539227</v>
-      </c>
-      <c r="AI21">
-        <f t="shared" si="8"/>
-        <v>7.1969549306125939</v>
-      </c>
-      <c r="AJ21">
-        <f t="shared" si="9"/>
         <v>11.912822697205609</v>
       </c>
       <c r="AL21">
@@ -2860,11 +2859,11 @@
       </c>
       <c r="AO21">
         <f t="shared" si="14"/>
-        <v>4.3799780881292838</v>
+        <v>4.4556971984526923</v>
       </c>
       <c r="AP21">
         <f t="shared" si="15"/>
-        <v>8.7987113823001444</v>
+        <v>8.8234489190491345</v>
       </c>
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.2">
@@ -2938,33 +2937,33 @@
         <v>0.3657647967338562</v>
       </c>
       <c r="Z22">
+        <f t="shared" si="6"/>
+        <v>104.75051263659994</v>
+      </c>
+      <c r="AB22">
+        <v>0.87192267179489136</v>
+      </c>
+      <c r="AC22">
+        <v>0.3117508590221405</v>
+      </c>
+      <c r="AD22">
+        <f t="shared" si="7"/>
+        <v>119.14610964453614</v>
+      </c>
+      <c r="AF22">
+        <f t="shared" si="8"/>
+        <v>3.6510369585172833</v>
+      </c>
+      <c r="AG22">
+        <f t="shared" si="9"/>
+        <v>27.738585587098928</v>
+      </c>
+      <c r="AI22">
         <f t="shared" si="10"/>
-        <v>104.75051263659994</v>
-      </c>
-      <c r="AB22">
-        <v>0.87247419357299805</v>
-      </c>
-      <c r="AC22">
-        <v>0.31184810400009161</v>
-      </c>
-      <c r="AD22">
+        <v>6.8205515112853758</v>
+      </c>
+      <c r="AJ22">
         <f t="shared" si="11"/>
-        <v>119.18429639120367</v>
-      </c>
-      <c r="AF22">
-        <f t="shared" si="6"/>
-        <v>3.6510369585172833</v>
-      </c>
-      <c r="AG22">
-        <f t="shared" si="7"/>
-        <v>27.738585587098928</v>
-      </c>
-      <c r="AI22">
-        <f t="shared" si="8"/>
-        <v>6.8205515112853758</v>
-      </c>
-      <c r="AJ22">
-        <f t="shared" si="9"/>
         <v>1.6812185950385681</v>
       </c>
       <c r="AL22">
@@ -2977,11 +2976,11 @@
       </c>
       <c r="AO22">
         <f t="shared" si="14"/>
-        <v>4.6559652081787339</v>
+        <v>4.7162355428059461</v>
       </c>
       <c r="AP22">
         <f t="shared" si="15"/>
-        <v>4.7700668570776354</v>
+        <v>4.7373959422612053</v>
       </c>
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.2">
@@ -3055,33 +3054,33 @@
         <v>0.45917254686355591</v>
       </c>
       <c r="Z23">
+        <f t="shared" si="6"/>
+        <v>90.460608740819751</v>
+      </c>
+      <c r="AB23">
+        <v>0.95645755529403687</v>
+      </c>
+      <c r="AC23">
+        <v>0.33471366763114929</v>
+      </c>
+      <c r="AD23">
+        <f t="shared" si="7"/>
+        <v>121.73117395843836</v>
+      </c>
+      <c r="AF23">
+        <f t="shared" si="8"/>
+        <v>3.7662477752224741</v>
+      </c>
+      <c r="AG23">
+        <f t="shared" si="9"/>
+        <v>18.874153622672829</v>
+      </c>
+      <c r="AI23">
         <f t="shared" si="10"/>
-        <v>90.460608740819751</v>
-      </c>
-      <c r="AB23">
-        <v>0.95693659782409668</v>
-      </c>
-      <c r="AC23">
-        <v>0.33479788899421692</v>
-      </c>
-      <c r="AD23">
+        <v>6.0943512639550246</v>
+      </c>
+      <c r="AJ23">
         <f t="shared" si="11"/>
-        <v>121.76150522585313</v>
-      </c>
-      <c r="AF23">
-        <f t="shared" si="6"/>
-        <v>3.7662477752224741</v>
-      </c>
-      <c r="AG23">
-        <f t="shared" si="7"/>
-        <v>18.874153622672829</v>
-      </c>
-      <c r="AI23">
-        <f t="shared" si="8"/>
-        <v>6.0943512639550246</v>
-      </c>
-      <c r="AJ23">
-        <f t="shared" si="9"/>
         <v>3.2386657140807316</v>
       </c>
       <c r="AL23">
@@ -3094,11 +3093,11 @@
       </c>
       <c r="AO23">
         <f t="shared" si="14"/>
-        <v>4.3159086267276585</v>
+        <v>4.3638080897873337</v>
       </c>
       <c r="AP23">
         <f t="shared" si="15"/>
-        <v>0.74769091835144363</v>
+        <v>0.77265871245426199</v>
       </c>
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.2">
@@ -3172,33 +3171,33 @@
         <v>0.43526840209960938</v>
       </c>
       <c r="Z24">
+        <f t="shared" si="6"/>
+        <v>92.779072377486202</v>
+      </c>
+      <c r="AB24">
+        <v>0.93378829956054688</v>
+      </c>
+      <c r="AC24">
+        <v>0.3259657621383667</v>
+      </c>
+      <c r="AD24">
+        <f t="shared" si="7"/>
+        <v>122.03544704801629</v>
+      </c>
+      <c r="AF24">
+        <f t="shared" si="8"/>
+        <v>3.8700182309803726</v>
+      </c>
+      <c r="AG24">
+        <f t="shared" si="9"/>
+        <v>18.622274506466983</v>
+      </c>
+      <c r="AI24">
         <f t="shared" si="10"/>
-        <v>92.779072377486202</v>
-      </c>
-      <c r="AB24">
-        <v>0.93430107831954956</v>
-      </c>
-      <c r="AC24">
-        <v>0.32606536149978638</v>
-      </c>
-      <c r="AD24">
+        <v>6.186491655128358</v>
+      </c>
+      <c r="AJ24">
         <f t="shared" si="11"/>
-        <v>122.06516415830635</v>
-      </c>
-      <c r="AF24">
-        <f t="shared" si="6"/>
-        <v>3.8700182309803726</v>
-      </c>
-      <c r="AG24">
-        <f t="shared" si="7"/>
-        <v>18.622274506466983</v>
-      </c>
-      <c r="AI24">
-        <f t="shared" si="8"/>
-        <v>6.186491655128358</v>
-      </c>
-      <c r="AJ24">
-        <f t="shared" si="9"/>
         <v>9.9729203544886715</v>
       </c>
       <c r="AL24">
@@ -3211,11 +3210,11 @@
       </c>
       <c r="AO24">
         <f t="shared" si="14"/>
-        <v>4.3077268303136593</v>
+        <v>4.3602462656656487</v>
       </c>
       <c r="AP24">
         <f t="shared" si="15"/>
-        <v>7.5149303665230347</v>
+        <v>7.5431806959477212</v>
       </c>
     </row>
     <row r="25" spans="1:42" x14ac:dyDescent="0.2">
@@ -3289,33 +3288,33 @@
         <v>0.42533254623413091</v>
       </c>
       <c r="Z25">
+        <f t="shared" si="6"/>
+        <v>124.42911766901474</v>
+      </c>
+      <c r="AB25">
+        <v>1.2353417873382571</v>
+      </c>
+      <c r="AC25">
+        <v>0.37790989875793463</v>
+      </c>
+      <c r="AD25">
+        <f t="shared" si="7"/>
+        <v>139.25423744455463</v>
+      </c>
+      <c r="AF25">
+        <f t="shared" si="8"/>
+        <v>3.333571561554558</v>
+      </c>
+      <c r="AG25">
+        <f t="shared" si="9"/>
+        <v>3.8276534915302731</v>
+      </c>
+      <c r="AI25">
         <f t="shared" si="10"/>
-        <v>124.42911766901474</v>
-      </c>
-      <c r="AB25">
-        <v>1.235687851905823</v>
-      </c>
-      <c r="AC25">
-        <v>0.37804639339447021</v>
-      </c>
-      <c r="AD25">
+        <v>4.9725242900604192</v>
+      </c>
+      <c r="AJ25">
         <f t="shared" si="11"/>
-        <v>139.24295547618894</v>
-      </c>
-      <c r="AF25">
-        <f t="shared" si="6"/>
-        <v>3.333571561554558</v>
-      </c>
-      <c r="AG25">
-        <f t="shared" si="7"/>
-        <v>3.8276534915302731</v>
-      </c>
-      <c r="AI25">
-        <f t="shared" si="8"/>
-        <v>4.9725242900604192</v>
-      </c>
-      <c r="AJ25">
-        <f t="shared" si="9"/>
         <v>11.333855534515514</v>
       </c>
       <c r="AL25">
@@ -3328,11 +3327,11 @@
       </c>
       <c r="AO25">
         <f t="shared" si="14"/>
-        <v>4.1433673178323591</v>
+        <v>4.1702127578731565</v>
       </c>
       <c r="AP25">
         <f t="shared" si="15"/>
-        <v>9.9310524874394908</v>
+        <v>9.9635721158995931</v>
       </c>
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.2">
@@ -3406,33 +3405,33 @@
         <v>0.83409583568572998</v>
       </c>
       <c r="Z26">
+        <f t="shared" si="6"/>
+        <v>78.975106222321756</v>
+      </c>
+      <c r="AB26">
+        <v>1.4662696123123169</v>
+      </c>
+      <c r="AC26">
+        <v>0.53257066011428833</v>
+      </c>
+      <c r="AD26">
+        <f t="shared" si="7"/>
+        <v>117.2859937526883</v>
+      </c>
+      <c r="AF26">
+        <f t="shared" si="8"/>
+        <v>5.5670046427003035</v>
+      </c>
+      <c r="AG26">
+        <f t="shared" si="9"/>
+        <v>51.846682582848466</v>
+      </c>
+      <c r="AI26">
         <f t="shared" si="10"/>
-        <v>78.975106222321756</v>
-      </c>
-      <c r="AB26">
-        <v>1.4664642810821531</v>
-      </c>
-      <c r="AC26">
-        <v>0.53264981508255005</v>
-      </c>
-      <c r="AD26">
+        <v>8.6569943970423537</v>
+      </c>
+      <c r="AJ26">
         <f t="shared" si="11"/>
-        <v>117.28413346787153</v>
-      </c>
-      <c r="AF26">
-        <f t="shared" si="6"/>
-        <v>5.5670046427003035</v>
-      </c>
-      <c r="AG26">
-        <f t="shared" si="7"/>
-        <v>51.846682582848466</v>
-      </c>
-      <c r="AI26">
-        <f t="shared" si="8"/>
-        <v>8.6569943970423537</v>
-      </c>
-      <c r="AJ26">
-        <f t="shared" si="9"/>
         <v>16.850973948809944</v>
       </c>
       <c r="AL26">
@@ -3445,11 +3444,11 @@
       </c>
       <c r="AO26">
         <f t="shared" si="14"/>
-        <v>7.9952141864512827</v>
+        <v>8.0074275480069765</v>
       </c>
       <c r="AP26">
         <f t="shared" si="15"/>
-        <v>15.783927541969705</v>
+        <v>15.79644255718943</v>
       </c>
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.2">
@@ -3523,33 +3522,33 @@
         <v>0.68571579456329346</v>
       </c>
       <c r="Z27">
+        <f t="shared" si="6"/>
+        <v>85.749713492701531</v>
+      </c>
+      <c r="AB27">
+        <v>1.360673069953918</v>
+      </c>
+      <c r="AC27">
+        <v>0.48109990358352661</v>
+      </c>
+      <c r="AD27">
+        <f t="shared" si="7"/>
+        <v>120.48363850733864</v>
+      </c>
+      <c r="AF27">
+        <f t="shared" si="8"/>
+        <v>4.7754027436527533</v>
+      </c>
+      <c r="AG27">
+        <f t="shared" si="9"/>
+        <v>10.576503028221776</v>
+      </c>
+      <c r="AI27">
         <f t="shared" si="10"/>
-        <v>85.749713492701531</v>
-      </c>
-      <c r="AB27">
-        <v>1.360906839370728</v>
-      </c>
-      <c r="AC27">
-        <v>0.481172114610672</v>
-      </c>
-      <c r="AD27">
+        <v>7.8882625771453787</v>
+      </c>
+      <c r="AJ27">
         <f t="shared" si="11"/>
-        <v>120.48625363986935</v>
-      </c>
-      <c r="AF27">
-        <f t="shared" si="6"/>
-        <v>4.7754027436527533</v>
-      </c>
-      <c r="AG27">
-        <f t="shared" si="7"/>
-        <v>10.576503028221776</v>
-      </c>
-      <c r="AI27">
-        <f t="shared" si="8"/>
-        <v>7.8882625771453787</v>
-      </c>
-      <c r="AJ27">
-        <f t="shared" si="9"/>
         <v>25.926756616179404</v>
       </c>
       <c r="AL27">
@@ -3562,11 +3561,11 @@
       </c>
       <c r="AO27">
         <f t="shared" si="14"/>
-        <v>7.11801533096315</v>
+        <v>7.1339701096152091</v>
       </c>
       <c r="AP27">
         <f t="shared" si="15"/>
-        <v>24.891965126955544</v>
+        <v>24.903236828245721</v>
       </c>
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.2">
@@ -3640,33 +3639,33 @@
         <v>0.82216966152191162</v>
       </c>
       <c r="Z28">
+        <f t="shared" si="6"/>
+        <v>115.79863044329494</v>
+      </c>
+      <c r="AB28">
+        <v>2.1347558498382568</v>
+      </c>
+      <c r="AC28">
+        <v>0.71777725219726563</v>
+      </c>
+      <c r="AD28">
+        <f t="shared" si="7"/>
+        <v>126.6975090828558</v>
+      </c>
+      <c r="AF28">
+        <f t="shared" si="8"/>
+        <v>4.1292825652155356</v>
+      </c>
+      <c r="AG28">
+        <f t="shared" si="9"/>
+        <v>9.3694273270283777</v>
+      </c>
+      <c r="AI28">
         <f t="shared" si="10"/>
-        <v>115.79863044329494</v>
-      </c>
-      <c r="AB28">
-        <v>2.1348543167114258</v>
-      </c>
-      <c r="AC28">
-        <v>0.71792900562286377</v>
-      </c>
-      <c r="AD28">
+        <v>9.7161630076689143</v>
+      </c>
+      <c r="AJ28">
         <f t="shared" si="11"/>
-        <v>126.67657095035092</v>
-      </c>
-      <c r="AF28">
-        <f t="shared" si="6"/>
-        <v>4.1292825652155356</v>
-      </c>
-      <c r="AG28">
-        <f t="shared" si="7"/>
-        <v>9.3694273270283777</v>
-      </c>
-      <c r="AI28">
-        <f t="shared" si="8"/>
-        <v>9.7161630076689143</v>
-      </c>
-      <c r="AJ28">
-        <f t="shared" si="9"/>
         <v>12.177243595873316</v>
       </c>
       <c r="AL28">
@@ -3679,11 +3678,11 @@
       </c>
       <c r="AO28">
         <f t="shared" si="14"/>
-        <v>9.1512695556650971</v>
+        <v>9.1554598136832652</v>
       </c>
       <c r="AP28">
         <f t="shared" si="15"/>
-        <v>10.660900246034871</v>
+        <v>10.679784445337773</v>
       </c>
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.2">
@@ -3757,33 +3756,33 @@
         <v>0.5606423020362854</v>
       </c>
       <c r="Z29">
+        <f t="shared" si="6"/>
+        <v>141.06008801625333</v>
+      </c>
+      <c r="AB29">
+        <v>1.7868689298629761</v>
+      </c>
+      <c r="AC29">
+        <v>0.519939124584198</v>
+      </c>
+      <c r="AD29">
+        <f t="shared" si="7"/>
+        <v>146.40292497872471</v>
+      </c>
+      <c r="AF29">
+        <f t="shared" si="8"/>
+        <v>4.1711175630894726</v>
+      </c>
+      <c r="AG29">
+        <f t="shared" si="9"/>
+        <v>11.894673351330512</v>
+      </c>
+      <c r="AI29">
         <f t="shared" si="10"/>
-        <v>141.06008801625333</v>
-      </c>
-      <c r="AB29">
-        <v>1.78692090511322</v>
-      </c>
-      <c r="AC29">
-        <v>0.52000439167022705</v>
-      </c>
-      <c r="AD29">
+        <v>9.3075841475347474</v>
+      </c>
+      <c r="AJ29">
         <f t="shared" si="11"/>
-        <v>146.38880750782934</v>
-      </c>
-      <c r="AF29">
-        <f t="shared" si="6"/>
-        <v>4.1711175630894726</v>
-      </c>
-      <c r="AG29">
-        <f t="shared" si="7"/>
-        <v>11.894673351330512</v>
-      </c>
-      <c r="AI29">
-        <f t="shared" si="8"/>
-        <v>9.3075841475347474</v>
-      </c>
-      <c r="AJ29">
-        <f t="shared" si="9"/>
         <v>1.0964245397153525</v>
       </c>
       <c r="AL29">
@@ -3796,11 +3795,11 @@
       </c>
       <c r="AO29">
         <f t="shared" si="14"/>
-        <v>8.9002852351149642</v>
+        <v>8.9029350057111358</v>
       </c>
       <c r="AP29">
         <f t="shared" si="15"/>
-        <v>0.27080440999365618</v>
+        <v>0.2582191639410043</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.2">
@@ -3874,33 +3873,33 @@
         <v>0.89298427104949951</v>
       </c>
       <c r="Z30">
+        <f t="shared" si="6"/>
+        <v>130.22495647400189</v>
+      </c>
+      <c r="AB30">
+        <v>2.6035282611846919</v>
+      </c>
+      <c r="AC30">
+        <v>0.815193772315979</v>
+      </c>
+      <c r="AD30">
+        <f t="shared" si="7"/>
+        <v>136.05390078194924</v>
+      </c>
+      <c r="AF30">
+        <f t="shared" si="8"/>
+        <v>4.108458406320378</v>
+      </c>
+      <c r="AG30">
+        <f t="shared" si="9"/>
+        <v>9.4979361646505289</v>
+      </c>
+      <c r="AI30">
         <f t="shared" si="10"/>
-        <v>130.22495647400189</v>
-      </c>
-      <c r="AB30">
-        <v>2.603691577911377</v>
-      </c>
-      <c r="AC30">
-        <v>0.81541800498962402</v>
-      </c>
-      <c r="AD30">
+        <v>7.679379325154569</v>
+      </c>
+      <c r="AJ30">
         <f t="shared" si="11"/>
-        <v>136.02501935188423</v>
-      </c>
-      <c r="AF30">
-        <f t="shared" si="6"/>
-        <v>4.108458406320378</v>
-      </c>
-      <c r="AG30">
-        <f t="shared" si="7"/>
-        <v>9.4979361646505289</v>
-      </c>
-      <c r="AI30">
-        <f t="shared" si="8"/>
-        <v>7.679379325154569</v>
-      </c>
-      <c r="AJ30">
-        <f t="shared" si="9"/>
         <v>5.4270325316265833</v>
       </c>
       <c r="AL30">
@@ -3913,11 +3912,11 @@
       </c>
       <c r="AO30">
         <f t="shared" si="14"/>
-        <v>6.9212605758632595</v>
+        <v>6.9270989459588872</v>
       </c>
       <c r="AP30">
         <f t="shared" si="15"/>
-        <v>3.1040705148152119</v>
+        <v>3.130716030613037</v>
       </c>
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.2">
@@ -3991,33 +3990,33 @@
         <v>2.2499954700469971</v>
       </c>
       <c r="Z31">
+        <f t="shared" si="6"/>
+        <v>81.058063941426369</v>
+      </c>
+      <c r="AB31">
+        <v>3.997169971466064</v>
+      </c>
+      <c r="AC31">
+        <v>1.5717077255249019</v>
+      </c>
+      <c r="AD31">
+        <f t="shared" si="7"/>
+        <v>108.34038711865459</v>
+      </c>
+      <c r="AF31">
+        <f t="shared" si="8"/>
+        <v>4.1427571444456763</v>
+      </c>
+      <c r="AG31">
+        <f t="shared" si="9"/>
+        <v>1.0708962384233855</v>
+      </c>
+      <c r="AI31">
         <f t="shared" si="10"/>
-        <v>81.058063941426369</v>
-      </c>
-      <c r="AB31">
-        <v>3.99755859375</v>
-      </c>
-      <c r="AC31">
-        <v>1.5723417997360229</v>
-      </c>
-      <c r="AD31">
+        <v>12.035734332947982</v>
+      </c>
+      <c r="AJ31">
         <f t="shared" si="11"/>
-        <v>108.3072260477627</v>
-      </c>
-      <c r="AF31">
-        <f t="shared" si="6"/>
-        <v>4.1427571444456763</v>
-      </c>
-      <c r="AG31">
-        <f t="shared" si="7"/>
-        <v>1.0708962384233855</v>
-      </c>
-      <c r="AI31">
-        <f t="shared" si="8"/>
-        <v>12.035734332947982</v>
-      </c>
-      <c r="AJ31">
-        <f t="shared" si="9"/>
         <v>32.732478700477159</v>
       </c>
       <c r="AL31">
@@ -4030,11 +4029,11 @@
       </c>
       <c r="AO31">
         <f t="shared" si="14"/>
-        <v>11.096217196708555</v>
+        <v>11.104859969619396</v>
       </c>
       <c r="AP31">
         <f t="shared" si="15"/>
-        <v>30.986182691655056</v>
+        <v>31.014013715274469</v>
       </c>
     </row>
     <row r="32" spans="1:42" x14ac:dyDescent="0.2">
@@ -4108,33 +4107,33 @@
         <v>1.1225990056991579</v>
       </c>
       <c r="Z32">
+        <f t="shared" si="6"/>
+        <v>127.14180940971868</v>
+      </c>
+      <c r="AB32">
+        <v>3.3568792343139648</v>
+      </c>
+      <c r="AC32">
+        <v>1.0388057231903081</v>
+      </c>
+      <c r="AD32">
+        <f t="shared" si="7"/>
+        <v>137.66100591004687</v>
+      </c>
+      <c r="AF32">
+        <f t="shared" si="8"/>
+        <v>4.0636118141049433</v>
+      </c>
+      <c r="AG32">
+        <f t="shared" si="9"/>
+        <v>12.452502537060967</v>
+      </c>
+      <c r="AI32">
         <f t="shared" si="10"/>
-        <v>127.14180940971868</v>
-      </c>
-      <c r="AB32">
-        <v>3.3571081161499019</v>
-      </c>
-      <c r="AC32">
-        <v>1.039155960083008</v>
-      </c>
-      <c r="AD32">
+        <v>5.0443135475403462</v>
+      </c>
+      <c r="AJ32">
         <f t="shared" si="11"/>
-        <v>137.62399164152825</v>
-      </c>
-      <c r="AF32">
-        <f t="shared" si="6"/>
-        <v>4.0636118141049433</v>
-      </c>
-      <c r="AG32">
-        <f t="shared" si="7"/>
-        <v>12.452502537060967</v>
-      </c>
-      <c r="AI32">
-        <f t="shared" si="8"/>
-        <v>5.0443135475403462</v>
-      </c>
-      <c r="AJ32">
-        <f t="shared" si="9"/>
         <v>0.35695300008774783</v>
       </c>
       <c r="AL32">
@@ -4147,11 +4146,11 @@
       </c>
       <c r="AO32">
         <f t="shared" si="14"/>
-        <v>4.1072833799908084</v>
+        <v>4.1138211798690412</v>
       </c>
       <c r="AP32">
         <f t="shared" si="15"/>
-        <v>3.3883155987471816</v>
+        <v>3.3534696239486572</v>
       </c>
     </row>
     <row r="33" spans="1:42" x14ac:dyDescent="0.2">
@@ -4225,33 +4224,33 @@
         <v>1.185233354568481</v>
       </c>
       <c r="Z33">
+        <f t="shared" si="6"/>
+        <v>108.97085931062652</v>
+      </c>
+      <c r="AB33">
+        <v>3.1829390525817871</v>
+      </c>
+      <c r="AC33">
+        <v>1.0020231008529661</v>
+      </c>
+      <c r="AD33">
+        <f t="shared" si="7"/>
+        <v>135.31942496921877</v>
+      </c>
+      <c r="AF33">
+        <f t="shared" si="8"/>
+        <v>64.403865791268757</v>
+      </c>
+      <c r="AG33">
+        <f t="shared" si="9"/>
+        <v>61.302675656108597</v>
+      </c>
+      <c r="AI33">
         <f t="shared" si="10"/>
-        <v>108.97085931062652</v>
-      </c>
-      <c r="AB33">
-        <v>3.1831469535827641</v>
-      </c>
-      <c r="AC33">
-        <v>1.002339124679565</v>
-      </c>
-      <c r="AD33">
+        <v>10.38304776048162</v>
+      </c>
+      <c r="AJ33">
         <f t="shared" si="11"/>
-        <v>135.2855965174318</v>
-      </c>
-      <c r="AF33">
-        <f t="shared" si="6"/>
-        <v>64.403865791268757</v>
-      </c>
-      <c r="AG33">
-        <f t="shared" si="7"/>
-        <v>61.302675656108597</v>
-      </c>
-      <c r="AI33">
-        <f t="shared" si="8"/>
-        <v>10.38304776048162</v>
-      </c>
-      <c r="AJ33">
-        <f t="shared" si="9"/>
         <v>11.816098571363076</v>
       </c>
       <c r="AL33">
@@ -4264,11 +4263,11 @@
       </c>
       <c r="AO33">
         <f t="shared" si="14"/>
-        <v>9.5285654393257175</v>
+        <v>9.5344744036554427</v>
       </c>
       <c r="AP33">
         <f t="shared" si="15"/>
-        <v>9.2905769520755666</v>
+        <v>9.3191763933967326</v>
       </c>
     </row>
     <row r="34" spans="1:42" x14ac:dyDescent="0.2">
@@ -4342,33 +4341,33 @@
         <v>1.499395608901978</v>
       </c>
       <c r="Z34">
+        <f t="shared" si="6"/>
+        <v>92.020872099947198</v>
+      </c>
+      <c r="AB34">
+        <v>3.166429996490479</v>
+      </c>
+      <c r="AC34">
+        <v>1.170170664787292</v>
+      </c>
+      <c r="AD34">
+        <f t="shared" si="7"/>
+        <v>115.27370165277742</v>
+      </c>
+      <c r="AF34">
+        <f t="shared" si="8"/>
+        <v>4.6146258694841285</v>
+      </c>
+      <c r="AG34">
+        <f t="shared" si="9"/>
+        <v>5.8941098486752752</v>
+      </c>
+      <c r="AI34">
         <f t="shared" si="10"/>
-        <v>92.020872099947198</v>
-      </c>
-      <c r="AB34">
-        <v>3.166686058044434</v>
-      </c>
-      <c r="AC34">
-        <v>1.170584559440613</v>
-      </c>
-      <c r="AD34">
+        <v>7.5538158290314321</v>
+      </c>
+      <c r="AJ34">
         <f t="shared" si="11"/>
-        <v>115.24226184998859</v>
-      </c>
-      <c r="AF34">
-        <f t="shared" si="6"/>
-        <v>4.6146258694841285</v>
-      </c>
-      <c r="AG34">
-        <f t="shared" si="7"/>
-        <v>5.8941098486752752</v>
-      </c>
-      <c r="AI34">
-        <f t="shared" si="8"/>
-        <v>7.5538158290314321</v>
-      </c>
-      <c r="AJ34">
-        <f t="shared" si="9"/>
         <v>27.960636108879054</v>
       </c>
       <c r="AL34">
@@ -4381,11 +4380,11 @@
       </c>
       <c r="AO34">
         <f t="shared" si="14"/>
-        <v>6.7057697302997914</v>
+        <v>6.7133135995498607</v>
       </c>
       <c r="AP34">
         <f t="shared" si="15"/>
-        <v>26.262389956496811</v>
+        <v>26.28846206064302</v>
       </c>
     </row>
     <row r="35" spans="1:42" x14ac:dyDescent="0.2">
@@ -4459,33 +4458,33 @@
         <v>1.449684262275696</v>
       </c>
       <c r="Z35">
+        <f t="shared" si="6"/>
+        <v>81.916148969306022</v>
+      </c>
+      <c r="AB35">
+        <v>2.539272785186768</v>
+      </c>
+      <c r="AC35">
+        <v>0.90633726119995117</v>
+      </c>
+      <c r="AD35">
+        <f t="shared" si="7"/>
+        <v>119.35182878296206</v>
+      </c>
+      <c r="AF35">
+        <f t="shared" si="8"/>
+        <v>4.1841537820301911</v>
+      </c>
+      <c r="AG35">
+        <f t="shared" si="9"/>
+        <v>12.540884875474065</v>
+      </c>
+      <c r="AI35">
         <f t="shared" si="10"/>
-        <v>81.916148969306022</v>
-      </c>
-      <c r="AB35">
-        <v>2.5394806861877441</v>
-      </c>
-      <c r="AC35">
-        <v>0.90659594535827637</v>
-      </c>
-      <c r="AD35">
+        <v>13.189348892885949</v>
+      </c>
+      <c r="AJ35">
         <f t="shared" si="11"/>
-        <v>119.32754250002912</v>
-      </c>
-      <c r="AF35">
-        <f t="shared" si="6"/>
-        <v>4.1841537820301911</v>
-      </c>
-      <c r="AG35">
-        <f t="shared" si="7"/>
-        <v>12.540884875474065</v>
-      </c>
-      <c r="AI35">
-        <f t="shared" si="8"/>
-        <v>13.189348892885949</v>
-      </c>
-      <c r="AJ35">
-        <f t="shared" si="9"/>
         <v>32.156990570620927</v>
       </c>
       <c r="AL35">
@@ -4498,11 +4497,11 @@
       </c>
       <c r="AO35">
         <f t="shared" si="14"/>
-        <v>12.498081242238852</v>
+        <v>12.505244807843432</v>
       </c>
       <c r="AP35">
         <f t="shared" si="15"/>
-        <v>30.736042069044512</v>
+        <v>30.755805546645949</v>
       </c>
     </row>
     <row r="36" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -4576,33 +4575,33 @@
         <v>1.2581450939178469</v>
       </c>
       <c r="Z36">
+        <f t="shared" si="6"/>
+        <v>87.073665449534516</v>
+      </c>
+      <c r="AB36">
+        <v>2.3515620231628418</v>
+      </c>
+      <c r="AC36">
+        <v>0.7938881516456604</v>
+      </c>
+      <c r="AD36">
+        <f t="shared" si="7"/>
+        <v>126.18469209282755</v>
+      </c>
+      <c r="AF36">
+        <f t="shared" si="8"/>
+        <v>4.111652548969329</v>
+      </c>
+      <c r="AG36">
+        <f t="shared" si="9"/>
+        <v>29.215118735809014</v>
+      </c>
+      <c r="AI36">
         <f t="shared" si="10"/>
-        <v>87.073665449534516</v>
-      </c>
-      <c r="AB36">
-        <v>2.3517355918884282</v>
-      </c>
-      <c r="AC36">
-        <v>0.79409676790237427</v>
-      </c>
-      <c r="AD36">
+        <v>11.62158196191813</v>
+      </c>
+      <c r="AJ36">
         <f t="shared" si="11"/>
-        <v>126.16085349792556</v>
-      </c>
-      <c r="AF36">
-        <f t="shared" si="6"/>
-        <v>4.111652548969329</v>
-      </c>
-      <c r="AG36">
-        <f t="shared" si="7"/>
-        <v>29.215118735809014</v>
-      </c>
-      <c r="AI36">
-        <f t="shared" si="8"/>
-        <v>11.62158196191813</v>
-      </c>
-      <c r="AJ36">
-        <f t="shared" si="9"/>
         <v>32.226179534574413</v>
       </c>
       <c r="AL36">
@@ -4615,11 +4614,11 @@
       </c>
       <c r="AO36">
         <f t="shared" si="14"/>
-        <v>10.95283635409208</v>
+        <v>10.959408437605385</v>
       </c>
       <c r="AP36">
         <f t="shared" si="15"/>
-        <v>30.809726592108188</v>
+        <v>30.82790348996598</v>
       </c>
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.2">
@@ -4693,33 +4692,33 @@
         <v>3.2283375263214111</v>
       </c>
       <c r="Z37">
+        <f t="shared" si="6"/>
+        <v>71.423176056409957</v>
+      </c>
+      <c r="AB37">
+        <v>5.2442569732666016</v>
+      </c>
+      <c r="AC37">
+        <v>2.1994633674621582</v>
+      </c>
+      <c r="AD37">
+        <f t="shared" si="7"/>
+        <v>101.57265066791282</v>
+      </c>
+      <c r="AF37">
+        <f t="shared" si="8"/>
+        <v>5.3921708259311494</v>
+      </c>
+      <c r="AG37">
+        <f t="shared" si="9"/>
+        <v>3.2215962646755849</v>
+      </c>
+      <c r="AI37">
         <f t="shared" si="10"/>
-        <v>71.423176056409957</v>
-      </c>
-      <c r="AB37">
-        <v>5.2448768615722656</v>
-      </c>
-      <c r="AC37">
-        <v>2.2004528045654301</v>
-      </c>
-      <c r="AD37">
+        <v>9.0008394335198592</v>
+      </c>
+      <c r="AJ37">
         <f t="shared" si="11"/>
-        <v>101.53897918449526</v>
-      </c>
-      <c r="AF37">
-        <f t="shared" si="6"/>
-        <v>5.3921708259311494</v>
-      </c>
-      <c r="AG37">
-        <f t="shared" si="7"/>
-        <v>3.2215962646755849</v>
-      </c>
-      <c r="AI37">
-        <f t="shared" si="8"/>
-        <v>9.0008394335198592</v>
-      </c>
-      <c r="AJ37">
-        <f t="shared" si="9"/>
         <v>32.925755045727094</v>
       </c>
       <c r="AL37">
@@ -4732,11 +4731,11 @@
       </c>
       <c r="AO37">
         <f t="shared" si="14"/>
-        <v>7.9151489444271066</v>
+        <v>7.9260323881770249</v>
       </c>
       <c r="AP37">
         <f t="shared" si="15"/>
-        <v>31.093730676851315</v>
+        <v>31.124714490444099</v>
       </c>
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.2">
@@ -4810,33 +4809,33 @@
         <v>0.92695754766464233</v>
       </c>
       <c r="Z38">
+        <f t="shared" si="6"/>
+        <v>134.89709863030177</v>
+      </c>
+      <c r="AB38">
+        <v>2.984222412109375</v>
+      </c>
+      <c r="AC38">
+        <v>0.86532515287399292</v>
+      </c>
+      <c r="AD38">
+        <f t="shared" si="7"/>
+        <v>146.9134017082124</v>
+      </c>
+      <c r="AF38">
+        <f t="shared" si="8"/>
+        <v>4.1069042972819183</v>
+      </c>
+      <c r="AG38">
+        <f t="shared" si="9"/>
+        <v>8.2463538883684944</v>
+      </c>
+      <c r="AI38">
         <f t="shared" si="10"/>
-        <v>134.89709863030177</v>
-      </c>
-      <c r="AB38">
-        <v>2.984399795532227</v>
-      </c>
-      <c r="AC38">
-        <v>0.8655896782875061</v>
-      </c>
-      <c r="AD38">
+        <v>4.5647785358512207</v>
+      </c>
+      <c r="AJ38">
         <f t="shared" si="11"/>
-        <v>146.87723469273169</v>
-      </c>
-      <c r="AF38">
-        <f t="shared" si="6"/>
-        <v>4.1069042972819183</v>
-      </c>
-      <c r="AG38">
-        <f t="shared" si="7"/>
-        <v>8.2463538883684944</v>
-      </c>
-      <c r="AI38">
-        <f t="shared" si="8"/>
-        <v>4.5647785358512207</v>
-      </c>
-      <c r="AJ38">
-        <f t="shared" si="9"/>
         <v>4.7502575531394982</v>
       </c>
       <c r="AL38">
@@ -4849,11 +4848,11 @@
       </c>
       <c r="AO38">
         <f t="shared" si="14"/>
-        <v>3.6824335797248029</v>
+        <v>3.6881583956954991</v>
       </c>
       <c r="AP38">
         <f t="shared" si="15"/>
-        <v>1.8883901062617032</v>
+        <v>1.9183731511484341</v>
       </c>
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.2">
@@ -4927,33 +4926,33 @@
         <v>3.1004500389099121</v>
       </c>
       <c r="Z39">
+        <f t="shared" si="6"/>
+        <v>80.499949174369604</v>
+      </c>
+      <c r="AB39">
+        <v>5.7620277404785156</v>
+      </c>
+      <c r="AC39">
+        <v>2.320294857025146</v>
+      </c>
+      <c r="AD39">
+        <f t="shared" si="7"/>
+        <v>105.7892948264532</v>
+      </c>
+      <c r="AF39">
+        <f t="shared" si="8"/>
+        <v>5.5950694182904614</v>
+      </c>
+      <c r="AG39">
+        <f t="shared" si="9"/>
+        <v>4.375201898579979</v>
+      </c>
+      <c r="AI39">
         <f t="shared" si="10"/>
-        <v>80.499949174369604</v>
-      </c>
-      <c r="AB39">
-        <v>5.7626638412475586</v>
-      </c>
-      <c r="AC39">
-        <v>2.3213567733764648</v>
-      </c>
-      <c r="AD39">
+        <v>9.2535244752727763</v>
+      </c>
+      <c r="AJ39">
         <f t="shared" si="11"/>
-        <v>105.75257427881903</v>
-      </c>
-      <c r="AF39">
-        <f t="shared" si="6"/>
-        <v>5.5950694182904614</v>
-      </c>
-      <c r="AG39">
-        <f t="shared" si="7"/>
-        <v>4.375201898579979</v>
-      </c>
-      <c r="AI39">
-        <f t="shared" si="8"/>
-        <v>9.2535244752727763</v>
-      </c>
-      <c r="AJ39">
-        <f t="shared" si="9"/>
         <v>25.874732147049293</v>
       </c>
       <c r="AL39">
@@ -4966,11 +4965,11 @@
       </c>
       <c r="AO39">
         <f t="shared" si="14"/>
-        <v>8.1442259428787533</v>
+        <v>8.1543652690876751</v>
       </c>
       <c r="AP39">
         <f t="shared" si="15"/>
-        <v>23.71235422207549</v>
+        <v>23.747252389985011</v>
       </c>
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.2">
@@ -5044,33 +5043,33 @@
         <v>4.4666094779968262</v>
       </c>
       <c r="Z40">
+        <f t="shared" si="6"/>
+        <v>62.118975973910089</v>
+      </c>
+      <c r="AB40">
+        <v>6.0839672088623047</v>
+      </c>
+      <c r="AC40">
+        <v>2.6339442729949951</v>
+      </c>
+      <c r="AD40">
+        <f t="shared" si="7"/>
+        <v>98.398807949750847</v>
+      </c>
+      <c r="AF40">
+        <f t="shared" si="8"/>
+        <v>3.0521090890563718</v>
+      </c>
+      <c r="AG40">
+        <f t="shared" si="9"/>
+        <v>0.1765696303101032</v>
+      </c>
+      <c r="AI40">
         <f t="shared" si="10"/>
-        <v>62.118975973910089</v>
-      </c>
-      <c r="AB40">
-        <v>6.0847935676574707</v>
-      </c>
-      <c r="AC40">
-        <v>2.63520336151123</v>
-      </c>
-      <c r="AD40">
+        <v>11.508605394470402</v>
+      </c>
+      <c r="AJ40">
         <f t="shared" si="11"/>
-        <v>98.365152130502977</v>
-      </c>
-      <c r="AF40">
-        <f t="shared" si="6"/>
-        <v>3.0521090890563718</v>
-      </c>
-      <c r="AG40">
-        <f t="shared" si="7"/>
-        <v>0.1765696303101032</v>
-      </c>
-      <c r="AI40">
-        <f t="shared" si="8"/>
-        <v>11.508605394470402</v>
-      </c>
-      <c r="AJ40">
-        <f t="shared" si="9"/>
         <v>39.247013728351071</v>
       </c>
       <c r="AL40">
@@ -5083,11 +5082,11 @@
       </c>
       <c r="AO40">
         <f t="shared" si="14"/>
-        <v>10.409706297925874</v>
+        <v>10.421873305128178</v>
       </c>
       <c r="AP40">
         <f t="shared" si="15"/>
-        <v>37.570695754395061</v>
+        <v>37.600524199971687</v>
       </c>
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.2">
@@ -5161,33 +5160,33 @@
         <v>1.020569920539856</v>
       </c>
       <c r="Z41">
+        <f t="shared" si="6"/>
+        <v>95.345934174494772</v>
+      </c>
+      <c r="AB41">
+        <v>2.1406326293945308</v>
+      </c>
+      <c r="AC41">
+        <v>0.78246039152145386</v>
+      </c>
+      <c r="AD41">
+        <f t="shared" si="7"/>
+        <v>116.54384260394676</v>
+      </c>
+      <c r="AF41">
+        <f t="shared" si="8"/>
+        <v>3.8151692737918483</v>
+      </c>
+      <c r="AG41">
+        <f t="shared" si="9"/>
+        <v>14.367041283621774</v>
+      </c>
+      <c r="AI41">
         <f t="shared" si="10"/>
-        <v>95.345934174494772</v>
-      </c>
-      <c r="AB41">
-        <v>2.1406707763671879</v>
-      </c>
-      <c r="AC41">
-        <v>0.7827262282371521</v>
-      </c>
-      <c r="AD41">
+        <v>7.0450901870574265</v>
+      </c>
+      <c r="AJ41">
         <f t="shared" si="11"/>
-        <v>116.50633706187578</v>
-      </c>
-      <c r="AF41">
-        <f t="shared" si="6"/>
-        <v>3.8151692737918483</v>
-      </c>
-      <c r="AG41">
-        <f t="shared" si="7"/>
-        <v>14.367041283621774</v>
-      </c>
-      <c r="AI41">
-        <f t="shared" si="8"/>
-        <v>7.0450901870574265</v>
-      </c>
-      <c r="AJ41">
-        <f t="shared" si="9"/>
         <v>12.459226284832726</v>
       </c>
       <c r="AL41">
@@ -5200,11 +5199,11 @@
       </c>
       <c r="AO41">
         <f t="shared" si="14"/>
-        <v>6.4637430583244004</v>
+        <v>6.4654098840107217</v>
       </c>
       <c r="AP41">
         <f t="shared" si="15"/>
-        <v>11.05484844068225</v>
+        <v>11.08505681509825</v>
       </c>
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.2">
@@ -5278,33 +5277,33 @@
         <v>0.67118847370147705</v>
       </c>
       <c r="Z42">
+        <f t="shared" si="6"/>
+        <v>106.79405149029421</v>
+      </c>
+      <c r="AB42">
+        <v>1.6613515615463259</v>
+      </c>
+      <c r="AC42">
+        <v>0.54060018062591553</v>
+      </c>
+      <c r="AD42">
+        <f t="shared" si="7"/>
+        <v>130.91665863488899</v>
+      </c>
+      <c r="AF42">
+        <f t="shared" si="8"/>
+        <v>4.064183722833314</v>
+      </c>
+      <c r="AG42">
+        <f t="shared" si="9"/>
+        <v>1.231517598654859</v>
+      </c>
+      <c r="AI42">
         <f t="shared" si="10"/>
-        <v>106.79405149029421</v>
-      </c>
-      <c r="AB42">
-        <v>1.6614412069320681</v>
-      </c>
-      <c r="AC42">
-        <v>0.5406913161277771</v>
-      </c>
-      <c r="AD42">
+        <v>6.4225073679262144</v>
+      </c>
+      <c r="AJ42">
         <f t="shared" si="11"/>
-        <v>130.90165513455233</v>
-      </c>
-      <c r="AF42">
-        <f t="shared" si="6"/>
-        <v>4.064183722833314</v>
-      </c>
-      <c r="AG42">
-        <f t="shared" si="7"/>
-        <v>1.231517598654859</v>
-      </c>
-      <c r="AI42">
-        <f t="shared" si="8"/>
-        <v>6.4225073679262144</v>
-      </c>
-      <c r="AJ42">
-        <f t="shared" si="9"/>
         <v>14.462615407341261</v>
       </c>
       <c r="AL42">
@@ -5317,11 +5316,11 @@
       </c>
       <c r="AO42">
         <f t="shared" si="14"/>
-        <v>6.0589614988087677</v>
+        <v>6.0640302190248807</v>
       </c>
       <c r="AP42">
         <f t="shared" si="15"/>
-        <v>13.601362054333247</v>
+        <v>13.615924861233353</v>
       </c>
     </row>
     <row r="43" spans="1:42" x14ac:dyDescent="0.2">
@@ -5395,33 +5394,33 @@
         <v>0.82050019502639771</v>
       </c>
       <c r="Z43">
+        <f t="shared" si="6"/>
+        <v>105.34807371864109</v>
+      </c>
+      <c r="AB43">
+        <v>2.018805980682373</v>
+      </c>
+      <c r="AC43">
+        <v>0.62740904092788696</v>
+      </c>
+      <c r="AD43">
+        <f t="shared" si="7"/>
+        <v>137.07345670407813</v>
+      </c>
+      <c r="AF43">
+        <f t="shared" si="8"/>
+        <v>4.3835484569684775</v>
+      </c>
+      <c r="AG43">
+        <f t="shared" si="9"/>
+        <v>2.0707287233986746</v>
+      </c>
+      <c r="AI43">
         <f t="shared" si="10"/>
-        <v>105.34807371864109</v>
-      </c>
-      <c r="AB43">
-        <v>2.018890380859375</v>
-      </c>
-      <c r="AC43">
-        <v>0.62754464149475098</v>
-      </c>
-      <c r="AD43">
+        <v>8.1098062603139454</v>
+      </c>
+      <c r="AJ43">
         <f t="shared" si="11"/>
-        <v>137.04956710281931</v>
-      </c>
-      <c r="AF43">
-        <f t="shared" si="6"/>
-        <v>4.3835484569684775</v>
-      </c>
-      <c r="AG43">
-        <f t="shared" si="7"/>
-        <v>2.0707287233986746</v>
-      </c>
-      <c r="AI43">
-        <f t="shared" si="8"/>
-        <v>8.1098062603139454</v>
-      </c>
-      <c r="AJ43">
-        <f t="shared" si="9"/>
         <v>20.59838133923159</v>
       </c>
       <c r="AL43">
@@ -5434,11 +5433,11 @@
       </c>
       <c r="AO43">
         <f t="shared" si="14"/>
-        <v>7.5345616534132454</v>
+        <v>7.5384271923434447</v>
       </c>
       <c r="AP43">
         <f t="shared" si="15"/>
-        <v>19.12250728235502</v>
+        <v>19.139983383868582</v>
       </c>
     </row>
     <row r="44" spans="1:42" x14ac:dyDescent="0.2">
@@ -5512,33 +5511,33 @@
         <v>1.65027928352356</v>
       </c>
       <c r="Z44">
+        <f t="shared" si="6"/>
+        <v>78.259940099466448</v>
+      </c>
+      <c r="AB44">
+        <v>2.7989902496337891</v>
+      </c>
+      <c r="AC44">
+        <v>0.96742987632751465</v>
+      </c>
+      <c r="AD44">
+        <f t="shared" si="7"/>
+        <v>123.25128197221312</v>
+      </c>
+      <c r="AF44">
+        <f t="shared" si="8"/>
+        <v>3.9787767271886918</v>
+      </c>
+      <c r="AG44">
+        <f t="shared" si="9"/>
+        <v>56.834822043922692</v>
+      </c>
+      <c r="AI44">
         <f t="shared" si="10"/>
-        <v>78.259940099466448</v>
-      </c>
-      <c r="AB44">
-        <v>2.799170970916748</v>
-      </c>
-      <c r="AC44">
-        <v>0.96773171424865723</v>
-      </c>
-      <c r="AD44">
+        <v>12.253116385825232</v>
+      </c>
+      <c r="AJ44">
         <f t="shared" si="11"/>
-        <v>123.22079502585675</v>
-      </c>
-      <c r="AF44">
-        <f t="shared" si="6"/>
-        <v>3.9787767271886918</v>
-      </c>
-      <c r="AG44">
-        <f t="shared" si="7"/>
-        <v>56.834822043922692</v>
-      </c>
-      <c r="AI44">
-        <f t="shared" si="8"/>
-        <v>12.253116385825232</v>
-      </c>
-      <c r="AJ44">
-        <f t="shared" si="9"/>
         <v>12.890475080466416</v>
       </c>
       <c r="AL44">
@@ -5551,11 +5550,11 @@
       </c>
       <c r="AO44">
         <f t="shared" si="14"/>
-        <v>11.530626709331608</v>
+        <v>11.536338507149528</v>
       </c>
       <c r="AP44">
         <f t="shared" si="15"/>
-        <v>10.931273423961601</v>
+        <v>10.959054180624516</v>
       </c>
     </row>
     <row r="45" spans="1:42" x14ac:dyDescent="0.2">
@@ -5629,33 +5628,33 @@
         <v>1.1111242771148679</v>
       </c>
       <c r="Z45">
+        <f t="shared" si="6"/>
+        <v>103.65756131273389</v>
+      </c>
+      <c r="AB45">
+        <v>2.5376453399658199</v>
+      </c>
+      <c r="AC45">
+        <v>0.85112857818603516</v>
+      </c>
+      <c r="AD45">
+        <f t="shared" si="7"/>
+        <v>127.01216153428683</v>
+      </c>
+      <c r="AF45">
+        <f t="shared" si="8"/>
+        <v>4.7073043691195764</v>
+      </c>
+      <c r="AG45">
+        <f t="shared" si="9"/>
+        <v>3.2827402662356167</v>
+      </c>
+      <c r="AI45">
         <f t="shared" si="10"/>
-        <v>103.65756131273389</v>
-      </c>
-      <c r="AB45">
-        <v>2.5378062725067139</v>
-      </c>
-      <c r="AC45">
-        <v>0.85136544704437256</v>
-      </c>
-      <c r="AD45">
+        <v>12.256289422242075</v>
+      </c>
+      <c r="AJ45">
         <f t="shared" si="11"/>
-        <v>126.98487654141421</v>
-      </c>
-      <c r="AF45">
-        <f t="shared" si="6"/>
-        <v>4.7073043691195764</v>
-      </c>
-      <c r="AG45">
-        <f t="shared" si="7"/>
-        <v>3.2827402662356167</v>
-      </c>
-      <c r="AI45">
-        <f t="shared" si="8"/>
-        <v>12.256289422242075</v>
-      </c>
-      <c r="AJ45">
-        <f t="shared" si="9"/>
         <v>19.985462489399133</v>
       </c>
       <c r="AL45">
@@ -5668,11 +5667,11 @@
       </c>
       <c r="AO45">
         <f t="shared" si="14"/>
-        <v>11.580855950570907</v>
+        <v>11.586462965444227</v>
       </c>
       <c r="AP45">
         <f t="shared" si="15"/>
-        <v>18.263685959641656</v>
+        <v>18.286426825457461</v>
       </c>
     </row>
     <row r="46" spans="1:42" x14ac:dyDescent="0.2">
@@ -5746,33 +5745,33 @@
         <v>1.6114711761474609</v>
       </c>
       <c r="Z46">
+        <f t="shared" si="6"/>
+        <v>106.09356539094222</v>
+      </c>
+      <c r="AB46">
+        <v>3.8822536468505859</v>
+      </c>
+      <c r="AC46">
+        <v>1.3878781795501709</v>
+      </c>
+      <c r="AD46">
+        <f t="shared" si="7"/>
+        <v>119.16318804358478</v>
+      </c>
+      <c r="AF46">
+        <f t="shared" si="8"/>
+        <v>3.8844941859082596</v>
+      </c>
+      <c r="AG46">
+        <f t="shared" si="9"/>
+        <v>10.771184902682798</v>
+      </c>
+      <c r="AI46">
         <f t="shared" si="10"/>
-        <v>106.09356539094222</v>
-      </c>
-      <c r="AB46">
-        <v>3.882563591003418</v>
-      </c>
-      <c r="AC46">
-        <v>1.3884246349334719</v>
-      </c>
-      <c r="AD46">
+        <v>8.6174973862561348</v>
+      </c>
+      <c r="AJ46">
         <f t="shared" si="11"/>
-        <v>119.12579764822063</v>
-      </c>
-      <c r="AF46">
-        <f t="shared" si="6"/>
-        <v>3.8844941859082596</v>
-      </c>
-      <c r="AG46">
-        <f t="shared" si="7"/>
-        <v>10.771184902682798</v>
-      </c>
-      <c r="AI46">
-        <f t="shared" si="8"/>
-        <v>8.6174973862561348</v>
-      </c>
-      <c r="AJ46">
-        <f t="shared" si="9"/>
         <v>11.152065458704092</v>
       </c>
       <c r="AL46">
@@ -5785,11 +5784,11 @@
       </c>
       <c r="AO46">
         <f t="shared" si="14"/>
-        <v>7.6745157062892604</v>
+        <v>7.681886028331256</v>
       </c>
       <c r="AP46">
         <f t="shared" si="15"/>
-        <v>8.7043243731278288</v>
+        <v>8.7402564735553021</v>
       </c>
     </row>
     <row r="47" spans="1:42" x14ac:dyDescent="0.2">
@@ -5863,33 +5862,33 @@
         <v>3.1605591773986821</v>
       </c>
       <c r="Z47">
+        <f t="shared" si="6"/>
+        <v>82.916953368222082</v>
+      </c>
+      <c r="AB47">
+        <v>6.0688610076904297</v>
+      </c>
+      <c r="AC47">
+        <v>2.5192115306854248</v>
+      </c>
+      <c r="AD47">
+        <f t="shared" si="7"/>
+        <v>102.62474961526495</v>
+      </c>
+      <c r="AF47">
+        <f t="shared" si="8"/>
+        <v>6.2759463050099438</v>
+      </c>
+      <c r="AG47">
+        <f t="shared" si="9"/>
+        <v>1.0075647763815918</v>
+      </c>
+      <c r="AI47">
         <f t="shared" si="10"/>
-        <v>82.916953368222082</v>
-      </c>
-      <c r="AB47">
-        <v>6.0695581436157227</v>
-      </c>
-      <c r="AC47">
-        <v>2.520357608795166</v>
-      </c>
-      <c r="AD47">
+        <v>8.267247924898065</v>
+      </c>
+      <c r="AJ47">
         <f t="shared" si="11"/>
-        <v>102.58986647354102</v>
-      </c>
-      <c r="AF47">
-        <f t="shared" si="6"/>
-        <v>6.2759463050099438</v>
-      </c>
-      <c r="AG47">
-        <f t="shared" si="7"/>
-        <v>1.0075647763815918</v>
-      </c>
-      <c r="AI47">
-        <f t="shared" si="8"/>
-        <v>8.267247924898065</v>
-      </c>
-      <c r="AJ47">
-        <f t="shared" si="9"/>
         <v>21.480633804752038</v>
       </c>
       <c r="AL47">
@@ -5902,11 +5901,11 @@
       </c>
       <c r="AO47">
         <f t="shared" si="14"/>
-        <v>7.1365033106529534</v>
+        <v>7.1471694049811791</v>
       </c>
       <c r="AP47">
         <f t="shared" si="15"/>
-        <v>19.237427218407209</v>
+        <v>19.274152251564555</v>
       </c>
     </row>
     <row r="48" spans="1:42" x14ac:dyDescent="0.2">
@@ -5980,33 +5979,33 @@
         <v>2.839781761169434</v>
       </c>
       <c r="Z48">
+        <f t="shared" si="6"/>
+        <v>97.890403074605743</v>
+      </c>
+      <c r="AB48">
+        <v>6.2838478088378906</v>
+      </c>
+      <c r="AC48">
+        <v>2.3071284294128418</v>
+      </c>
+      <c r="AD48">
+        <f t="shared" si="7"/>
+        <v>116.02816988718142</v>
+      </c>
+      <c r="AF48">
+        <f t="shared" si="8"/>
+        <v>5.8006759119568931</v>
+      </c>
+      <c r="AG48">
+        <f t="shared" si="9"/>
+        <v>0.66094489918848365</v>
+      </c>
+      <c r="AI48">
         <f t="shared" si="10"/>
-        <v>97.890403074605743</v>
-      </c>
-      <c r="AB48">
-        <v>6.284492015838623</v>
-      </c>
-      <c r="AC48">
-        <v>2.3081881999969478</v>
-      </c>
-      <c r="AD48">
+        <v>10.651966455341029</v>
+      </c>
+      <c r="AJ48">
         <f t="shared" si="11"/>
-        <v>115.98678676862052</v>
-      </c>
-      <c r="AF48">
-        <f t="shared" si="6"/>
-        <v>5.8006759119568931</v>
-      </c>
-      <c r="AG48">
-        <f t="shared" si="7"/>
-        <v>0.66094489918848365</v>
-      </c>
-      <c r="AI48">
-        <f t="shared" si="8"/>
-        <v>10.651966455341029</v>
-      </c>
-      <c r="AJ48">
-        <f t="shared" si="9"/>
         <v>23.131829170280323</v>
       </c>
       <c r="AL48">
@@ -6019,11 +6018,11 @@
       </c>
       <c r="AO48">
         <f t="shared" si="14"/>
-        <v>9.5261867519129453</v>
+        <v>9.5354609881965597</v>
       </c>
       <c r="AP48">
         <f t="shared" si="15"/>
-        <v>20.596229660568032</v>
+        <v>20.63268673112794</v>
       </c>
     </row>
     <row r="49" spans="1:42" x14ac:dyDescent="0.2">
@@ -6097,33 +6096,33 @@
         <v>11.848756790161129</v>
       </c>
       <c r="Z49">
+        <f t="shared" si="6"/>
+        <v>50.379371363106422</v>
+      </c>
+      <c r="AB49">
+        <v>11.910408020019529</v>
+      </c>
+      <c r="AC49">
+        <v>6.7531614303588867</v>
+      </c>
+      <c r="AD49">
+        <f t="shared" si="7"/>
+        <v>75.132711567218593</v>
+      </c>
+      <c r="AF49">
+        <f t="shared" si="8"/>
+        <v>21.464885739310454</v>
+      </c>
+      <c r="AG49">
+        <f t="shared" si="9"/>
+        <v>1.8976474164133772</v>
+      </c>
+      <c r="AI49">
         <f t="shared" si="10"/>
-        <v>50.379371363106422</v>
-      </c>
-      <c r="AB49">
-        <v>11.912270545959471</v>
-      </c>
-      <c r="AC49">
-        <v>6.7560234069824219</v>
-      </c>
-      <c r="AD49">
+        <v>53.258887095876219</v>
+      </c>
+      <c r="AJ49">
         <f t="shared" si="11"/>
-        <v>75.112628086294393</v>
-      </c>
-      <c r="AF49">
-        <f t="shared" si="6"/>
-        <v>21.464885739310454</v>
-      </c>
-      <c r="AG49">
-        <f t="shared" si="7"/>
-        <v>1.8976474164133772</v>
-      </c>
-      <c r="AI49">
-        <f t="shared" si="8"/>
-        <v>53.258887095876219</v>
-      </c>
-      <c r="AJ49">
-        <f t="shared" si="9"/>
         <v>86.642853950415457</v>
       </c>
       <c r="AL49">
@@ -6136,11 +6135,11 @@
       </c>
       <c r="AO49">
         <f t="shared" si="14"/>
-        <v>52.574764925712749</v>
+        <v>52.582180030179437</v>
       </c>
       <c r="AP49">
         <f t="shared" si="15"/>
-        <v>86.30998296457463</v>
+        <v>86.315782309303174</v>
       </c>
     </row>
     <row r="50" spans="1:42" x14ac:dyDescent="0.2">
@@ -6172,11 +6171,11 @@
       </c>
       <c r="AO50" s="2">
         <f>AVERAGE(AO3:AO49)</f>
-        <v>6.7611442505092523</v>
+        <v>6.7683237077500591</v>
       </c>
       <c r="AP50" s="2">
         <f>AVERAGE(AP3:AP49)</f>
-        <v>13.919183654194741</v>
+        <v>13.889515242921334</v>
       </c>
     </row>
   </sheetData>
